--- a/Result/checksun_type/工業型機器人.xlsx
+++ b/Result/checksun_type/工業型機器人.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>444.0</t>
+          <t>456.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-18.05</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-18.35</t>
+          <t>-21.06</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>456</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,57 +1029,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>15.03</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>711.8</t>
+          <t>702.8</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>747.5</t>
+          <t>740.6</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>770.14</t>
+          <t>771.72</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>668.28</t>
+          <t>670.89</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-58.22</t>
+          <t>-56.83</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-20.97</t>
+          <t>-24.23</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-15.45</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-114.74</t>
+          <t>-117.18</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>410737.9315068494</t>
+          <t>410925.6604095563</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>306608.0</t>
+          <t>310495.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>359349.6</t>
+          <t>321361.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>389319.8</t>
+          <t>392151.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>672018.02</t>
+          <t>673300.18</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-29970</t>
+          <t>-70790</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-52561.74436342486</t>
+          <t>-52226.97299810403</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-52013.69</v>
+        <v>-50385.73</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>165.39</t>
+          <t>156.60</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,27 +1177,27 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>8.851156069364162</t>
+          <t>5.417317991953463</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>103.4820897941542</t>
+          <t>102.0481335952849</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>93.23644997543802</t>
+          <t>95.34284575725091</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>18.28</t>
+          <t>17.68</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>59.81</t>
+          <t>56.77</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1267,17 +1267,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>679.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>444.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-16.82</t>
+          <t>-18.35</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>456</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,62 +1455,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>15.24</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>722.4</t>
+          <t>711.8</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>754.55</t>
+          <t>747.5</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>768.06</t>
+          <t>770.14</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>665.62</t>
+          <t>668.28</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-66.42</t>
+          <t>-58.22</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-18.85</t>
+          <t>-20.97</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-112.59</t>
+          <t>-114.74</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>410737.9315068494</t>
+          <t>410925.6604095563</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>228169.0</t>
+          <t>306608.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>354425.0</t>
+          <t>359349.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>390521.3</t>
+          <t>389319.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>675976.46</t>
+          <t>672018.02</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-36096</t>
+          <t>-29970</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-52661.39013608223</t>
+          <t>-52561.74436342486</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-52065.26</v>
+        <v>-52013.69</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>170.36</t>
+          <t>165.39</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,42 +1608,42 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>8.851156069364162</t>
+          <t>5.417317991953463</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>103.4820897941542</t>
+          <t>102.0481335952849</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>93.23644997543802</t>
+          <t>95.34284575725091</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>59.81</t>
+          <t>56.77</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>699.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>679.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>448.0</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-16.12</t>
+          <t>-16.82</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>456</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1891,57 +1891,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>722.4</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>760.7</t>
+          <t>754.55</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>766.1</t>
+          <t>768.06</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>662.74</t>
+          <t>665.62</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-81.98</t>
+          <t>-66.42</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-17.19</t>
+          <t>-18.85</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-110.50</t>
+          <t>-112.59</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>410737.9315068494</t>
+          <t>410925.6604095563</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>323363.0</t>
+          <t>228169.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>471049.8</t>
+          <t>354425.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>445989.1</t>
+          <t>390521.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>679269.88</t>
+          <t>675976.46</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>25060</t>
+          <t>-36096</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-52769.77804672284</t>
+          <t>-52661.39013608223</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-41875.27</v>
+        <v>-52065.26</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>172.66</t>
+          <t>170.36</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,42 +2039,42 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>8.851156069364162</t>
+          <t>5.417317991953463</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>103.4820897941542</t>
+          <t>102.0481335952849</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>93.23644997543802</t>
+          <t>95.34284575725091</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.62</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>59.81</t>
+          <t>56.77</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>710.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>606.0</t>
+          <t>448.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>713.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-14.24</t>
+          <t>-16.12</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>456</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>15.60</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>737.8</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>765.9</t>
+          <t>760.7</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>763.84</t>
+          <t>766.1</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>659.24</t>
+          <t>662.74</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-105.47</t>
+          <t>-81.98</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-15.43</t>
+          <t>-17.19</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-7.51</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-108.35</t>
+          <t>-110.50</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>410737.9315068494</t>
+          <t>410925.6604095563</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>438172.0</t>
+          <t>323363.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>490720.6</t>
+          <t>471049.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>467960.7</t>
+          <t>445989.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>683118.66</t>
+          <t>679269.88</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>22759</t>
+          <t>25060</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-54750.59814941225</t>
+          <t>-52769.77804672284</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-36021.95</v>
+        <v>-41875.27</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>178.78</t>
+          <t>172.66</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,42 +2470,42 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>8.851156069364162</t>
+          <t>5.417317991953463</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>103.4820897941542</t>
+          <t>102.0481335952849</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>93.23644997543802</t>
+          <t>95.34284575725091</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.78</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>59.81</t>
+          <t>56.77</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>748.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>710.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>713.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>606.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-8.64</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-14.24</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>18.93</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>456</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.07</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>52.47</t>
+          <t>27.16</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>735.2</t>
+          <t>737.8</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>771.95</t>
+          <t>765.9</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>761.14</t>
+          <t>763.84</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>655.4</t>
+          <t>659.24</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-163.86</t>
+          <t>-105.47</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-14.59</t>
+          <t>-15.43</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-7.51</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-106.15</t>
+          <t>-108.35</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>410737.9315068494</t>
+          <t>410925.6604095563</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>500436.0</t>
+          <t>438172.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>462942.0</t>
+          <t>490720.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>451797.8</t>
+          <t>467960.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>687666.36</t>
+          <t>683118.66</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>22759</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-58155.80653900002</t>
+          <t>-54750.59814941225</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-38674.54</v>
+        <v>-36021.95</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>173.80</t>
+          <t>178.78</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,42 +2901,42 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>8.851156069364162</t>
+          <t>5.417317991953463</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>103.4820897941542</t>
+          <t>102.0481335952849</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>93.23644997543802</t>
+          <t>95.34284575725091</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>59.81</t>
+          <t>56.77</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>751.0</t>
+          <t>748.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>376.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-6.71</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-12.12</t>
+          <t>-15.76</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>456</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>57.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>59.26</t>
+          <t>52.47</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>16.13</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>740.6</t>
+          <t>735.2</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>780.25</t>
+          <t>771.95</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>759.12</t>
+          <t>761.14</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>651.25</t>
+          <t>655.4</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-267.06</t>
+          <t>-163.86</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-14.59</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-103.63</t>
+          <t>-106.15</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>410737.9315068494</t>
+          <t>410925.6604095563</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>281985.0</t>
+          <t>500436.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>419290.0</t>
+          <t>462942.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>432429.0</t>
+          <t>451797.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>696544.24</t>
+          <t>687666.36</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-13139</t>
+          <t>11144</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-61697.85522680334</t>
+          <t>-58155.80653900002</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-47753.86</v>
+        <v>-38674.54</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>185.66</t>
+          <t>173.80</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,22 +3332,22 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>8.851156069364162</t>
+          <t>5.417317991953463</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>103.4820897941542</t>
+          <t>102.0481335952849</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>93.23644997543802</t>
+          <t>95.34284575725091</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
@@ -3357,17 +3357,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>59.81</t>
+          <t>56.77</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>756.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>761.0</t>
+          <t>751.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>742.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1050.0</t>
+          <t>376.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>747.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-9.41</t>
+          <t>-12.12</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>32.80</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>456</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>57.41</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>59.26</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.67</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>744.8</t>
+          <t>740.6</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>789.55</t>
+          <t>780.25</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>756.36</t>
+          <t>759.12</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>646.51</t>
+          <t>651.25</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-972.48</t>
+          <t>-267.06</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-11.64</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-101.21</t>
+          <t>-103.63</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>410737.9315068494</t>
+          <t>410925.6604095563</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>811293.0</t>
+          <t>281985.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>426617.6</t>
+          <t>419290.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>444428.2</t>
+          <t>432429.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>709505.24</t>
+          <t>696544.24</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-17810</t>
+          <t>-13139</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-64233.12749927216</t>
+          <t>-61697.85522680334</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-35613.35</v>
+        <v>-47753.86</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>194.46</t>
+          <t>185.66</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,42 +3763,42 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>8.851156069364162</t>
+          <t>5.417317991953463</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>103.4820897941542</t>
+          <t>102.0481335952849</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>93.23644997543802</t>
+          <t>95.34284575725091</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>59.81</t>
+          <t>56.77</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>763.0</t>
+          <t>756.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>761.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>757.0</t>
+          <t>742.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>747.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>582.0</t>
+          <t>1050.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>727.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-14.75</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-14.47</t>
+          <t>-9.41</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>32.80</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>456</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-5.67</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>16.99</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>742.2</t>
+          <t>744.8</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>800.05</t>
+          <t>789.55</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>752.5</t>
+          <t>756.36</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>641.89</t>
+          <t>646.51</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-960.76</t>
+          <t>-972.48</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-13.37</t>
+          <t>-11.64</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-98.27</t>
+          <t>-101.21</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>410737.9315068494</t>
+          <t>410925.6604095563</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>421717.0</t>
+          <t>811293.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>420928.4</t>
+          <t>426617.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>387118.0</t>
+          <t>444428.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>709717.56</t>
+          <t>709505.24</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>33810</t>
+          <t>-17810</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-69436.72264493338</t>
+          <t>-64233.12749927216</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-73709.44</v>
+        <v>-35613.35</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>178.01</t>
+          <t>194.46</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,42 +4194,42 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>8.851156069364162</t>
+          <t>5.417317991953463</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>103.4820897941542</t>
+          <t>102.0481335952849</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>93.23644997543802</t>
+          <t>95.34284575725091</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>20.28</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>59.81</t>
+          <t>56.77</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>763.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>744.0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>757.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>727.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>412.0</t>
+          <t>582.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>727.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-8.35</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>14.07</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-14.47</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>456</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>11.39</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>8.71</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>750.8</t>
+          <t>742.2</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>813.65</t>
+          <t>800.05</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>748.46</t>
+          <t>752.5</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>637.92</t>
+          <t>641.89</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-308.26</t>
+          <t>-960.76</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-11.00</t>
+          <t>-13.37</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-94.13</t>
+          <t>-98.27</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>410737.9315068494</t>
+          <t>410925.6604095563</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>299279.0</t>
+          <t>421717.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>445200.8</t>
+          <t>420928.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>390301.9</t>
+          <t>387118.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>708135.86</t>
+          <t>709717.56</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>54898</t>
+          <t>33810</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-68659.86428072592</t>
+          <t>-69436.72264493338</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-83759.66</v>
+        <v>-73709.44</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>173.80</t>
+          <t>178.01</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,27 +4625,27 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>8.851156069364162</t>
+          <t>5.417317991953463</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>103.4820897941542</t>
+          <t>102.0481335952849</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>93.23644997543802</t>
+          <t>95.34284575725091</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>59.81</t>
+          <t>56.77</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
+          <t>700.0</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
           <t>744.0</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>754.0</t>
-        </is>
-      </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>709.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>727.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>376.0</t>
+          <t>412.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-6.71</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>14.07</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-12.59</t>
+          <t>-15.76</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>456</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>13.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>33.47</t>
+          <t>23.56</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-8.69</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>8.71</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>754.6</t>
+          <t>750.8</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>826.4</t>
+          <t>813.65</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>743.7</t>
+          <t>748.46</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>633.74</t>
+          <t>637.92</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-171.67</t>
+          <t>-308.26</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-6.70</t>
+          <t>-11.00</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-89.60</t>
+          <t>-94.13</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>410737.9315068494</t>
+          <t>410925.6604095563</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>282176.0</t>
+          <t>299279.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>440653.6</t>
+          <t>445200.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>416013.2</t>
+          <t>390301.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>712407.32</t>
+          <t>708135.86</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>24640</t>
+          <t>54898</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-65914.4463804971</t>
+          <t>-68659.86428072592</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-82007.34</v>
+        <v>-83759.66</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>184.13</t>
+          <t>173.80</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,27 +5056,27 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>8.851156069364162</t>
+          <t>5.417317991953463</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>103.4820897941542</t>
+          <t>102.0481335952849</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>93.23644997543802</t>
+          <t>95.34284575725091</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>19.57</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>59.81</t>
+          <t>56.77</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>764.0</t>
+          <t>744.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>754.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>709.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>414.0</t>
+          <t>376.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>768.0</t>
+          <t>743.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>-10.73</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-9.65</t>
+          <t>-12.59</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12.93</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>456</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>13.79</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>40.54</t>
+          <t>33.47</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-9.62</t>
+          <t>-8.69</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>11.12</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>756.0</t>
+          <t>754.6</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>836.45</t>
+          <t>826.4</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>743.7</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>629.3</t>
+          <t>633.74</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-128.95</t>
+          <t>-171.67</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-6.70</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-85.14</t>
+          <t>-89.60</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>410737.9315068494</t>
+          <t>410925.6604095563</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>318623.0</t>
+          <t>282176.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>445568.0</t>
+          <t>440653.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>448611.4</t>
+          <t>416013.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>716409.4</t>
+          <t>712407.32</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-3043</t>
+          <t>24640</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-62988.46483201619</t>
+          <t>-65914.4463804971</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-74742.74000000001</v>
+        <v>-82007.34</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>193.69</t>
+          <t>184.13</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,27 +5487,27 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>8.851156069364162</t>
+          <t>5.417317991953463</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>103.4820897941542</t>
+          <t>102.0481335952849</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>93.23644997543802</t>
+          <t>95.34284575725091</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>59.81</t>
+          <t>56.77</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>760.0</t>
+          <t>764.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>783.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>757.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>768.0</t>
+          <t>743.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3457.008</t>
+          <t>4701.928</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>25.67</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-8.94</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10.72</t>
+          <t>14.59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5770,57 +5770,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>204.6</t>
+          <t>201.2</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>214.72</t>
+          <t>213.98</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>215.02</t>
+          <t>214.79</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>213.92</t>
+          <t>213.72</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-237.34</t>
+          <t>-163.83</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-105.33</t>
+          <t>-109.03</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1330844234.989146</t>
+          <t>1330911637.588873</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>685726947.0</t>
+          <t>918324556.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>817177497.0</t>
+          <t>878838587.8</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>650263422.9</t>
+          <t>691621829.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>838743112.42</t>
+          <t>845368183.24</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>166914074</t>
+          <t>187216758</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-18945073.74552811</t>
+          <t>-10057429.00225778</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>28134361.9</v>
+        <v>38824617.09</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-11.87</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,27 +5918,27 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>-4.950545490506922</t>
+          <t>0.5246961718756727</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-6.771993768554716</t>
+          <t>-3.316042339543704</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-1.150062658716753</t>
+          <t>-1.626286550608443</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>70228</t>
+          <t>68282</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>195.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5006.119</t>
+          <t>3457.008</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>25.67</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-8.94</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>10.72</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,57 +6201,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>207.7</t>
+          <t>204.6</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>215.3</t>
+          <t>214.72</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>215.19</t>
+          <t>215.02</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>214.13</t>
+          <t>213.92</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-511.52</t>
+          <t>-237.34</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-102.17</t>
+          <t>-105.33</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1330844234.989146</t>
+          <t>1330911637.588873</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>1002681628.0</t>
+          <t>685726947.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>756541012.2</t>
+          <t>817177497.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>657490336.6</t>
+          <t>650263422.9</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>837159531.8</t>
+          <t>838743112.42</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>99050675</t>
+          <t>166914074</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-27504971.13491017</t>
+          <t>-18945073.74552811</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>36778942.52</v>
+        <v>28134361.9</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-8.68</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,42 +6349,42 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>-4.950545490506922</t>
+          <t>0.5246961718756727</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-6.771993768554716</t>
+          <t>-3.316042339543704</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-1.150062658716753</t>
+          <t>-1.626286550608443</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>70228</t>
+          <t>68282</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
+          <t>195.0</t>
+        </is>
+      </c>
+      <c r="CD14" t="inlineStr">
+        <is>
           <t>201.0</t>
         </is>
       </c>
-      <c r="CD14" t="inlineStr">
-        <is>
-          <t>205.0</t>
-        </is>
-      </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5932.964</t>
+          <t>5006.119</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>15.06</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-5.96</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18.40</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6632,57 +6632,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>211.3</t>
+          <t>207.7</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>215.75</t>
+          <t>215.3</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>215.46</t>
+          <t>215.19</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>214.3</t>
+          <t>214.13</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-1398.14</t>
+          <t>-511.52</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-99.40</t>
+          <t>-102.17</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1330844234.989146</t>
+          <t>1330911637.588873</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>1219768240.0</t>
+          <t>1002681628.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>600139410.0</t>
+          <t>756541012.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>623193432.6</t>
+          <t>657490336.6</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>825475916.8</t>
+          <t>837159531.8</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-23054022</t>
+          <t>99050675</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-39192955.43611298</t>
+          <t>-27504971.13491017</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>13855379.65</v>
+        <v>36778942.52</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-8.68</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,27 +6780,27 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>-4.950545490506922</t>
+          <t>0.5246961718756727</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-6.771993768554716</t>
+          <t>-3.316042339543704</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-1.150062658716753</t>
+          <t>-1.626286550608443</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>70228</t>
+          <t>68282</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>196.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2678.776</t>
+          <t>5932.964</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-18.01</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>-5.96</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>18.40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7063,57 +7063,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>213.8</t>
+          <t>211.3</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>215.92</t>
+          <t>215.75</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>215.67</t>
+          <t>215.46</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>214.41</t>
+          <t>214.3</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-230.30</t>
+          <t>-1398.14</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-97.28</t>
+          <t>-99.40</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1330844234.989146</t>
+          <t>1330911637.588873</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>567691568.0</t>
+          <t>1219768240.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>439899852.8</t>
+          <t>600139410.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>536558115.5</t>
+          <t>623193432.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>818287549.92</t>
+          <t>825475916.8</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-96658262</t>
+          <t>-23054022</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-48838107.26937589</t>
+          <t>-39192955.43611298</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-42646682.16</v>
+        <v>13855379.65</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,22 +7211,22 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>-4.950545490506922</t>
+          <t>0.5246961718756727</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-6.771993768554716</t>
+          <t>-3.316042339543704</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-1.150062658716753</t>
+          <t>-1.626286550608443</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>70228</t>
+          <t>68282</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>209.5</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2889.254</t>
+          <t>2678.776</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>209.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-18.01</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7489,62 +7489,62 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>215.3</t>
+          <t>213.8</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>216.22</t>
+          <t>215.92</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>215.78</t>
+          <t>215.67</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>214.37</t>
+          <t>214.41</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-110.18</t>
+          <t>-230.30</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-95.72</t>
+          <t>-97.28</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1330844234.989146</t>
+          <t>1330911637.588873</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>610019102.0</t>
+          <t>567691568.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>504405071.0</t>
+          <t>439899852.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>521300497.5</t>
+          <t>536558115.5</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>817903324.56</t>
+          <t>818287549.92</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-16895426</t>
+          <t>-96658262</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-49963820.92529882</t>
+          <t>-48838107.26937589</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-51975459.81</v>
+        <v>-42646682.16</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-4.11</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,27 +7642,27 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>-4.950545490506922</t>
+          <t>0.5246961718756727</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-6.771993768554716</t>
+          <t>-3.316042339543704</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-1.150062658716753</t>
+          <t>-1.626286550608443</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>70228</t>
+          <t>68282</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>217.0</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>209.0</t>
+          <t>209.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>209.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1787.511</t>
+          <t>2889.254</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-7.81</t>
+          <t>-8.81</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,12 +7905,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7920,62 +7920,62 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>218.3</t>
+          <t>215.3</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>216.95</t>
+          <t>216.22</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>215.86</t>
+          <t>215.78</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>214.34</t>
+          <t>214.37</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-40.27</t>
+          <t>-110.18</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-94.54</t>
+          <t>-95.72</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1330844234.989146</t>
+          <t>1330911637.588873</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>382544523.0</t>
+          <t>610019102.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>483349348.8</t>
+          <t>504405071.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>525432672.9</t>
+          <t>521300497.5</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>817817970.04</t>
+          <t>817903324.56</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-42083324</t>
+          <t>-16895426</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-49598068.40058749</t>
+          <t>-49963820.92529882</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-67981111.53</v>
+        <v>-51975459.81</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-4.11</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,42 +8073,42 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>-4.950545490506922</t>
+          <t>0.5246961718756727</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-6.771993768554716</t>
+          <t>-3.316042339543704</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-1.150062658716753</t>
+          <t>-1.626286550608443</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>70228</t>
+          <t>68282</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>216.5</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>216.5</t>
+          <t>217.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>212.5</t>
+          <t>209.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1014.871</t>
+          <t>1787.511</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,72 +8220,72 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>214.0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-10.88</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-2.87</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-8.01</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>220.0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
           <t>218.0</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>-9.82</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>-3.6</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>220.0</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>218.0</t>
-        </is>
-      </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,17 +8336,17 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -8356,57 +8356,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>220.2</t>
+          <t>218.3</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>217.68</t>
+          <t>216.95</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>215.88</t>
+          <t>215.86</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>214.24</t>
+          <t>214.34</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-40.27</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-93.99</t>
+          <t>-94.54</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,45 +8426,45 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1330844234.989146</t>
+          <t>1330911637.588873</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>220673617.0</t>
+          <t>382544523.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>558439661.0</t>
+          <t>483349348.8</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>552641417.0</t>
+          <t>525432672.9</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>844929542.22</t>
+          <t>817817970.04</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>5798244</t>
+          <t>-42083324</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-46255696.92225825</t>
+          <t>-49598068.40058749</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-64046155.11</v>
+        <v>-67981111.53</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,27 +8504,27 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>-4.950545490506922</t>
+          <t>0.5246961718756727</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-6.771993768554716</t>
+          <t>-3.316042339543704</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-1.150062658716753</t>
+          <t>-1.626286550608443</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>70228</t>
+          <t>68282</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>219.5</t>
+          <t>216.5</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>216.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>216.0</t>
+          <t>212.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1945.088</t>
+          <t>1014.871</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>217.5</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-9.57</t>
+          <t>-12.95</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
           <t>6.25</t>
         </is>
       </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>35.42</t>
-        </is>
-      </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>220.7</t>
+          <t>220.2</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>217.85</t>
+          <t>217.68</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>215.58</t>
+          <t>215.88</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>214.11</t>
+          <t>214.24</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-93.93</t>
+          <t>-93.99</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1330844234.989146</t>
+          <t>1330911637.588873</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>418570454.0</t>
+          <t>220673617.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>646247455.2</t>
+          <t>558439661.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>657338972.5</t>
+          <t>552641417.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>852341614.72</t>
+          <t>844929542.22</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-11091517</t>
+          <t>5798244</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-43021068.16036207</t>
+          <t>-46255696.92225825</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-38794114.76</v>
+        <v>-64046155.11</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,22 +8935,22 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>-4.950545490506922</t>
+          <t>0.5246961718756727</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>-6.771993768554716</t>
+          <t>-3.316042339543704</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>-1.150062658716753</t>
+          <t>-1.626286550608443</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>70228</t>
+          <t>68282</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>219.5</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
+          <t>220.0</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
+          <t>216.0</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
           <t>218.0</t>
-        </is>
-      </c>
-      <c r="CE20" t="inlineStr">
-        <is>
-          <t>211.0</t>
-        </is>
-      </c>
-      <c r="CF20" t="inlineStr">
-        <is>
-          <t>217.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3999.43</t>
+          <t>1945.088</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>217.0</t>
+          <t>217.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-9.32</t>
+          <t>-12.69</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-5.76</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>35.42</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>221.1</t>
+          <t>220.7</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>217.82</t>
+          <t>217.85</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>215.35</t>
+          <t>215.58</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>213.92</t>
+          <t>214.11</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>36.34</t>
+          <t>10.29</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-94.08</t>
+          <t>-93.93</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1330844234.989146</t>
+          <t>1330911637.588873</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>890217659.0</t>
+          <t>418570454.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>633216378.2</t>
+          <t>646247455.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>690143066.0</t>
+          <t>657338972.5</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>855601077.24</t>
+          <t>852341614.72</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-56926687</t>
+          <t>-11091517</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-43789605.14215445</t>
+          <t>-43021068.16036207</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-22537499.84</v>
+        <v>-38794114.76</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,27 +9366,27 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>-4.950545490506922</t>
+          <t>0.5246961718756727</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-6.771993768554716</t>
+          <t>-3.316042339543704</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>-1.150062658716753</t>
+          <t>-1.626286550608443</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>70228</t>
+          <t>68282</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>229.5</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>230.5</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>216.0</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>217.0</t>
+          <t>217.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2248.781</t>
+          <t>3999.43</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>217.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-13.35</t>
+          <t>-12.44</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9593,12 +9593,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>12.41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-5.76</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>96.43</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>221.5</t>
+          <t>221.1</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>217.88</t>
+          <t>217.82</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>215.07</t>
+          <t>215.35</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>213.77</t>
+          <t>213.92</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>85.30</t>
+          <t>36.34</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-94.62</t>
+          <t>-94.08</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1330844234.989146</t>
+          <t>1330911637.588873</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>504740491.0</t>
+          <t>890217659.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>538195924.0</t>
+          <t>633216378.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>629296351.2</t>
+          <t>690143066.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>860642512.9</t>
+          <t>855601077.24</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-91100427</t>
+          <t>-56926687</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-47653624.28847943</t>
+          <t>-43789605.14215445</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-49042482.63</v>
+        <v>-22537499.84</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,27 +9797,27 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>-4.950545490506922</t>
+          <t>0.5246961718756727</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>-6.771993768554716</t>
+          <t>-3.316042339543704</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>-1.150062658716753</t>
+          <t>-1.626286550608443</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>70228</t>
+          <t>68282</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>223.5</t>
+          <t>229.5</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>230.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>216.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>217.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3388.462</t>
+          <t>2248.781</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>223.5</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-12.59</t>
+          <t>-16.58</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-7.57</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10024,12 +10024,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10.51</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,12 +10060,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10075,62 +10075,62 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>96.43</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>220.5</t>
+          <t>221.5</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>217.35</t>
+          <t>217.88</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>214.8</t>
+          <t>215.07</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>213.48</t>
+          <t>213.77</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>86.80</t>
+          <t>85.30</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-95.77</t>
+          <t>-94.62</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1330844234.989146</t>
+          <t>1330911637.588873</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>757996084.0</t>
+          <t>504740491.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>567515997.0</t>
+          <t>538195924.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>613999882.3</t>
+          <t>629296351.2</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>872369467.16</t>
+          <t>860642512.9</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-46483885</t>
+          <t>-91100427</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-47401104.58973911</t>
+          <t>-47653624.28847943</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-43854101.39</v>
+        <v>-49042482.63</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,27 +10228,27 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>-4.950545490506922</t>
+          <t>0.5246961718756727</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-6.771993768554716</t>
+          <t>-3.316042339543704</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>-1.150062658716753</t>
+          <t>-1.626286550608443</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>70228</t>
+          <t>68282</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>222.0</t>
+          <t>223.5</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>220.5</t>
+          <t>222.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>223.5</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/工業型機器人.xlsx
+++ b/Result/checksun_type/工業型機器人.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>456.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-18.05</t>
+          <t>-22.67</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-21.06</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>565</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,57 +1029,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-6.42</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>702.8</t>
+          <t>686.2</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>740.6</t>
+          <t>733.3</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>771.72</t>
+          <t>772.84</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>670.89</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-56.83</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-24.23</t>
+          <t>-28.51</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-18.06</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-117.18</t>
+          <t>-120.08</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>410925.6604095563</t>
+          <t>411456.4132653062</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>310495.0</t>
+          <t>377978.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>321361.4</t>
+          <t>309322.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>392151.7</t>
+          <t>400021.6</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>673300.18</t>
+          <t>677723.46</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-70790</t>
+          <t>-90699</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-52226.97299810403</t>
+          <t>-50795.94465057103</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-50385.73</v>
+        <v>-42925.29</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>156.60</t>
+          <t>147.04</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>54.65</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>699.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>444.0</t>
+          <t>456.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-18.05</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-18.35</t>
+          <t>-21.06</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>565</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>15.03</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>711.8</t>
+          <t>702.8</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>747.5</t>
+          <t>740.6</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>770.14</t>
+          <t>771.72</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>668.28</t>
+          <t>670.89</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-58.22</t>
+          <t>-56.83</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-20.97</t>
+          <t>-24.23</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-15.45</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-114.74</t>
+          <t>-117.18</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>410925.6604095563</t>
+          <t>411456.4132653062</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>306608.0</t>
+          <t>310495.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>359349.6</t>
+          <t>321361.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>389319.8</t>
+          <t>392151.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>672018.02</t>
+          <t>673300.18</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-29970</t>
+          <t>-70790</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-52561.74436342486</t>
+          <t>-52226.97299810403</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-52013.69</v>
+        <v>-50385.73</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>165.39</t>
+          <t>156.60</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>18.28</t>
+          <t>17.68</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>54.65</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1698,17 +1698,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>679.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>444.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-7.43</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-16.82</t>
+          <t>-18.35</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>565</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,62 +1886,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>15.24</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>722.4</t>
+          <t>711.8</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>754.55</t>
+          <t>747.5</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>768.06</t>
+          <t>770.14</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>665.62</t>
+          <t>668.28</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-66.42</t>
+          <t>-58.22</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-18.85</t>
+          <t>-20.97</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-112.59</t>
+          <t>-114.74</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>410925.6604095563</t>
+          <t>411456.4132653062</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>228169.0</t>
+          <t>306608.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>354425.0</t>
+          <t>359349.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>390521.3</t>
+          <t>389319.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>675976.46</t>
+          <t>672018.02</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-36096</t>
+          <t>-29970</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-52661.39013608223</t>
+          <t>-52561.74436342486</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-52065.26</v>
+        <v>-52013.69</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>170.36</t>
+          <t>165.39</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>54.65</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>699.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>679.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>448.0</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-9.44</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-16.12</t>
+          <t>-16.82</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>565</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2322,57 +2322,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>722.4</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>760.7</t>
+          <t>754.55</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>766.1</t>
+          <t>768.06</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>662.74</t>
+          <t>665.62</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-81.98</t>
+          <t>-66.42</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-17.19</t>
+          <t>-18.85</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-110.50</t>
+          <t>-112.59</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>410925.6604095563</t>
+          <t>411456.4132653062</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>323363.0</t>
+          <t>228169.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>471049.8</t>
+          <t>354425.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>445989.1</t>
+          <t>390521.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>679269.88</t>
+          <t>675976.46</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>25060</t>
+          <t>-36096</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-52769.77804672284</t>
+          <t>-52661.39013608223</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-41875.27</v>
+        <v>-52065.26</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>172.66</t>
+          <t>170.36</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.62</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>54.65</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>710.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>606.0</t>
+          <t>448.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>713.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-8.64</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-14.24</t>
+          <t>-16.12</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>565</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>15.60</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>737.8</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>765.9</t>
+          <t>760.7</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>763.84</t>
+          <t>766.1</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>659.24</t>
+          <t>662.74</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-105.47</t>
+          <t>-81.98</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-15.43</t>
+          <t>-17.19</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-7.51</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-108.35</t>
+          <t>-110.50</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>410925.6604095563</t>
+          <t>411456.4132653062</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>438172.0</t>
+          <t>323363.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>490720.6</t>
+          <t>471049.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>467960.7</t>
+          <t>445989.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>683118.66</t>
+          <t>679269.88</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>22759</t>
+          <t>25060</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-54750.59814941225</t>
+          <t>-52769.77804672284</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-36021.95</v>
+        <v>-41875.27</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>178.78</t>
+          <t>172.66</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.78</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>54.65</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>748.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>710.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>713.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>606.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-6.71</t>
+          <t>-12.85</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-14.24</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>18.93</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>565</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.07</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>52.47</t>
+          <t>27.16</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>735.2</t>
+          <t>737.8</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>771.95</t>
+          <t>765.9</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>761.14</t>
+          <t>763.84</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>655.4</t>
+          <t>659.24</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-163.86</t>
+          <t>-105.47</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-14.59</t>
+          <t>-15.43</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-7.51</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-106.15</t>
+          <t>-108.35</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>410925.6604095563</t>
+          <t>411456.4132653062</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>500436.0</t>
+          <t>438172.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>462942.0</t>
+          <t>490720.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>451797.8</t>
+          <t>467960.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>687666.36</t>
+          <t>683118.66</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>22759</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-58155.80653900002</t>
+          <t>-54750.59814941225</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-38674.54</v>
+        <v>-36021.95</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>173.80</t>
+          <t>178.78</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>54.65</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>751.0</t>
+          <t>748.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>376.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-10.84</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-12.12</t>
+          <t>-15.76</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>565</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>57.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>59.26</t>
+          <t>52.47</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>16.13</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>740.6</t>
+          <t>735.2</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>780.25</t>
+          <t>771.95</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>759.12</t>
+          <t>761.14</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>651.25</t>
+          <t>655.4</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-267.06</t>
+          <t>-163.86</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-14.59</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-103.63</t>
+          <t>-106.15</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>410925.6604095563</t>
+          <t>411456.4132653062</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>281985.0</t>
+          <t>500436.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>419290.0</t>
+          <t>462942.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>432429.0</t>
+          <t>451797.8</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>696544.24</t>
+          <t>687666.36</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-13139</t>
+          <t>11144</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-61697.85522680334</t>
+          <t>-58155.80653900002</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-47753.86</v>
+        <v>-38674.54</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>185.66</t>
+          <t>173.80</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3788,17 +3788,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>54.65</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>756.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>761.0</t>
+          <t>751.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>742.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1050.0</t>
+          <t>376.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>747.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-14.75</t>
+          <t>-15.63</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-9.41</t>
+          <t>-12.12</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>32.80</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>565</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>57.41</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>59.26</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.67</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>744.8</t>
+          <t>740.6</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>789.55</t>
+          <t>780.25</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>756.36</t>
+          <t>759.12</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>646.51</t>
+          <t>651.25</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-972.48</t>
+          <t>-267.06</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-11.64</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-101.21</t>
+          <t>-103.63</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>410925.6604095563</t>
+          <t>411456.4132653062</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>811293.0</t>
+          <t>281985.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>426617.6</t>
+          <t>419290.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>444428.2</t>
+          <t>432429.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>709505.24</t>
+          <t>696544.24</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-17810</t>
+          <t>-13139</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-64233.12749927216</t>
+          <t>-61697.85522680334</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-35613.35</v>
+        <v>-47753.86</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>194.46</t>
+          <t>185.66</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>54.65</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>763.0</t>
+          <t>756.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>761.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>757.0</t>
+          <t>742.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>747.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>582.0</t>
+          <t>1050.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>727.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-8.35</t>
+          <t>-19.2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-14.47</t>
+          <t>-9.41</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>32.80</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>565</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-5.67</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>16.99</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>742.2</t>
+          <t>744.8</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>800.05</t>
+          <t>789.55</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>752.5</t>
+          <t>756.36</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>641.89</t>
+          <t>646.51</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-960.76</t>
+          <t>-972.48</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-13.37</t>
+          <t>-11.64</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-98.27</t>
+          <t>-101.21</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>410925.6604095563</t>
+          <t>411456.4132653062</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>421717.0</t>
+          <t>811293.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>420928.4</t>
+          <t>426617.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>387118.0</t>
+          <t>444428.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>709717.56</t>
+          <t>709505.24</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>33810</t>
+          <t>-17810</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-69436.72264493338</t>
+          <t>-64233.12749927216</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-73709.44</v>
+        <v>-35613.35</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>178.01</t>
+          <t>194.46</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,22 +4645,22 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>20.28</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>54.65</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>763.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>744.0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>757.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>727.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>412.0</t>
+          <t>582.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>727.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.71</t>
+          <t>-12.54</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14.07</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-14.47</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>565</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>11.39</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>8.71</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>750.8</t>
+          <t>742.2</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>813.65</t>
+          <t>800.05</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>748.46</t>
+          <t>752.5</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>637.92</t>
+          <t>641.89</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-308.26</t>
+          <t>-960.76</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-11.00</t>
+          <t>-13.37</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-94.13</t>
+          <t>-98.27</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>410925.6604095563</t>
+          <t>411456.4132653062</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>299279.0</t>
+          <t>421717.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>445200.8</t>
+          <t>420928.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>390301.9</t>
+          <t>387118.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>708135.86</t>
+          <t>709717.56</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>54898</t>
+          <t>33810</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-68659.86428072592</t>
+          <t>-69436.72264493338</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-83759.66</v>
+        <v>-73709.44</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>173.80</t>
+          <t>178.01</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>54.65</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
+          <t>700.0</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
           <t>744.0</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>754.0</t>
-        </is>
-      </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>709.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>727.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>376.0</t>
+          <t>412.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-10.73</t>
+          <t>-10.84</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>14.07</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-12.59</t>
+          <t>-15.76</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>565</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>13.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>33.47</t>
+          <t>23.56</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-8.69</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>8.71</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>754.6</t>
+          <t>750.8</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>826.4</t>
+          <t>813.65</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>743.7</t>
+          <t>748.46</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>633.74</t>
+          <t>637.92</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-171.67</t>
+          <t>-308.26</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-6.70</t>
+          <t>-11.00</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-89.60</t>
+          <t>-94.13</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>410925.6604095563</t>
+          <t>411456.4132653062</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>282176.0</t>
+          <t>299279.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>440653.6</t>
+          <t>445200.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>416013.2</t>
+          <t>390301.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>712407.32</t>
+          <t>708135.86</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>24640</t>
+          <t>54898</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-65914.4463804971</t>
+          <t>-68659.86428072592</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-82007.34</v>
+        <v>-83759.66</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>184.13</t>
+          <t>173.80</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>19.57</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>54.65</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>764.0</t>
+          <t>744.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>754.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>709.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4701.928</t>
+          <t>3839.598</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-14.45</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14.59</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5770,57 +5770,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>201.2</t>
+          <t>196.6</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>213.98</t>
+          <t>212.75</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>214.79</t>
+          <t>214.42</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>213.72</t>
+          <t>213.34</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-163.83</t>
+          <t>-130.49</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-109.03</t>
+          <t>-113.40</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1330911637.588873</t>
+          <t>1330556225.941558</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>918324556.0</t>
+          <t>723074244.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>878838587.8</t>
+          <t>909915123.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>691621829.4</t>
+          <t>674907487.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>845368183.24</t>
+          <t>854335140.06</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>187216758</t>
+          <t>235007635</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-10057429.00225778</t>
+          <t>-3788069.634011253</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>38824617.09</v>
+        <v>30693406.89</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-11.87</t>
+          <t>-14.84</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>47.34</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>68282</t>
+          <t>65982</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>191.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3457.008</t>
+          <t>4701.928</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>25.67</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-8.94</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10.72</t>
+          <t>14.59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,57 +6201,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>204.6</t>
+          <t>201.2</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>214.72</t>
+          <t>213.98</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>215.02</t>
+          <t>214.79</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>213.92</t>
+          <t>213.72</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-237.34</t>
+          <t>-163.83</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-105.33</t>
+          <t>-109.03</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1330911637.588873</t>
+          <t>1330556225.941558</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>685726947.0</t>
+          <t>918324556.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>817177497.0</t>
+          <t>878838587.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>650263422.9</t>
+          <t>691621829.4</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>838743112.42</t>
+          <t>845368183.24</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>166914074</t>
+          <t>187216758</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-18945073.74552811</t>
+          <t>-10057429.00225778</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>28134361.9</v>
+        <v>38824617.09</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-11.87</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>47.34</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>68282</t>
+          <t>65982</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>195.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5006.119</t>
+          <t>3457.008</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-6.43</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>25.67</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-8.94</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>10.72</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6632,57 +6632,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>207.7</t>
+          <t>204.6</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>215.3</t>
+          <t>214.72</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>215.19</t>
+          <t>215.02</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>214.13</t>
+          <t>213.92</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-511.52</t>
+          <t>-237.34</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-102.17</t>
+          <t>-105.33</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1330911637.588873</t>
+          <t>1330556225.941558</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>1002681628.0</t>
+          <t>685726947.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>756541012.2</t>
+          <t>817177497.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>657490336.6</t>
+          <t>650263422.9</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>837159531.8</t>
+          <t>838743112.42</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>99050675</t>
+          <t>166914074</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-27504971.13491017</t>
+          <t>-18945073.74552811</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>36778942.52</v>
+        <v>28134361.9</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-8.68</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>47.34</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>68282</t>
+          <t>65982</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
+          <t>195.0</t>
+        </is>
+      </c>
+      <c r="CD15" t="inlineStr">
+        <is>
           <t>201.0</t>
         </is>
       </c>
-      <c r="CD15" t="inlineStr">
-        <is>
-          <t>205.0</t>
-        </is>
-      </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5932.964</t>
+          <t>5006.119</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-7.24</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>15.06</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-5.96</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18.40</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7063,57 +7063,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>211.3</t>
+          <t>207.7</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>215.75</t>
+          <t>215.3</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>215.46</t>
+          <t>215.19</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>214.3</t>
+          <t>214.13</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-1398.14</t>
+          <t>-511.52</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-99.40</t>
+          <t>-102.17</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1330911637.588873</t>
+          <t>1330556225.941558</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>1219768240.0</t>
+          <t>1002681628.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>600139410.0</t>
+          <t>756541012.2</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>623193432.6</t>
+          <t>657490336.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>825475916.8</t>
+          <t>837159531.8</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-23054022</t>
+          <t>99050675</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-39192955.43611298</t>
+          <t>-27504971.13491017</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>13855379.65</v>
+        <v>36778942.52</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-8.68</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>47.34</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>68282</t>
+          <t>65982</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>196.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2678.776</t>
+          <t>5932.964</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-9.92</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-18.01</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>-5.96</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>18.40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7494,57 +7494,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>213.8</t>
+          <t>211.3</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>215.92</t>
+          <t>215.75</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>215.67</t>
+          <t>215.46</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>214.41</t>
+          <t>214.3</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-230.30</t>
+          <t>-1398.14</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-97.28</t>
+          <t>-99.40</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1330911637.588873</t>
+          <t>1330556225.941558</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>567691568.0</t>
+          <t>1219768240.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>439899852.8</t>
+          <t>600139410.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>536558115.5</t>
+          <t>623193432.6</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>818287549.92</t>
+          <t>825475916.8</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-96658262</t>
+          <t>-23054022</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-48838107.26937589</t>
+          <t>-39192955.43611298</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-42646682.16</v>
+        <v>13855379.65</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>47.34</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>68282</t>
+          <t>65982</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>209.5</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2889.254</t>
+          <t>2678.776</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>209.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-8.81</t>
+          <t>-12.33</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-18.01</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,12 +7905,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7920,62 +7920,62 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>215.3</t>
+          <t>213.8</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>216.22</t>
+          <t>215.92</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>215.78</t>
+          <t>215.67</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>214.37</t>
+          <t>214.41</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-110.18</t>
+          <t>-230.30</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-95.72</t>
+          <t>-97.28</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1330911637.588873</t>
+          <t>1330556225.941558</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>610019102.0</t>
+          <t>567691568.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>504405071.0</t>
+          <t>439899852.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>521300497.5</t>
+          <t>536558115.5</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>817903324.56</t>
+          <t>818287549.92</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-16895426</t>
+          <t>-96658262</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-49963820.92529882</t>
+          <t>-48838107.26937589</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-51975459.81</v>
+        <v>-42646682.16</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-4.11</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>47.34</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>68282</t>
+          <t>65982</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>217.0</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>209.0</t>
+          <t>209.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>209.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1787.511</t>
+          <t>2889.254</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-10.88</t>
+          <t>-12.6</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,12 +8336,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8351,62 +8351,62 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>218.3</t>
+          <t>215.3</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>216.95</t>
+          <t>216.22</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>215.86</t>
+          <t>215.78</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>214.34</t>
+          <t>214.37</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-40.27</t>
+          <t>-110.18</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-94.54</t>
+          <t>-95.72</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1330911637.588873</t>
+          <t>1330556225.941558</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>382544523.0</t>
+          <t>610019102.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>483349348.8</t>
+          <t>504405071.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>525432672.9</t>
+          <t>521300497.5</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>817817970.04</t>
+          <t>817903324.56</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-42083324</t>
+          <t>-16895426</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-49598068.40058749</t>
+          <t>-49963820.92529882</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-67981111.53</v>
+        <v>-51975459.81</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-4.11</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8524,22 +8524,22 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>47.34</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>68282</t>
+          <t>65982</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>216.5</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>216.5</t>
+          <t>217.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>212.5</t>
+          <t>209.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1014.871</t>
+          <t>1787.511</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,72 +8651,72 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>214.0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-14.75</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-5.26</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-8.01</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>220.0</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
           <t>218.0</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>-12.95</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-2.87</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>220.0</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>218.0</t>
-        </is>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,17 +8767,17 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -8787,57 +8787,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>220.2</t>
+          <t>218.3</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>217.68</t>
+          <t>216.95</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>215.88</t>
+          <t>215.86</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>214.24</t>
+          <t>214.34</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-40.27</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-93.99</t>
+          <t>-94.54</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,45 +8857,45 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1330911637.588873</t>
+          <t>1330556225.941558</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>220673617.0</t>
+          <t>382544523.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>558439661.0</t>
+          <t>483349348.8</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>552641417.0</t>
+          <t>525432672.9</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>844929542.22</t>
+          <t>817817970.04</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>5798244</t>
+          <t>-42083324</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-46255696.92225825</t>
+          <t>-49598068.40058749</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-64046155.11</v>
+        <v>-67981111.53</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>47.34</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>68282</t>
+          <t>65982</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>219.5</t>
+          <t>216.5</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>216.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>216.0</t>
+          <t>212.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1945.088</t>
+          <t>1014.871</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>217.5</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-12.69</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
           <t>6.25</t>
         </is>
       </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>35.42</t>
-        </is>
-      </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>220.7</t>
+          <t>220.2</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>217.85</t>
+          <t>217.68</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>215.58</t>
+          <t>215.88</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>214.11</t>
+          <t>214.24</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-93.93</t>
+          <t>-93.99</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1330911637.588873</t>
+          <t>1330556225.941558</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>418570454.0</t>
+          <t>220673617.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>646247455.2</t>
+          <t>558439661.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>657338972.5</t>
+          <t>552641417.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>852341614.72</t>
+          <t>844929542.22</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-11091517</t>
+          <t>5798244</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-43021068.16036207</t>
+          <t>-46255696.92225825</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-38794114.76</v>
+        <v>-64046155.11</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>47.34</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>68282</t>
+          <t>65982</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>219.5</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
+          <t>220.0</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
+        <is>
+          <t>216.0</t>
+        </is>
+      </c>
+      <c r="CF21" t="inlineStr">
+        <is>
           <t>218.0</t>
-        </is>
-      </c>
-      <c r="CE21" t="inlineStr">
-        <is>
-          <t>211.0</t>
-        </is>
-      </c>
-      <c r="CF21" t="inlineStr">
-        <is>
-          <t>217.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3999.43</t>
+          <t>1945.088</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>217.0</t>
+          <t>217.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-12.44</t>
+          <t>-16.62</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9593,12 +9593,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-5.76</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>35.42</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>221.1</t>
+          <t>220.7</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>217.82</t>
+          <t>217.85</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>215.35</t>
+          <t>215.58</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>213.92</t>
+          <t>214.11</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>36.34</t>
+          <t>10.29</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-94.08</t>
+          <t>-93.93</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1330911637.588873</t>
+          <t>1330556225.941558</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>890217659.0</t>
+          <t>418570454.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>633216378.2</t>
+          <t>646247455.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>690143066.0</t>
+          <t>657338972.5</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>855601077.24</t>
+          <t>852341614.72</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-56926687</t>
+          <t>-11091517</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-43789605.14215445</t>
+          <t>-43021068.16036207</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-22537499.84</v>
+        <v>-38794114.76</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>47.34</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>68282</t>
+          <t>65982</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>229.5</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>230.5</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>216.0</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>217.0</t>
+          <t>217.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2248.781</t>
+          <t>3999.43</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>217.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-16.58</t>
+          <t>-16.35</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10024,12 +10024,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>12.41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-5.76</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>96.43</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>221.5</t>
+          <t>221.1</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>217.88</t>
+          <t>217.82</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>215.07</t>
+          <t>215.35</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>213.77</t>
+          <t>213.92</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>85.30</t>
+          <t>36.34</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-94.62</t>
+          <t>-94.08</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1330911637.588873</t>
+          <t>1330556225.941558</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>504740491.0</t>
+          <t>890217659.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>538195924.0</t>
+          <t>633216378.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>629296351.2</t>
+          <t>690143066.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>860642512.9</t>
+          <t>855601077.24</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-91100427</t>
+          <t>-56926687</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-47653624.28847943</t>
+          <t>-43789605.14215445</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-49042482.63</v>
+        <v>-22537499.84</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>47.34</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>68282</t>
+          <t>65982</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>223.5</t>
+          <t>229.5</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>230.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>222.5</t>
+          <t>216.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>217.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/工業型機器人.xlsx
+++ b/Result/checksun_type/工業型機器人.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>371.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-22.67</t>
+          <t>-23.31</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,57 +1029,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-6.42</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>686.2</t>
+          <t>671.6</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>733.3</t>
+          <t>725.65</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>772.84</t>
+          <t>773.56</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>675.4</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-57.81</t>
+          <t>-53.49</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-28.51</t>
+          <t>-32.01</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-18.06</t>
+          <t>-20.85</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-120.08</t>
+          <t>-123.18</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>411456.4132653062</t>
+          <t>411289.6525423729</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>377978.0</t>
+          <t>241508.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>309322.6</t>
+          <t>292951.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>400021.6</t>
+          <t>382000.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>677723.46</t>
+          <t>675976.12</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-90699</t>
+          <t>-89049</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-50795.94465057103</t>
+          <t>-50191.19890369411</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-42925.29</v>
+        <v>-46865.1</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>147.04</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>54.65</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>693.0</t>
+          <t>667.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>456.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-18.05</t>
+          <t>-22.67</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-21.06</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-6.42</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>702.8</t>
+          <t>686.2</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>740.6</t>
+          <t>733.3</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>771.72</t>
+          <t>772.84</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>670.89</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-56.83</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-24.23</t>
+          <t>-28.51</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-18.06</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-117.18</t>
+          <t>-120.08</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>411456.4132653062</t>
+          <t>411289.6525423729</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>310495.0</t>
+          <t>377978.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>321361.4</t>
+          <t>309322.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>392151.7</t>
+          <t>400021.6</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>673300.18</t>
+          <t>677723.46</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-70790</t>
+          <t>-90699</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-52226.97299810403</t>
+          <t>-50795.94465057103</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-50385.73</v>
+        <v>-42925.29</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>156.60</t>
+          <t>147.04</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>54.65</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>699.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>444.0</t>
+          <t>456.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-7.43</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-18.05</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-18.35</t>
+          <t>-21.06</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1891,57 +1891,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>15.03</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>711.8</t>
+          <t>702.8</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>747.5</t>
+          <t>740.6</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>770.14</t>
+          <t>771.72</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>668.28</t>
+          <t>670.89</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-58.22</t>
+          <t>-56.83</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-20.97</t>
+          <t>-24.23</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-15.45</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-114.74</t>
+          <t>-117.18</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>411456.4132653062</t>
+          <t>411289.6525423729</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>306608.0</t>
+          <t>310495.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>359349.6</t>
+          <t>321361.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>389319.8</t>
+          <t>392151.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>672018.02</t>
+          <t>673300.18</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-29970</t>
+          <t>-70790</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-52561.74436342486</t>
+          <t>-52226.97299810403</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-52013.69</v>
+        <v>-50385.73</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>165.39</t>
+          <t>156.60</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>18.28</t>
+          <t>17.68</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>54.65</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>679.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>444.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-9.44</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-16.82</t>
+          <t>-18.35</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,62 +2317,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>15.24</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>722.4</t>
+          <t>711.8</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>754.55</t>
+          <t>747.5</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>768.06</t>
+          <t>770.14</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>665.62</t>
+          <t>668.28</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-66.42</t>
+          <t>-58.22</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-18.85</t>
+          <t>-20.97</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-112.59</t>
+          <t>-114.74</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>411456.4132653062</t>
+          <t>411289.6525423729</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>228169.0</t>
+          <t>306608.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>354425.0</t>
+          <t>359349.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>390521.3</t>
+          <t>389319.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>675976.46</t>
+          <t>672018.02</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-36096</t>
+          <t>-29970</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-52661.39013608223</t>
+          <t>-52561.74436342486</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-52065.26</v>
+        <v>-52013.69</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>170.36</t>
+          <t>165.39</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>54.65</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>699.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>679.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>448.0</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-10.47</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-16.12</t>
+          <t>-16.82</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2753,57 +2753,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>722.4</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>760.7</t>
+          <t>754.55</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>766.1</t>
+          <t>768.06</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>662.74</t>
+          <t>665.62</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-81.98</t>
+          <t>-66.42</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-17.19</t>
+          <t>-18.85</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-110.50</t>
+          <t>-112.59</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>411456.4132653062</t>
+          <t>411289.6525423729</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>323363.0</t>
+          <t>228169.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>471049.8</t>
+          <t>354425.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>445989.1</t>
+          <t>390521.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>679269.88</t>
+          <t>675976.46</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>25060</t>
+          <t>-36096</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-52769.77804672284</t>
+          <t>-52661.39013608223</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-41875.27</v>
+        <v>-52065.26</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>172.66</t>
+          <t>170.36</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.62</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>54.65</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>710.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>606.0</t>
+          <t>448.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>713.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-12.85</t>
+          <t>-11.41</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-14.24</t>
+          <t>-16.12</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>15.60</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>737.8</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>765.9</t>
+          <t>760.7</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>763.84</t>
+          <t>766.1</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>659.24</t>
+          <t>662.74</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-105.47</t>
+          <t>-81.98</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-15.43</t>
+          <t>-17.19</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-7.51</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-108.35</t>
+          <t>-110.50</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>411456.4132653062</t>
+          <t>411289.6525423729</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>438172.0</t>
+          <t>323363.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>490720.6</t>
+          <t>471049.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>467960.7</t>
+          <t>445989.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>683118.66</t>
+          <t>679269.88</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>22759</t>
+          <t>25060</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-54750.59814941225</t>
+          <t>-52769.77804672284</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-36021.95</v>
+        <v>-41875.27</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>178.78</t>
+          <t>172.66</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.78</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>54.65</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>748.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>710.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>713.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>606.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-10.84</t>
+          <t>-13.91</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-14.24</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>18.93</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.07</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>52.47</t>
+          <t>27.16</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>735.2</t>
+          <t>737.8</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>771.95</t>
+          <t>765.9</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>761.14</t>
+          <t>763.84</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>655.4</t>
+          <t>659.24</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-163.86</t>
+          <t>-105.47</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-14.59</t>
+          <t>-15.43</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-7.51</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-106.15</t>
+          <t>-108.35</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>411456.4132653062</t>
+          <t>411289.6525423729</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>500436.0</t>
+          <t>438172.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>462942.0</t>
+          <t>490720.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>451797.8</t>
+          <t>467960.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>687666.36</t>
+          <t>683118.66</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>22759</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-58155.80653900002</t>
+          <t>-54750.59814941225</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-38674.54</v>
+        <v>-36021.95</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>173.80</t>
+          <t>178.78</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>54.65</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>751.0</t>
+          <t>748.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>376.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-15.63</t>
+          <t>-11.88</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-12.12</t>
+          <t>-15.76</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>57.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>59.26</t>
+          <t>52.47</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>16.13</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>740.6</t>
+          <t>735.2</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>780.25</t>
+          <t>771.95</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>759.12</t>
+          <t>761.14</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>651.25</t>
+          <t>655.4</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-267.06</t>
+          <t>-163.86</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-14.59</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-103.63</t>
+          <t>-106.15</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>411456.4132653062</t>
+          <t>411289.6525423729</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>281985.0</t>
+          <t>500436.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>419290.0</t>
+          <t>462942.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>432429.0</t>
+          <t>451797.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>696544.24</t>
+          <t>687666.36</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-13139</t>
+          <t>11144</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-61697.85522680334</t>
+          <t>-58155.80653900002</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-47753.86</v>
+        <v>-38674.54</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>185.66</t>
+          <t>173.80</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4219,17 +4219,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>54.65</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>756.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>761.0</t>
+          <t>751.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>742.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1050.0</t>
+          <t>376.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>747.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-19.2</t>
+          <t>-16.72</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-9.41</t>
+          <t>-12.12</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>32.80</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>57.41</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>59.26</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.67</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>744.8</t>
+          <t>740.6</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>789.55</t>
+          <t>780.25</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>756.36</t>
+          <t>759.12</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>646.51</t>
+          <t>651.25</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-972.48</t>
+          <t>-267.06</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-11.64</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-101.21</t>
+          <t>-103.63</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>411456.4132653062</t>
+          <t>411289.6525423729</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>811293.0</t>
+          <t>281985.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>426617.6</t>
+          <t>419290.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>444428.2</t>
+          <t>432429.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>709505.24</t>
+          <t>696544.24</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-17810</t>
+          <t>-13139</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-64233.12749927216</t>
+          <t>-61697.85522680334</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-35613.35</v>
+        <v>-47753.86</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>194.46</t>
+          <t>185.66</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>54.65</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>763.0</t>
+          <t>756.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>761.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>757.0</t>
+          <t>742.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>747.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>582.0</t>
+          <t>1050.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>727.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-12.54</t>
+          <t>-20.31</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-14.47</t>
+          <t>-9.41</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>32.80</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-5.67</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>16.99</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>742.2</t>
+          <t>744.8</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>800.05</t>
+          <t>789.55</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>752.5</t>
+          <t>756.36</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>641.89</t>
+          <t>646.51</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-960.76</t>
+          <t>-972.48</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-13.37</t>
+          <t>-11.64</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-98.27</t>
+          <t>-101.21</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>411456.4132653062</t>
+          <t>411289.6525423729</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>421717.0</t>
+          <t>811293.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>420928.4</t>
+          <t>426617.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>387118.0</t>
+          <t>444428.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>709717.56</t>
+          <t>709505.24</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>33810</t>
+          <t>-17810</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-69436.72264493338</t>
+          <t>-64233.12749927216</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-73709.44</v>
+        <v>-35613.35</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>178.01</t>
+          <t>194.46</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>20.28</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>54.65</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>763.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>744.0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>757.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>727.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>412.0</t>
+          <t>582.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>727.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-10.84</t>
+          <t>-13.59</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>14.07</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-14.47</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>11.39</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>8.71</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>750.8</t>
+          <t>742.2</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>813.65</t>
+          <t>800.05</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>748.46</t>
+          <t>752.5</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>637.92</t>
+          <t>641.89</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-308.26</t>
+          <t>-960.76</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-11.00</t>
+          <t>-13.37</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-94.13</t>
+          <t>-98.27</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>411456.4132653062</t>
+          <t>411289.6525423729</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>299279.0</t>
+          <t>421717.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>445200.8</t>
+          <t>420928.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>390301.9</t>
+          <t>387118.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>708135.86</t>
+          <t>709717.56</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>54898</t>
+          <t>33810</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-68659.86428072592</t>
+          <t>-69436.72264493338</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-83759.66</v>
+        <v>-73709.44</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>173.80</t>
+          <t>178.01</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>54.65</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
+          <t>700.0</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
           <t>744.0</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>754.0</t>
-        </is>
-      </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>709.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>727.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3839.598</t>
+          <t>2437.772</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5770,57 +5770,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-8.70</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>196.6</t>
+          <t>192.9</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>212.75</t>
+          <t>211.28</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>214.42</t>
+          <t>214.03</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>213.34</t>
+          <t>212.96</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-130.49</t>
+          <t>-101.13</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-113.40</t>
+          <t>-117.94</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1330556225.941558</t>
+          <t>1329625337.950288</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>723074244.0</t>
+          <t>456346640.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>909915123.0</t>
+          <t>757230803.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>674907487.9</t>
+          <t>678685106.5</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>854335140.06</t>
+          <t>856936697.08</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>235007635</t>
+          <t>78545696</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-3788069.634011253</t>
+          <t>-2554573.646779964</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>30693406.89</v>
+        <v>4229654.28</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
@@ -6003,17 +6003,17 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>191.5</t>
+          <t>190.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4701.928</t>
+          <t>3839.598</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-14.45</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14.59</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,57 +6201,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>201.2</t>
+          <t>196.6</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>213.98</t>
+          <t>212.75</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>214.79</t>
+          <t>214.42</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>213.72</t>
+          <t>213.34</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-163.83</t>
+          <t>-130.49</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-109.03</t>
+          <t>-113.40</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1330556225.941558</t>
+          <t>1329625337.950288</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>918324556.0</t>
+          <t>723074244.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>878838587.8</t>
+          <t>909915123.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>691621829.4</t>
+          <t>674907487.9</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>845368183.24</t>
+          <t>854335140.06</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>187216758</t>
+          <t>235007635</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-10057429.00225778</t>
+          <t>-3788069.634011253</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>38824617.09</v>
+        <v>30693406.89</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-11.87</t>
+          <t>-14.84</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>191.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3457.008</t>
+          <t>4701.928</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-6.43</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>25.67</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-8.94</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10.72</t>
+          <t>14.59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6632,57 +6632,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>204.6</t>
+          <t>201.2</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>214.72</t>
+          <t>213.98</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>215.02</t>
+          <t>214.79</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>213.92</t>
+          <t>213.72</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-237.34</t>
+          <t>-163.83</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-105.33</t>
+          <t>-109.03</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1330556225.941558</t>
+          <t>1329625337.950288</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>685726947.0</t>
+          <t>918324556.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>817177497.0</t>
+          <t>878838587.8</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>650263422.9</t>
+          <t>691621829.4</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>838743112.42</t>
+          <t>845368183.24</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>166914074</t>
+          <t>187216758</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-18945073.74552811</t>
+          <t>-10057429.00225778</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>28134361.9</v>
+        <v>38824617.09</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-11.87</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>195.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5006.119</t>
+          <t>3457.008</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-7.24</t>
+          <t>-6.43</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>25.67</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-8.94</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>10.72</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7063,57 +7063,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>207.7</t>
+          <t>204.6</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>215.3</t>
+          <t>214.72</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>215.19</t>
+          <t>215.02</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>214.13</t>
+          <t>213.92</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-511.52</t>
+          <t>-237.34</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-102.17</t>
+          <t>-105.33</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1330556225.941558</t>
+          <t>1329625337.950288</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>1002681628.0</t>
+          <t>685726947.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>756541012.2</t>
+          <t>817177497.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>657490336.6</t>
+          <t>650263422.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>837159531.8</t>
+          <t>838743112.42</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>99050675</t>
+          <t>166914074</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-27504971.13491017</t>
+          <t>-18945073.74552811</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>36778942.52</v>
+        <v>28134361.9</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-8.68</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7231,17 +7231,17 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
+          <t>195.0</t>
+        </is>
+      </c>
+      <c r="CD16" t="inlineStr">
+        <is>
           <t>201.0</t>
         </is>
       </c>
-      <c r="CD16" t="inlineStr">
-        <is>
-          <t>205.0</t>
-        </is>
-      </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5932.964</t>
+          <t>5006.119</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-9.92</t>
+          <t>-7.24</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>15.06</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-5.96</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18.40</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7494,57 +7494,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>211.3</t>
+          <t>207.7</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>215.75</t>
+          <t>215.3</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>215.46</t>
+          <t>215.19</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>214.3</t>
+          <t>214.13</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-1398.14</t>
+          <t>-511.52</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-99.40</t>
+          <t>-102.17</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1330556225.941558</t>
+          <t>1329625337.950288</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>1219768240.0</t>
+          <t>1002681628.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>600139410.0</t>
+          <t>756541012.2</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>623193432.6</t>
+          <t>657490336.6</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>825475916.8</t>
+          <t>837159531.8</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-23054022</t>
+          <t>99050675</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-39192955.43611298</t>
+          <t>-27504971.13491017</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>13855379.65</v>
+        <v>36778942.52</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-8.68</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>196.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2678.776</t>
+          <t>5932.964</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-12.33</t>
+          <t>-9.92</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-18.01</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>-5.96</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>18.40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,12 +7905,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7925,57 +7925,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>213.8</t>
+          <t>211.3</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>215.92</t>
+          <t>215.75</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>215.67</t>
+          <t>215.46</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>214.41</t>
+          <t>214.3</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-230.30</t>
+          <t>-1398.14</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-97.28</t>
+          <t>-99.40</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1330556225.941558</t>
+          <t>1329625337.950288</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>567691568.0</t>
+          <t>1219768240.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>439899852.8</t>
+          <t>600139410.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>536558115.5</t>
+          <t>623193432.6</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>818287549.92</t>
+          <t>825475916.8</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-96658262</t>
+          <t>-23054022</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-48838107.26937589</t>
+          <t>-39192955.43611298</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-42646682.16</v>
+        <v>13855379.65</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -8133,7 +8133,7 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>209.5</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2889.254</t>
+          <t>2678.776</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>209.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-12.6</t>
+          <t>-12.33</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-18.01</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,12 +8336,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8351,62 +8351,62 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>215.3</t>
+          <t>213.8</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>216.22</t>
+          <t>215.92</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>215.78</t>
+          <t>215.67</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>214.37</t>
+          <t>214.41</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-110.18</t>
+          <t>-230.30</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-95.72</t>
+          <t>-97.28</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1330556225.941558</t>
+          <t>1329625337.950288</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>610019102.0</t>
+          <t>567691568.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>504405071.0</t>
+          <t>439899852.8</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>521300497.5</t>
+          <t>536558115.5</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>817903324.56</t>
+          <t>818287549.92</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-16895426</t>
+          <t>-96658262</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-49963820.92529882</t>
+          <t>-48838107.26937589</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-51975459.81</v>
+        <v>-42646682.16</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-4.11</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>217.0</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>209.0</t>
+          <t>209.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>209.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1787.511</t>
+          <t>2889.254</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-14.75</t>
+          <t>-12.6</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,12 +8767,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8782,62 +8782,62 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>218.3</t>
+          <t>215.3</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>216.95</t>
+          <t>216.22</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>215.86</t>
+          <t>215.78</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>214.34</t>
+          <t>214.37</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-40.27</t>
+          <t>-110.18</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-94.54</t>
+          <t>-95.72</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1330556225.941558</t>
+          <t>1329625337.950288</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>382544523.0</t>
+          <t>610019102.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>483349348.8</t>
+          <t>504405071.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>525432672.9</t>
+          <t>521300497.5</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>817817970.04</t>
+          <t>817903324.56</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-42083324</t>
+          <t>-16895426</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-49598068.40058749</t>
+          <t>-49963820.92529882</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-67981111.53</v>
+        <v>-51975459.81</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-4.11</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8955,17 +8955,17 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>216.5</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>216.5</t>
+          <t>217.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>212.5</t>
+          <t>209.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1014.871</t>
+          <t>1787.511</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,72 +9082,72 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>214.0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-14.75</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-4.46</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-8.01</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>220.0</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
           <t>218.0</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>-16.89</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>-5.26</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>220.0</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>218.0</t>
-        </is>
-      </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,17 +9198,17 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -9218,57 +9218,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>220.2</t>
+          <t>218.3</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>217.68</t>
+          <t>216.95</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>215.88</t>
+          <t>215.86</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>214.24</t>
+          <t>214.34</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-40.27</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-93.99</t>
+          <t>-94.54</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,45 +9288,45 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1330556225.941558</t>
+          <t>1329625337.950288</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>220673617.0</t>
+          <t>382544523.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>558439661.0</t>
+          <t>483349348.8</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>552641417.0</t>
+          <t>525432672.9</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>844929542.22</t>
+          <t>817817970.04</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>5798244</t>
+          <t>-42083324</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-46255696.92225825</t>
+          <t>-49598068.40058749</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-64046155.11</v>
+        <v>-67981111.53</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>219.5</t>
+          <t>216.5</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>216.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>216.0</t>
+          <t>212.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1945.088</t>
+          <t>1014.871</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>217.5</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-16.62</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9593,12 +9593,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
           <t>6.25</t>
         </is>
       </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>35.42</t>
-        </is>
-      </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>220.7</t>
+          <t>220.2</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>217.85</t>
+          <t>217.68</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>215.58</t>
+          <t>215.88</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>214.11</t>
+          <t>214.24</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-93.93</t>
+          <t>-93.99</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1330556225.941558</t>
+          <t>1329625337.950288</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>418570454.0</t>
+          <t>220673617.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>646247455.2</t>
+          <t>558439661.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>657338972.5</t>
+          <t>552641417.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>852341614.72</t>
+          <t>844929542.22</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-11091517</t>
+          <t>5798244</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-43021068.16036207</t>
+          <t>-46255696.92225825</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-38794114.76</v>
+        <v>-64046155.11</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
@@ -9857,7 +9857,7 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>219.5</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
+          <t>220.0</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
+        <is>
+          <t>216.0</t>
+        </is>
+      </c>
+      <c r="CF22" t="inlineStr">
+        <is>
           <t>218.0</t>
-        </is>
-      </c>
-      <c r="CE22" t="inlineStr">
-        <is>
-          <t>211.0</t>
-        </is>
-      </c>
-      <c r="CF22" t="inlineStr">
-        <is>
-          <t>217.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3999.43</t>
+          <t>1945.088</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>217.0</t>
+          <t>217.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-16.35</t>
+          <t>-16.62</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10024,12 +10024,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-5.76</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>35.42</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>221.1</t>
+          <t>220.7</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>217.82</t>
+          <t>217.85</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>215.35</t>
+          <t>215.58</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>213.92</t>
+          <t>214.11</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>36.34</t>
+          <t>10.29</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-94.08</t>
+          <t>-93.93</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1330556225.941558</t>
+          <t>1329625337.950288</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>890217659.0</t>
+          <t>418570454.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>633216378.2</t>
+          <t>646247455.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>690143066.0</t>
+          <t>657338972.5</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>855601077.24</t>
+          <t>852341614.72</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-56926687</t>
+          <t>-11091517</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-43789605.14215445</t>
+          <t>-43021068.16036207</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-22537499.84</v>
+        <v>-38794114.76</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>229.5</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>230.5</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>216.0</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>217.0</t>
+          <t>217.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/工業型機器人.xlsx
+++ b/Result/checksun_type/工業型機器人.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>371.0</t>
+          <t>377.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-23.31</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>377</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,57 +1029,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>671.6</t>
+          <t>657.8</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>725.65</t>
+          <t>718.95</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>773.56</t>
+          <t>774.36</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>675.4</t>
+          <t>677.44</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-53.49</t>
+          <t>-46.43</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-32.01</t>
+          <t>-34.54</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-20.85</t>
+          <t>-23.59</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-123.18</t>
+          <t>-126.22</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>411289.6525423729</t>
+          <t>411144.5422297298</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>241508.0</t>
+          <t>245558.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>292951.6</t>
+          <t>296429.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>382000.7</t>
+          <t>325427.2</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>675976.12</t>
+          <t>674644.66</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-89049</t>
+          <t>-28997</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-50191.19890369411</t>
+          <t>-49876.79689592369</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-46865.1</v>
+        <v>-48147.59</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,17 +1197,17 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>667.0</t>
+          <t>672.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>371.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-22.67</t>
+          <t>-23.31</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>377</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-6.42</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>686.2</t>
+          <t>671.6</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>733.3</t>
+          <t>725.65</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>772.84</t>
+          <t>773.56</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>675.4</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-57.81</t>
+          <t>-53.49</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-28.51</t>
+          <t>-32.01</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-18.06</t>
+          <t>-20.85</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-120.08</t>
+          <t>-123.18</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>411289.6525423729</t>
+          <t>411144.5422297298</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>377978.0</t>
+          <t>241508.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>309322.6</t>
+          <t>292951.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>400021.6</t>
+          <t>382000.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>677723.46</t>
+          <t>675976.12</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-90699</t>
+          <t>-89049</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-50795.94465057103</t>
+          <t>-50191.19890369411</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-42925.29</v>
+        <v>-46865.1</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>147.04</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,17 +1628,17 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>693.0</t>
+          <t>667.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>456.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-18.05</t>
+          <t>-22.67</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-21.06</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>377</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1891,57 +1891,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-6.42</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>702.8</t>
+          <t>686.2</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>740.6</t>
+          <t>733.3</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>771.72</t>
+          <t>772.84</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>670.89</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-56.83</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-24.23</t>
+          <t>-28.51</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-18.06</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-117.18</t>
+          <t>-120.08</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>411289.6525423729</t>
+          <t>411144.5422297298</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>310495.0</t>
+          <t>377978.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>321361.4</t>
+          <t>309322.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>392151.7</t>
+          <t>400021.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>673300.18</t>
+          <t>677723.46</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-70790</t>
+          <t>-90699</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-52226.97299810403</t>
+          <t>-50795.94465057103</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-50385.73</v>
+        <v>-42925.29</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>156.60</t>
+          <t>147.04</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>699.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>444.0</t>
+          <t>456.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-5.17</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-18.05</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-18.35</t>
+          <t>-21.06</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>377</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2322,57 +2322,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>15.03</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>711.8</t>
+          <t>702.8</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>747.5</t>
+          <t>740.6</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>770.14</t>
+          <t>771.72</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>668.28</t>
+          <t>670.89</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-58.22</t>
+          <t>-56.83</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-20.97</t>
+          <t>-24.23</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-15.45</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-114.74</t>
+          <t>-117.18</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>411289.6525423729</t>
+          <t>411144.5422297298</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>306608.0</t>
+          <t>310495.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>359349.6</t>
+          <t>321361.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>389319.8</t>
+          <t>392151.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>672018.02</t>
+          <t>673300.18</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-29970</t>
+          <t>-70790</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-52561.74436342486</t>
+          <t>-52226.97299810403</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-52013.69</v>
+        <v>-50385.73</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>165.39</t>
+          <t>156.60</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>18.28</t>
+          <t>17.68</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2560,17 +2560,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>679.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>444.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-10.47</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-16.82</t>
+          <t>-18.35</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>377</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,62 +2748,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>15.24</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>722.4</t>
+          <t>711.8</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>754.55</t>
+          <t>747.5</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>768.06</t>
+          <t>770.14</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>665.62</t>
+          <t>668.28</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-66.42</t>
+          <t>-58.22</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-18.85</t>
+          <t>-20.97</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-112.59</t>
+          <t>-114.74</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>411289.6525423729</t>
+          <t>411144.5422297298</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>228169.0</t>
+          <t>306608.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>354425.0</t>
+          <t>359349.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>390521.3</t>
+          <t>389319.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>675976.46</t>
+          <t>672018.02</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-36096</t>
+          <t>-29970</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-52661.39013608223</t>
+          <t>-52561.74436342486</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-52065.26</v>
+        <v>-52013.69</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>170.36</t>
+          <t>165.39</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>699.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>679.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>448.0</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-11.41</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-16.12</t>
+          <t>-16.82</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>377</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3184,57 +3184,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>722.4</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>760.7</t>
+          <t>754.55</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>766.1</t>
+          <t>768.06</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>662.74</t>
+          <t>665.62</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-81.98</t>
+          <t>-66.42</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-17.19</t>
+          <t>-18.85</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-110.50</t>
+          <t>-112.59</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>411289.6525423729</t>
+          <t>411144.5422297298</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>323363.0</t>
+          <t>228169.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>471049.8</t>
+          <t>354425.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>445989.1</t>
+          <t>390521.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>679269.88</t>
+          <t>675976.46</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>25060</t>
+          <t>-36096</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-52769.77804672284</t>
+          <t>-52661.39013608223</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-41875.27</v>
+        <v>-52065.26</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>172.66</t>
+          <t>170.36</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,17 +3352,17 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.62</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>710.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>606.0</t>
+          <t>448.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>713.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-13.91</t>
+          <t>-11.76</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-14.24</t>
+          <t>-16.12</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>377</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>15.60</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>737.8</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>765.9</t>
+          <t>760.7</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>763.84</t>
+          <t>766.1</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>659.24</t>
+          <t>662.74</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-105.47</t>
+          <t>-81.98</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-15.43</t>
+          <t>-17.19</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-7.51</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-108.35</t>
+          <t>-110.50</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>411289.6525423729</t>
+          <t>411144.5422297298</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>438172.0</t>
+          <t>323363.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>490720.6</t>
+          <t>471049.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>467960.7</t>
+          <t>445989.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>683118.66</t>
+          <t>679269.88</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>22759</t>
+          <t>25060</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-54750.59814941225</t>
+          <t>-52769.77804672284</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-36021.95</v>
+        <v>-41875.27</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>178.78</t>
+          <t>172.66</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,17 +3783,17 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.78</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>748.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>710.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>713.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>606.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-11.88</t>
+          <t>-14.26</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-14.24</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>18.93</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>377</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.07</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>52.47</t>
+          <t>27.16</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>735.2</t>
+          <t>737.8</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>771.95</t>
+          <t>765.9</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>761.14</t>
+          <t>763.84</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>655.4</t>
+          <t>659.24</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-163.86</t>
+          <t>-105.47</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-14.59</t>
+          <t>-15.43</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-7.51</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-106.15</t>
+          <t>-108.35</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>411289.6525423729</t>
+          <t>411144.5422297298</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>500436.0</t>
+          <t>438172.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>462942.0</t>
+          <t>490720.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>451797.8</t>
+          <t>467960.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>687666.36</t>
+          <t>683118.66</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>22759</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-58155.80653900002</t>
+          <t>-54750.59814941225</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-38674.54</v>
+        <v>-36021.95</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>173.80</t>
+          <t>178.78</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,17 +4214,17 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>751.0</t>
+          <t>748.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>376.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-16.72</t>
+          <t>-12.23</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-12.12</t>
+          <t>-15.76</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>377</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>57.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>59.26</t>
+          <t>52.47</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>16.13</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>740.6</t>
+          <t>735.2</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>780.25</t>
+          <t>771.95</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>759.12</t>
+          <t>761.14</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>651.25</t>
+          <t>655.4</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-267.06</t>
+          <t>-163.86</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-14.59</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-103.63</t>
+          <t>-106.15</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>411289.6525423729</t>
+          <t>411144.5422297298</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>281985.0</t>
+          <t>500436.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>419290.0</t>
+          <t>462942.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>432429.0</t>
+          <t>451797.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>696544.24</t>
+          <t>687666.36</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-13139</t>
+          <t>11144</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-61697.85522680334</t>
+          <t>-58155.80653900002</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-47753.86</v>
+        <v>-38674.54</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>185.66</t>
+          <t>173.80</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>756.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>761.0</t>
+          <t>751.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>742.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1050.0</t>
+          <t>376.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>747.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-20.31</t>
+          <t>-17.08</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-9.41</t>
+          <t>-12.12</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>32.80</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>377</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>57.41</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>59.26</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-5.67</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>744.8</t>
+          <t>740.6</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>789.55</t>
+          <t>780.25</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>756.36</t>
+          <t>759.12</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>646.51</t>
+          <t>651.25</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-972.48</t>
+          <t>-267.06</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-11.64</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-101.21</t>
+          <t>-103.63</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>411289.6525423729</t>
+          <t>411144.5422297298</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>811293.0</t>
+          <t>281985.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>426617.6</t>
+          <t>419290.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>444428.2</t>
+          <t>432429.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>709505.24</t>
+          <t>696544.24</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-17810</t>
+          <t>-13139</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-64233.12749927216</t>
+          <t>-61697.85522680334</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-35613.35</v>
+        <v>-47753.86</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>194.46</t>
+          <t>185.66</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>763.0</t>
+          <t>756.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>761.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>757.0</t>
+          <t>742.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>747.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>582.0</t>
+          <t>1050.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>727.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-13.59</t>
+          <t>-20.69</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-14.47</t>
+          <t>-9.41</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>32.80</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>377</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-5.67</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>16.99</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>742.2</t>
+          <t>744.8</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>800.05</t>
+          <t>789.55</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>752.5</t>
+          <t>756.36</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>641.89</t>
+          <t>646.51</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-960.76</t>
+          <t>-972.48</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-13.37</t>
+          <t>-11.64</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-98.27</t>
+          <t>-101.21</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>411289.6525423729</t>
+          <t>411144.5422297298</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>421717.0</t>
+          <t>811293.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>420928.4</t>
+          <t>426617.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>387118.0</t>
+          <t>444428.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>709717.56</t>
+          <t>709505.24</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>33810</t>
+          <t>-17810</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-69436.72264493338</t>
+          <t>-64233.12749927216</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-73709.44</v>
+        <v>-35613.35</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>178.01</t>
+          <t>194.46</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>20.28</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>763.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>744.0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>757.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>727.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2437.772</t>
+          <t>3128.645</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5770,57 +5770,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-8.70</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>192.9</t>
+          <t>190.2</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>211.28</t>
+          <t>209.58</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>214.03</t>
+          <t>213.6</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>212.96</t>
+          <t>212.58</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-101.13</t>
+          <t>-78.19</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-117.94</t>
+          <t>-122.29</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1329625337.950288</t>
+          <t>1328980452.88705</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>456346640.0</t>
+          <t>587620146.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>757230803.0</t>
+          <t>674218506.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>678685106.5</t>
+          <t>715379759.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>856936697.08</t>
+          <t>864477556.2</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>78545696</t>
+          <t>-41161252</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-2554573.646779964</t>
+          <t>-2862362.462649101</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>4229654.28</v>
+        <v>-4555200.95</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
@@ -6003,17 +6003,17 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
+          <t>189.5</t>
+        </is>
+      </c>
+      <c r="CD13" t="inlineStr">
+        <is>
+          <t>191.5</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
           <t>186.5</t>
-        </is>
-      </c>
-      <c r="CD13" t="inlineStr">
-        <is>
-          <t>190.0</t>
-        </is>
-      </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>185.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3839.598</t>
+          <t>2437.772</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6080,12 +6080,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,57 +6201,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-8.70</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>196.6</t>
+          <t>192.9</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>212.75</t>
+          <t>211.28</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>214.42</t>
+          <t>214.03</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>213.34</t>
+          <t>212.96</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-130.49</t>
+          <t>-101.13</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-113.40</t>
+          <t>-117.94</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1329625337.950288</t>
+          <t>1328980452.88705</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>723074244.0</t>
+          <t>456346640.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>909915123.0</t>
+          <t>757230803.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>674907487.9</t>
+          <t>678685106.5</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>854335140.06</t>
+          <t>856936697.08</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>235007635</t>
+          <t>78545696</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-3788069.634011253</t>
+          <t>-2554573.646779964</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>30693406.89</v>
+        <v>4229654.28</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
@@ -6434,17 +6434,17 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>191.5</t>
+          <t>190.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4701.928</t>
+          <t>3839.598</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-14.45</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14.59</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6632,57 +6632,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>201.2</t>
+          <t>196.6</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>213.98</t>
+          <t>212.75</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>214.79</t>
+          <t>214.42</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>213.72</t>
+          <t>213.34</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-163.83</t>
+          <t>-130.49</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-109.03</t>
+          <t>-113.40</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1329625337.950288</t>
+          <t>1328980452.88705</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>918324556.0</t>
+          <t>723074244.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>878838587.8</t>
+          <t>909915123.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>691621829.4</t>
+          <t>674907487.9</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>845368183.24</t>
+          <t>854335140.06</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>187216758</t>
+          <t>235007635</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-10057429.00225778</t>
+          <t>-3788069.634011253</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>38824617.09</v>
+        <v>30693406.89</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-11.87</t>
+          <t>-14.84</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>191.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3457.008</t>
+          <t>4701.928</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-6.43</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>25.67</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-8.94</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10.72</t>
+          <t>14.59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7063,57 +7063,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>204.6</t>
+          <t>201.2</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>214.72</t>
+          <t>213.98</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>215.02</t>
+          <t>214.79</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>213.92</t>
+          <t>213.72</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-237.34</t>
+          <t>-163.83</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-105.33</t>
+          <t>-109.03</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1329625337.950288</t>
+          <t>1328980452.88705</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>685726947.0</t>
+          <t>918324556.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>817177497.0</t>
+          <t>878838587.8</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>650263422.9</t>
+          <t>691621829.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>838743112.42</t>
+          <t>845368183.24</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>166914074</t>
+          <t>187216758</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-18945073.74552811</t>
+          <t>-10057429.00225778</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>28134361.9</v>
+        <v>38824617.09</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-11.87</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>195.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5006.119</t>
+          <t>3457.008</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-7.24</t>
+          <t>-6.43</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>25.67</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-8.94</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>10.72</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7494,57 +7494,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>207.7</t>
+          <t>204.6</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>215.3</t>
+          <t>214.72</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>215.19</t>
+          <t>215.02</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>214.13</t>
+          <t>213.92</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-511.52</t>
+          <t>-237.34</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-102.17</t>
+          <t>-105.33</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1329625337.950288</t>
+          <t>1328980452.88705</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>1002681628.0</t>
+          <t>685726947.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>756541012.2</t>
+          <t>817177497.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>657490336.6</t>
+          <t>650263422.9</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>837159531.8</t>
+          <t>838743112.42</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>99050675</t>
+          <t>166914074</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-27504971.13491017</t>
+          <t>-18945073.74552811</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>36778942.52</v>
+        <v>28134361.9</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-8.68</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,17 +7662,17 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
+          <t>195.0</t>
+        </is>
+      </c>
+      <c r="CD17" t="inlineStr">
+        <is>
           <t>201.0</t>
         </is>
       </c>
-      <c r="CD17" t="inlineStr">
-        <is>
-          <t>205.0</t>
-        </is>
-      </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5932.964</t>
+          <t>5006.119</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-9.92</t>
+          <t>-7.24</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>15.06</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-5.96</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18.40</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,12 +7905,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7925,57 +7925,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>211.3</t>
+          <t>207.7</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>215.75</t>
+          <t>215.3</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>215.46</t>
+          <t>215.19</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>214.3</t>
+          <t>214.13</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-1398.14</t>
+          <t>-511.52</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-99.40</t>
+          <t>-102.17</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1329625337.950288</t>
+          <t>1328980452.88705</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>1219768240.0</t>
+          <t>1002681628.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>600139410.0</t>
+          <t>756541012.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>623193432.6</t>
+          <t>657490336.6</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>825475916.8</t>
+          <t>837159531.8</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-23054022</t>
+          <t>99050675</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-39192955.43611298</t>
+          <t>-27504971.13491017</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>13855379.65</v>
+        <v>36778942.52</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-8.68</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -8133,7 +8133,7 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>196.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2678.776</t>
+          <t>5932.964</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-12.33</t>
+          <t>-9.92</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-18.01</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>-5.96</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>18.40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,12 +8336,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8356,57 +8356,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>213.8</t>
+          <t>211.3</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>215.92</t>
+          <t>215.75</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>215.67</t>
+          <t>215.46</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>214.41</t>
+          <t>214.3</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-230.30</t>
+          <t>-1398.14</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-97.28</t>
+          <t>-99.40</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1329625337.950288</t>
+          <t>1328980452.88705</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>567691568.0</t>
+          <t>1219768240.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>439899852.8</t>
+          <t>600139410.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>536558115.5</t>
+          <t>623193432.6</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>818287549.92</t>
+          <t>825475916.8</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-96658262</t>
+          <t>-23054022</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-48838107.26937589</t>
+          <t>-39192955.43611298</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-42646682.16</v>
+        <v>13855379.65</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>209.5</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2889.254</t>
+          <t>2678.776</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>209.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-12.6</t>
+          <t>-12.33</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-18.01</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,12 +8767,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8782,62 +8782,62 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>215.3</t>
+          <t>213.8</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>216.22</t>
+          <t>215.92</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>215.78</t>
+          <t>215.67</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>214.37</t>
+          <t>214.41</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-110.18</t>
+          <t>-230.30</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-95.72</t>
+          <t>-97.28</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1329625337.950288</t>
+          <t>1328980452.88705</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>610019102.0</t>
+          <t>567691568.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>504405071.0</t>
+          <t>439899852.8</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>521300497.5</t>
+          <t>536558115.5</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>817903324.56</t>
+          <t>818287549.92</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-16895426</t>
+          <t>-96658262</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-49963820.92529882</t>
+          <t>-48838107.26937589</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-51975459.81</v>
+        <v>-42646682.16</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-4.11</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>217.0</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>209.0</t>
+          <t>209.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>209.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1787.511</t>
+          <t>2889.254</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-14.75</t>
+          <t>-12.6</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,12 +9198,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9213,62 +9213,62 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>218.3</t>
+          <t>215.3</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>216.95</t>
+          <t>216.22</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>215.86</t>
+          <t>215.78</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>214.34</t>
+          <t>214.37</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-40.27</t>
+          <t>-110.18</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-94.54</t>
+          <t>-95.72</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1329625337.950288</t>
+          <t>1328980452.88705</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>382544523.0</t>
+          <t>610019102.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>483349348.8</t>
+          <t>504405071.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>525432672.9</t>
+          <t>521300497.5</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>817817970.04</t>
+          <t>817903324.56</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-42083324</t>
+          <t>-16895426</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-49598068.40058749</t>
+          <t>-49963820.92529882</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-67981111.53</v>
+        <v>-51975459.81</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-4.11</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>216.5</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>216.5</t>
+          <t>217.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>212.5</t>
+          <t>209.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1014.871</t>
+          <t>1787.511</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,72 +9513,72 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>214.0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-14.75</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-4.43</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-8.01</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>220.0</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
           <t>218.0</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>-16.89</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>-4.46</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>220.0</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>218.0</t>
-        </is>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -9593,12 +9593,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,17 +9629,17 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -9649,57 +9649,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>220.2</t>
+          <t>218.3</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>217.68</t>
+          <t>216.95</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>215.88</t>
+          <t>215.86</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>214.24</t>
+          <t>214.34</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-40.27</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-93.99</t>
+          <t>-94.54</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,45 +9719,45 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1329625337.950288</t>
+          <t>1328980452.88705</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>220673617.0</t>
+          <t>382544523.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>558439661.0</t>
+          <t>483349348.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>552641417.0</t>
+          <t>525432672.9</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>844929542.22</t>
+          <t>817817970.04</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>5798244</t>
+          <t>-42083324</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-46255696.92225825</t>
+          <t>-49598068.40058749</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-64046155.11</v>
+        <v>-67981111.53</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
@@ -9857,7 +9857,7 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>219.5</t>
+          <t>216.5</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>216.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>216.0</t>
+          <t>212.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9934,7 +9934,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1945.088</t>
+          <t>1014.871</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>217.5</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-16.62</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10024,12 +10024,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
           <t>6.25</t>
         </is>
       </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>35.42</t>
-        </is>
-      </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>220.7</t>
+          <t>220.2</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>217.85</t>
+          <t>217.68</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>215.58</t>
+          <t>215.88</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>214.11</t>
+          <t>214.24</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-93.93</t>
+          <t>-93.99</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1329625337.950288</t>
+          <t>1328980452.88705</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>418570454.0</t>
+          <t>220673617.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>646247455.2</t>
+          <t>558439661.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>657338972.5</t>
+          <t>552641417.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>852341614.72</t>
+          <t>844929542.22</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-11091517</t>
+          <t>5798244</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-43021068.16036207</t>
+          <t>-46255696.92225825</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-38794114.76</v>
+        <v>-64046155.11</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>219.5</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
+          <t>220.0</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
+          <t>216.0</t>
+        </is>
+      </c>
+      <c r="CF23" t="inlineStr">
+        <is>
           <t>218.0</t>
-        </is>
-      </c>
-      <c r="CE23" t="inlineStr">
-        <is>
-          <t>211.0</t>
-        </is>
-      </c>
-      <c r="CF23" t="inlineStr">
-        <is>
-          <t>217.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/工業型機器人.xlsx
+++ b/Result/checksun_type/工業型機器人.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI23"/>
+  <dimension ref="A1:CJ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,165 +701,170 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>Volume_Price_Change_sum</t>
+          <t>VPC_MACD</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>Volume_Price_Change</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -878,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>377.0</t>
+          <t>428.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-11.10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-28.24</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>428</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,57 +1034,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-10.02</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-7.9</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>657.8</t>
+          <t>641.0</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>718.95</t>
+          <t>712.35</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>774.36</t>
+          <t>773.42</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>677.44</t>
+          <t>679.24</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-46.43</t>
+          <t>-44.55</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-34.54</t>
+          <t>-38.37</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-23.59</t>
+          <t>-26.55</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-126.22</t>
+          <t>-129.51</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,198 +1104,203 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>411144.5422297298</t>
+          <t>411084.8333333334</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>245558.0</t>
+          <t>262274.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>296429.4</t>
+          <t>287562.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>325427.2</t>
+          <t>323456.1</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>674644.66</t>
+          <t>664782.5</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-28997</t>
+          <t>-35893</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-49876.79689592369</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-48147.59</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-49370.81863454734</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-46587.93819697743</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>262274</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>261.5</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>143.98</t>
-        </is>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
+          <t>133.27</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>102.0481335952849</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>95.34284575725091</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
           <t>9.59</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>53.98</t>
-        </is>
-      </c>
       <c r="BV2" t="inlineStr">
         <is>
+          <t>51.61</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
           <t>66.48%</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>53.80%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
+          <t>14189</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
           <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>竹陞科技-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>664.0</t>
-        </is>
-      </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>672.0</t>
+          <t>624.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>630.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>600.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
+          <t>610.0</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
           <t>37.96</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>** 自動化 - 自動化機台、控制器、工業型機器人、AGV及AMR** 其他 - 其他電子產品及電子服務產業** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備** 雲端運算 - 設備管理軟體、營運管理軟體、虛擬化軟體、系統整合、顧問諮詢、設備安裝服務、PaaS** 資通訊安全 - 安全營運與事件回應** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1309,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>371.0</t>
+          <t>377.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-23.31</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1450,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>428</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1460,57 +1470,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>671.6</t>
+          <t>657.8</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>725.65</t>
+          <t>718.95</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>773.56</t>
+          <t>774.36</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>675.4</t>
+          <t>677.44</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-53.49</t>
+          <t>-46.43</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-32.01</t>
+          <t>-34.54</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-20.85</t>
+          <t>-23.59</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-123.18</t>
+          <t>-126.22</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,198 +1540,203 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>411144.5422297298</t>
+          <t>411084.8333333334</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>241508.0</t>
+          <t>245558.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>292951.6</t>
+          <t>296429.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>382000.7</t>
+          <t>325427.2</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>675976.12</t>
+          <t>674644.66</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-89049</t>
+          <t>-28997</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-50191.19890369411</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>-46865.1</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-49876.79689592369</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-48147.58585318638</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>245558</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>261.5</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>144.74</t>
-        </is>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
+          <t>143.98</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>102.0481335952849</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>95.34284575725091</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
           <t>9.59</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>53.98</t>
-        </is>
-      </c>
       <c r="BV3" t="inlineStr">
         <is>
+          <t>51.61</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
           <t>66.48%</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>53.80%</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
+          <t>14189</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
           <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>竹陞科技-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>645.0</t>
-        </is>
-      </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>667.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>672.0</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>638.0</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>640.0</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
+          <t>638.0</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
           <t>37.96</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>** 自動化 - 自動化機台、控制器、工業型機器人、AGV及AMR** 其他 - 其他電子產品及電子服務產業** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備** 雲端運算 - 設備管理軟體、營運管理軟體、虛擬化軟體、系統整合、顧問諮詢、設備安裝服務、PaaS** 資通訊安全 - 安全營運與事件回應** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1740,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>371.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.92</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-22.67</t>
+          <t>-23.31</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1886,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>428</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1891,57 +1906,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-6.42</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>686.2</t>
+          <t>671.6</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>733.3</t>
+          <t>725.65</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>772.84</t>
+          <t>773.56</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>675.4</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-57.81</t>
+          <t>-53.49</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-28.51</t>
+          <t>-32.01</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-18.06</t>
+          <t>-20.85</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-120.08</t>
+          <t>-123.18</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,198 +1976,203 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>411144.5422297298</t>
+          <t>411084.8333333334</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>377978.0</t>
+          <t>241508.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>309322.6</t>
+          <t>292951.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>400021.6</t>
+          <t>382000.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>677723.46</t>
+          <t>675976.12</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-90699</t>
+          <t>-89049</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-50795.94465057103</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>-42925.29</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-50191.19890369411</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-46865.09729587106</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>241508</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
           <t>261.5</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>147.04</t>
-        </is>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
+          <t>144.74</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>102.0481335952849</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>95.34284575725091</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
           <t>9.59</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>53.98</t>
-        </is>
-      </c>
       <c r="BV4" t="inlineStr">
         <is>
+          <t>51.61</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
           <t>66.48%</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>53.80%</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
+          <t>14189</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
           <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>竹陞科技-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>671.0</t>
-        </is>
-      </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>693.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>667.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
+          <t>640.0</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
           <t>37.96</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>** 自動化 - 自動化機台、控制器、工業型機器人、AGV及AMR** 其他 - 其他電子產品及電子服務產業** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備** 雲端運算 - 設備管理軟體、營運管理軟體、虛擬化軟體、系統整合、顧問諮詢、設備安裝服務、PaaS** 資通訊安全 - 安全營運與事件回應** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2171,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>456.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>-5.9</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-18.05</t>
+          <t>-22.67</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-21.06</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>428</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2322,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-6.42</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>702.8</t>
+          <t>686.2</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>740.6</t>
+          <t>733.3</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>771.72</t>
+          <t>772.84</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>670.89</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-56.83</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-24.23</t>
+          <t>-28.51</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-18.06</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-117.18</t>
+          <t>-120.08</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,198 +2412,203 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>411144.5422297298</t>
+          <t>411084.8333333334</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>310495.0</t>
+          <t>377978.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>321361.4</t>
+          <t>309322.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>392151.7</t>
+          <t>400021.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>673300.18</t>
+          <t>677723.46</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-70790</t>
+          <t>-90699</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-52226.97299810403</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>-50385.73</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-50795.94465057103</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-42925.28873913951</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>377978</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>261.5</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>156.60</t>
-        </is>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
+          <t>147.04</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>102.0481335952849</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>95.34284575725091</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
           <t>9.59</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>53.98</t>
-        </is>
-      </c>
       <c r="BV5" t="inlineStr">
         <is>
+          <t>51.61</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
           <t>66.48%</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>53.80%</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
+          <t>14189</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
           <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>竹陞科技-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>699.0</t>
-        </is>
-      </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
+          <t>646.0</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
           <t>37.96</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>** 自動化 - 自動化機台、控制器、工業型機器人、AGV及AMR** 其他 - 其他電子產品及電子服務產業** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備** 雲端運算 - 設備管理軟體、營運管理軟體、虛擬化軟體、系統整合、顧問諮詢、設備安裝服務、PaaS** 資通訊安全 - 安全營運與事件回應** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2602,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>444.0</t>
+          <t>456.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-10.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-18.05</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-18.35</t>
+          <t>-21.06</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>428</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2753,57 +2778,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>15.03</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>711.8</t>
+          <t>702.8</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>747.5</t>
+          <t>740.6</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>770.14</t>
+          <t>771.72</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>668.28</t>
+          <t>670.89</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-58.22</t>
+          <t>-56.83</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-20.97</t>
+          <t>-24.23</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-15.45</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-114.74</t>
+          <t>-117.18</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,198 +2848,203 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>411144.5422297298</t>
+          <t>411084.8333333334</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>306608.0</t>
+          <t>310495.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>359349.6</t>
+          <t>321361.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>389319.8</t>
+          <t>392151.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>672018.02</t>
+          <t>673300.18</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-29970</t>
+          <t>-70790</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-52561.74436342486</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>-52013.69</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-52226.97299810403</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-50385.73048883944</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>310495</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
           <t>261.5</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>165.39</t>
-        </is>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
+          <t>156.60</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BJ6" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BL6" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>102.0481335952849</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>95.34284575725091</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ6" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>18.28</t>
-        </is>
-      </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>17.68</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
           <t>9.59</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>53.98</t>
-        </is>
-      </c>
       <c r="BV6" t="inlineStr">
         <is>
+          <t>51.61</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
           <t>66.48%</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>53.80%</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
+          <t>14189</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
           <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>竹陞科技-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>699.0</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>706.0</t>
-        </is>
-      </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>679.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
+          <t>671.0</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
           <t>37.96</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>** 自動化 - 自動化機台、控制器、工業型機器人、AGV及AMR** 其他 - 其他電子產品及電子服務產業** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備** 雲端運算 - 設備管理軟體、營運管理軟體、虛擬化軟體、系統整合、顧問諮詢、設備安裝服務、PaaS** 資通訊安全 - 安全營運與事件回應** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3033,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>444.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>-13.77</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-16.82</t>
+          <t>-18.35</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>428</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,62 +3209,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>15.24</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>722.4</t>
+          <t>711.8</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>754.55</t>
+          <t>747.5</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>768.06</t>
+          <t>770.14</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>665.62</t>
+          <t>668.28</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-66.42</t>
+          <t>-58.22</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-18.85</t>
+          <t>-20.97</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-112.59</t>
+          <t>-114.74</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,198 +3284,203 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>411144.5422297298</t>
+          <t>411084.8333333334</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>228169.0</t>
+          <t>306608.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>354425.0</t>
+          <t>359349.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>390521.3</t>
+          <t>389319.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>675976.46</t>
+          <t>672018.02</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-36096</t>
+          <t>-29970</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-52661.39013608223</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>-52065.26</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-52561.74436342486</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-52013.69261380937</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>306608</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
           <t>261.5</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>170.36</t>
-        </is>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
+          <t>165.39</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BL7" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>102.0481335952849</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>95.34284575725091</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
           <t>9.59</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>53.98</t>
-        </is>
-      </c>
       <c r="BV7" t="inlineStr">
         <is>
+          <t>51.61</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
           <t>66.48%</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>53.80%</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
+          <t>14189</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
           <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>竹陞科技-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>715.0</t>
-        </is>
-      </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>699.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>679.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
+          <t>694.0</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
           <t>37.96</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>** 自動化 - 自動化機台、控制器、工業型機器人、AGV及AMR** 其他 - 其他電子產品及電子服務產業** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備** 雲端運算 - 設備管理軟體、營運管理軟體、虛擬化軟體、系統整合、顧問諮詢、設備安裝服務、PaaS** 資通訊安全 - 安全營運與事件回應** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3464,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>448.0</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-11.76</t>
+          <t>-15.9</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-16.12</t>
+          <t>-16.82</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>428</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3615,57 +3650,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>722.4</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>760.7</t>
+          <t>754.55</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>766.1</t>
+          <t>768.06</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>662.74</t>
+          <t>665.62</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-81.98</t>
+          <t>-66.42</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-17.19</t>
+          <t>-18.85</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-110.50</t>
+          <t>-112.59</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,198 +3720,203 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>411144.5422297298</t>
+          <t>411084.8333333334</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>323363.0</t>
+          <t>228169.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>471049.8</t>
+          <t>354425.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>445989.1</t>
+          <t>390521.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>679269.88</t>
+          <t>675976.46</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>25060</t>
+          <t>-36096</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-52769.77804672284</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>-41875.27</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-52661.39013608223</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-52065.25662755885</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>228169</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
           <t>261.5</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>172.66</t>
-        </is>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
+          <t>170.36</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BL8" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>102.0481335952849</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>95.34284575725091</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>18.62</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
           <t>9.59</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>53.98</t>
-        </is>
-      </c>
       <c r="BV8" t="inlineStr">
         <is>
+          <t>51.61</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
           <t>66.48%</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>53.80%</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
+          <t>14189</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
           <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>竹陞科技-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>735.0</t>
-        </is>
-      </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>710.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
+          <t>707.0</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
           <t>37.96</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>** 自動化 - 自動化機台、控制器、工業型機器人、AGV及AMR** 其他 - 其他電子產品及電子服務產業** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備** 雲端運算 - 設備管理軟體、營運管理軟體、虛擬化軟體、系統整合、顧問諮詢、設備安裝服務、PaaS** 資通訊安全 - 安全營運與事件回應** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3895,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>606.0</t>
+          <t>448.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>713.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-14.26</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-14.24</t>
+          <t>-16.12</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>428</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>15.60</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>737.8</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>765.9</t>
+          <t>760.7</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>763.84</t>
+          <t>766.1</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>659.24</t>
+          <t>662.74</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-105.47</t>
+          <t>-81.98</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-15.43</t>
+          <t>-17.19</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-7.51</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-108.35</t>
+          <t>-110.50</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,198 +4156,203 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>411144.5422297298</t>
+          <t>411084.8333333334</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>438172.0</t>
+          <t>323363.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>490720.6</t>
+          <t>471049.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>467960.7</t>
+          <t>445989.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>683118.66</t>
+          <t>679269.88</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>22759</t>
+          <t>25060</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-54750.59814941225</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>-36021.95</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-52769.77804672284</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-41875.26748193102</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>323363</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
           <t>261.5</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>178.78</t>
-        </is>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
+          <t>172.66</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BJ9" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BL9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>102.0481335952849</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>95.34284575725091</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>18.78</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
           <t>9.59</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>53.98</t>
-        </is>
-      </c>
       <c r="BV9" t="inlineStr">
         <is>
+          <t>51.61</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
           <t>66.48%</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>53.80%</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
+          <t>14189</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
           <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>竹陞科技-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>739.0</t>
-        </is>
-      </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>748.0</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>710.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
+          <t>713.0</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
           <t>37.96</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>** 自動化 - 自動化機台、控制器、工業型機器人、AGV及AMR** 其他 - 其他電子產品及電子服務產業** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備** 雲端運算 - 設備管理軟體、營運管理軟體、虛擬化軟體、系統整合、顧問諮詢、設備安裝服務、PaaS** 資通訊安全 - 安全營運與事件回應** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4326,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>606.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-12.23</t>
+          <t>-19.51</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-14.24</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>18.93</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>428</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.07</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>52.47</t>
+          <t>27.16</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>735.2</t>
+          <t>737.8</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>771.95</t>
+          <t>765.9</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>761.14</t>
+          <t>763.84</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>655.4</t>
+          <t>659.24</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-163.86</t>
+          <t>-105.47</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-14.59</t>
+          <t>-15.43</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-7.51</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-106.15</t>
+          <t>-108.35</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,198 +4592,203 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>411144.5422297298</t>
+          <t>411084.8333333334</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>500436.0</t>
+          <t>438172.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>462942.0</t>
+          <t>490720.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>451797.8</t>
+          <t>467960.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>687666.36</t>
+          <t>683118.66</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>22759</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-58155.80653900002</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>-38674.54</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-54750.59814941225</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-36021.95200667955</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>438172</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
           <t>261.5</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>173.80</t>
-        </is>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
+          <t>178.78</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BJ10" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BL10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>102.0481335952849</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>95.34284575725091</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
           <t>9.59</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>53.98</t>
-        </is>
-      </c>
       <c r="BV10" t="inlineStr">
         <is>
+          <t>51.61</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
           <t>66.48%</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>53.80%</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
+          <t>14189</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
           <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>竹陞科技-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>750.0</t>
-        </is>
-      </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>751.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>748.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
+          <t>729.0</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
           <t>37.96</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>** 自動化 - 自動化機台、控制器、工業型機器人、AGV及AMR** 其他 - 其他電子產品及電子服務產業** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備** 雲端運算 - 設備管理軟體、營運管理軟體、虛擬化軟體、系統整合、顧問諮詢、設備安裝服務、PaaS** 資通訊安全 - 安全營運與事件回應** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4757,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>376.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-17.08</t>
+          <t>-17.38</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-12.12</t>
+          <t>-15.76</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>428</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>57.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>59.26</t>
+          <t>52.47</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>16.13</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>740.6</t>
+          <t>735.2</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>780.25</t>
+          <t>771.95</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>759.12</t>
+          <t>761.14</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>651.25</t>
+          <t>655.4</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-267.06</t>
+          <t>-163.86</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-14.59</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-103.63</t>
+          <t>-106.15</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,198 +5028,203 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>411144.5422297298</t>
+          <t>411084.8333333334</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>281985.0</t>
+          <t>500436.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>419290.0</t>
+          <t>462942.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>432429.0</t>
+          <t>451797.8</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>696544.24</t>
+          <t>687666.36</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-13139</t>
+          <t>11144</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-61697.85522680334</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-47753.86</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-58155.80653900002</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-38674.53875608178</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>500436</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
           <t>261.5</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>185.66</t>
-        </is>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
+          <t>173.80</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BL11" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>102.0481335952849</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>95.34284575725091</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BQ11" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
+      <c r="BR11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>19.68</t>
-        </is>
-      </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
           <t>9.59</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>53.98</t>
-        </is>
-      </c>
       <c r="BV11" t="inlineStr">
         <is>
+          <t>51.61</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
           <t>66.48%</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>53.80%</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
+          <t>14189</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
           <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>竹陞科技-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>756.0</t>
-        </is>
-      </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>761.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>742.0</t>
+          <t>751.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
+          <t>716.0</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
           <t>37.96</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>** 自動化 - 自動化機台、控制器、工業型機器人、AGV及AMR** 其他 - 其他電子產品及電子服務產業** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備** 雲端運算 - 設備管理軟體、營運管理軟體、虛擬化軟體、系統整合、顧問諮詢、設備安裝服務、PaaS** 資通訊安全 - 安全營運與事件回應** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5188,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1050.0</t>
+          <t>376.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>747.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-20.69</t>
+          <t>-22.46</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-9.41</t>
+          <t>-12.12</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>32.80</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>428</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>57.41</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>59.26</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.67</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>744.8</t>
+          <t>740.6</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>789.55</t>
+          <t>780.25</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>756.36</t>
+          <t>759.12</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>646.51</t>
+          <t>651.25</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-972.48</t>
+          <t>-267.06</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-11.64</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-101.21</t>
+          <t>-103.63</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,198 +5464,203 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>411144.5422297298</t>
+          <t>411084.8333333334</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>811293.0</t>
+          <t>281985.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>426617.6</t>
+          <t>419290.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>444428.2</t>
+          <t>432429.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>709505.24</t>
+          <t>696544.24</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-17810</t>
+          <t>-13139</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-64233.12749927216</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>-35613.35</v>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-61697.85522680334</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-47753.85772822483</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>281985</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
           <t>261.5</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/05/15</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>194.46</t>
-        </is>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
+          <t>185.66</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BJ12" t="inlineStr">
         <is>
           <t>竹陞科技</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BL12" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>5.417317991953463</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>102.0481335952849</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>95.34284575725091</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ12" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>20.28</t>
-        </is>
-      </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
           <t>9.59</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>53.98</t>
-        </is>
-      </c>
       <c r="BV12" t="inlineStr">
         <is>
+          <t>51.61</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
           <t>66.48%</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>53.80%</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
+          <t>14189</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
           <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>竹陞科技-其他電子業-上櫃</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>763.0</t>
-        </is>
-      </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>756.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>757.0</t>
+          <t>761.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>742.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
+          <t>747.0</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
           <t>37.96</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>** 自動化 - 自動化機台、控制器、工業型機器人、AGV及AMR** 其他 - 其他電子產品及電子服務產業** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備** 雲端運算 - 設備管理軟體、營運管理軟體、虛擬化軟體、系統整合、顧問諮詢、設備安裝服務、PaaS** 資通訊安全 - 安全營運與事件回應** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5619,42 +5679,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>-1.63</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2375.624</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>183.5</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>3128.645</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>186.5</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-13.38</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-14.45</t>
+          <t>-15.83</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>7.37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5810,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5770,57 +5830,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-9.85</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>190.2</t>
+          <t>187.2</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>209.58</t>
+          <t>207.65</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>213.6</t>
+          <t>213.15</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>212.58</t>
+          <t>212.2</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-78.19</t>
+          <t>-63.70</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-8.14</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-122.29</t>
+          <t>-126.52</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,198 +5900,203 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1328980452.88705</t>
+          <t>1328011393.327586</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>587620146.0</t>
+          <t>436343333.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>674218506.6</t>
+          <t>624341783.8</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>715379759.4</t>
+          <t>720759640.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>864477556.2</t>
+          <t>863704924.02</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-41161252</t>
+          <t>-96417856</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-2862362.462649101</t>
-        </is>
-      </c>
-      <c r="BC13" t="n">
-        <v>-4555200.95</v>
-      </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-5796842.170584051</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>-21936480.56422627</t>
+        </is>
+      </c>
+      <c r="BD13" t="n">
+        <v>436343333</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
           <t>219.0</t>
         </is>
       </c>
-      <c r="BF13" t="inlineStr">
+      <c r="BG13" t="inlineStr">
         <is>
           <t>2025/09/18</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>-14.84</t>
-        </is>
-      </c>
       <c r="BH13" t="inlineStr">
         <is>
+          <t>-16.21</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
           <t>上銀</t>
         </is>
       </c>
-      <c r="BI13" t="inlineStr">
+      <c r="BJ13" t="inlineStr">
         <is>
           <t>上銀</t>
         </is>
       </c>
-      <c r="BJ13" t="inlineStr">
+      <c r="BK13" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK13" t="inlineStr">
+      <c r="BL13" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL13" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
       <c r="BM13" t="inlineStr">
         <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
           <t>0.5246961718756727</t>
         </is>
       </c>
-      <c r="BN13" t="inlineStr">
+      <c r="BO13" t="inlineStr">
         <is>
           <t>-3.316042339543704</t>
         </is>
       </c>
-      <c r="BO13" t="inlineStr">
+      <c r="BP13" t="inlineStr">
         <is>
           <t>-1.626286550608443</t>
         </is>
       </c>
-      <c r="BP13" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="BU13" t="inlineStr">
+        <is>
           <t>16.95</t>
         </is>
       </c>
-      <c r="BU13" t="inlineStr">
-        <is>
-          <t>47.34</t>
-        </is>
-      </c>
       <c r="BV13" t="inlineStr">
         <is>
+          <t>46.57</t>
+        </is>
+      </c>
+      <c r="BW13" t="inlineStr">
+        <is>
           <t>28.60%</t>
         </is>
       </c>
-      <c r="BW13" t="inlineStr">
+      <c r="BX13" t="inlineStr">
         <is>
           <t>6.85%</t>
         </is>
       </c>
-      <c r="BX13" t="inlineStr">
-        <is>
-          <t>40.81</t>
-        </is>
-      </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>65982</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
+          <t>64921</t>
+        </is>
+      </c>
+      <c r="CA13" t="inlineStr">
+        <is>
           <t>線性滑軌64.00%、滾珠螺桿20.00%、其他9.00%、機器人7.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA13" t="inlineStr">
+      <c r="CB13" t="inlineStr">
         <is>
           <t>上銀-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB13" t="inlineStr">
+      <c r="CC13" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="CC13" t="inlineStr">
-        <is>
-          <t>189.5</t>
-        </is>
-      </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>191.5</t>
+          <t>184.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>186.5</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>186.5</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
+          <t>183.5</t>
+        </is>
+      </c>
+      <c r="CH13" t="inlineStr">
+        <is>
           <t>104.05</t>
         </is>
       </c>
-      <c r="CH13" t="inlineStr">
+      <c r="CI13" t="inlineStr">
         <is>
           <t>** 電機機械 - 傳動元件** 自動化 - 工業型機器人</t>
         </is>
       </c>
-      <c r="CI13" t="inlineStr">
+      <c r="CJ13" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -6055,7 +6120,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2437.772</t>
+          <t>3128.645</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6075,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6160,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6246,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,57 +6266,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-8.70</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>192.9</t>
+          <t>190.2</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>211.28</t>
+          <t>209.58</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>214.03</t>
+          <t>213.6</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>212.96</t>
+          <t>212.58</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-101.13</t>
+          <t>-78.19</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-117.94</t>
+          <t>-122.29</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,198 +6336,203 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1328980452.88705</t>
+          <t>1328011393.327586</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>456346640.0</t>
+          <t>587620146.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>757230803.0</t>
+          <t>674218506.6</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>678685106.5</t>
+          <t>715379759.4</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>856936697.08</t>
+          <t>864477556.2</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>78545696</t>
+          <t>-41161252</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-2554573.646779964</t>
-        </is>
-      </c>
-      <c r="BC14" t="n">
-        <v>4229654.28</v>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-2862362.462649101</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>-4555200.949929357</t>
+        </is>
+      </c>
+      <c r="BD14" t="n">
+        <v>587620146</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
           <t>219.0</t>
         </is>
       </c>
-      <c r="BF14" t="inlineStr">
+      <c r="BG14" t="inlineStr">
         <is>
           <t>2025/09/18</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr">
+      <c r="BH14" t="inlineStr">
         <is>
           <t>-14.84</t>
         </is>
       </c>
-      <c r="BH14" t="inlineStr">
+      <c r="BI14" t="inlineStr">
         <is>
           <t>上銀</t>
         </is>
       </c>
-      <c r="BI14" t="inlineStr">
+      <c r="BJ14" t="inlineStr">
         <is>
           <t>上銀</t>
         </is>
       </c>
-      <c r="BJ14" t="inlineStr">
+      <c r="BK14" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK14" t="inlineStr">
+      <c r="BL14" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL14" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
       <c r="BM14" t="inlineStr">
         <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
           <t>0.5246961718756727</t>
         </is>
       </c>
-      <c r="BN14" t="inlineStr">
+      <c r="BO14" t="inlineStr">
         <is>
           <t>-3.316042339543704</t>
         </is>
       </c>
-      <c r="BO14" t="inlineStr">
+      <c r="BP14" t="inlineStr">
         <is>
           <t>-1.626286550608443</t>
         </is>
       </c>
-      <c r="BP14" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
           <t>1.79</t>
         </is>
       </c>
-      <c r="BS14" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
       <c r="BT14" t="inlineStr">
         <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="BU14" t="inlineStr">
+        <is>
           <t>16.95</t>
         </is>
       </c>
-      <c r="BU14" t="inlineStr">
-        <is>
-          <t>47.34</t>
-        </is>
-      </c>
       <c r="BV14" t="inlineStr">
         <is>
+          <t>46.57</t>
+        </is>
+      </c>
+      <c r="BW14" t="inlineStr">
+        <is>
           <t>28.60%</t>
         </is>
       </c>
-      <c r="BW14" t="inlineStr">
+      <c r="BX14" t="inlineStr">
         <is>
           <t>6.85%</t>
         </is>
       </c>
-      <c r="BX14" t="inlineStr">
-        <is>
-          <t>40.81</t>
-        </is>
-      </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>65982</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
+          <t>64921</t>
+        </is>
+      </c>
+      <c r="CA14" t="inlineStr">
+        <is>
           <t>線性滑軌64.00%、滾珠螺桿20.00%、其他9.00%、機器人7.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA14" t="inlineStr">
+      <c r="CB14" t="inlineStr">
         <is>
           <t>上銀-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB14" t="inlineStr">
+      <c r="CC14" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="CC14" t="inlineStr">
+      <c r="CD14" t="inlineStr">
+        <is>
+          <t>189.5</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>191.5</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
         <is>
           <t>186.5</t>
         </is>
       </c>
-      <c r="CD14" t="inlineStr">
-        <is>
-          <t>190.0</t>
-        </is>
-      </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>185.0</t>
-        </is>
-      </c>
-      <c r="CF14" t="inlineStr">
+      <c r="CG14" t="inlineStr">
         <is>
           <t>186.5</t>
         </is>
       </c>
-      <c r="CG14" t="inlineStr">
+      <c r="CH14" t="inlineStr">
         <is>
           <t>104.05</t>
         </is>
       </c>
-      <c r="CH14" t="inlineStr">
+      <c r="CI14" t="inlineStr">
         <is>
           <t>** 電機機械 - 傳動元件** 自動化 - 工業型機器人</t>
         </is>
       </c>
-      <c r="CI14" t="inlineStr">
+      <c r="CJ14" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -6481,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3839.598</t>
+          <t>2437.772</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6506,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6591,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6682,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6632,57 +6702,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-8.70</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>196.6</t>
+          <t>192.9</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>212.75</t>
+          <t>211.28</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>214.42</t>
+          <t>214.03</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>213.34</t>
+          <t>212.96</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-130.49</t>
+          <t>-101.13</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-113.40</t>
+          <t>-117.94</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,198 +6772,203 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1328980452.88705</t>
+          <t>1328011393.327586</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>723074244.0</t>
+          <t>456346640.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>909915123.0</t>
+          <t>757230803.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>674907487.9</t>
+          <t>678685106.5</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>854335140.06</t>
+          <t>856936697.08</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>235007635</t>
+          <t>78545696</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-3788069.634011253</t>
-        </is>
-      </c>
-      <c r="BC15" t="n">
-        <v>30693406.89</v>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-2554573.646779964</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>4229654.282992125</t>
+        </is>
+      </c>
+      <c r="BD15" t="n">
+        <v>456346640</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
           <t>219.0</t>
         </is>
       </c>
-      <c r="BF15" t="inlineStr">
+      <c r="BG15" t="inlineStr">
         <is>
           <t>2025/09/18</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr">
+      <c r="BH15" t="inlineStr">
         <is>
           <t>-14.84</t>
         </is>
       </c>
-      <c r="BH15" t="inlineStr">
+      <c r="BI15" t="inlineStr">
         <is>
           <t>上銀</t>
         </is>
       </c>
-      <c r="BI15" t="inlineStr">
+      <c r="BJ15" t="inlineStr">
         <is>
           <t>上銀</t>
         </is>
       </c>
-      <c r="BJ15" t="inlineStr">
+      <c r="BK15" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK15" t="inlineStr">
+      <c r="BL15" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL15" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
       <c r="BM15" t="inlineStr">
         <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
           <t>0.5246961718756727</t>
         </is>
       </c>
-      <c r="BN15" t="inlineStr">
+      <c r="BO15" t="inlineStr">
         <is>
           <t>-3.316042339543704</t>
         </is>
       </c>
-      <c r="BO15" t="inlineStr">
+      <c r="BP15" t="inlineStr">
         <is>
           <t>-1.626286550608443</t>
         </is>
       </c>
-      <c r="BP15" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ15" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR15" t="inlineStr">
+      <c r="BS15" t="inlineStr">
         <is>
           <t>1.79</t>
         </is>
       </c>
-      <c r="BS15" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
       <c r="BT15" t="inlineStr">
         <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="BU15" t="inlineStr">
+        <is>
           <t>16.95</t>
         </is>
       </c>
-      <c r="BU15" t="inlineStr">
-        <is>
-          <t>47.34</t>
-        </is>
-      </c>
       <c r="BV15" t="inlineStr">
         <is>
+          <t>46.57</t>
+        </is>
+      </c>
+      <c r="BW15" t="inlineStr">
+        <is>
           <t>28.60%</t>
         </is>
       </c>
-      <c r="BW15" t="inlineStr">
+      <c r="BX15" t="inlineStr">
         <is>
           <t>6.85%</t>
         </is>
       </c>
-      <c r="BX15" t="inlineStr">
-        <is>
-          <t>40.81</t>
-        </is>
-      </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>65982</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
+          <t>64921</t>
+        </is>
+      </c>
+      <c r="CA15" t="inlineStr">
+        <is>
           <t>線性滑軌64.00%、滾珠螺桿20.00%、其他9.00%、機器人7.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA15" t="inlineStr">
+      <c r="CB15" t="inlineStr">
         <is>
           <t>上銀-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB15" t="inlineStr">
+      <c r="CC15" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="CC15" t="inlineStr">
-        <is>
-          <t>191.0</t>
-        </is>
-      </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>191.5</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>190.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
+          <t>185.0</t>
+        </is>
+      </c>
+      <c r="CG15" t="inlineStr">
+        <is>
           <t>186.5</t>
         </is>
       </c>
-      <c r="CG15" t="inlineStr">
+      <c r="CH15" t="inlineStr">
         <is>
           <t>104.05</t>
         </is>
       </c>
-      <c r="CH15" t="inlineStr">
+      <c r="CI15" t="inlineStr">
         <is>
           <t>** 電機機械 - 傳動元件** 自動化 - 工業型機器人</t>
         </is>
       </c>
-      <c r="CI15" t="inlineStr">
+      <c r="CJ15" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -6912,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4701.928</t>
+          <t>3839.598</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-14.45</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14.59</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7118,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7063,57 +7138,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>201.2</t>
+          <t>196.6</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>213.98</t>
+          <t>212.75</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>214.79</t>
+          <t>214.42</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>213.72</t>
+          <t>213.34</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-163.83</t>
+          <t>-130.49</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-109.03</t>
+          <t>-113.40</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,198 +7208,203 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1328980452.88705</t>
+          <t>1328011393.327586</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>918324556.0</t>
+          <t>723074244.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>878838587.8</t>
+          <t>909915123.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>691621829.4</t>
+          <t>674907487.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>845368183.24</t>
+          <t>854335140.06</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>187216758</t>
+          <t>235007635</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-10057429.00225778</t>
-        </is>
-      </c>
-      <c r="BC16" t="n">
-        <v>38824617.09</v>
-      </c>
-      <c r="BD16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-3788069.634011253</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>30693406.89134467</t>
+        </is>
+      </c>
+      <c r="BD16" t="n">
+        <v>723074244</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
           <t>219.0</t>
         </is>
       </c>
-      <c r="BF16" t="inlineStr">
+      <c r="BG16" t="inlineStr">
         <is>
           <t>2025/09/18</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>-11.87</t>
-        </is>
-      </c>
       <c r="BH16" t="inlineStr">
         <is>
+          <t>-14.84</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
           <t>上銀</t>
         </is>
       </c>
-      <c r="BI16" t="inlineStr">
+      <c r="BJ16" t="inlineStr">
         <is>
           <t>上銀</t>
         </is>
       </c>
-      <c r="BJ16" t="inlineStr">
+      <c r="BK16" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK16" t="inlineStr">
+      <c r="BL16" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL16" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
       <c r="BM16" t="inlineStr">
         <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
           <t>0.5246961718756727</t>
         </is>
       </c>
-      <c r="BN16" t="inlineStr">
+      <c r="BO16" t="inlineStr">
         <is>
           <t>-3.316042339543704</t>
         </is>
       </c>
-      <c r="BO16" t="inlineStr">
+      <c r="BP16" t="inlineStr">
         <is>
           <t>-1.626286550608443</t>
         </is>
       </c>
-      <c r="BP16" t="inlineStr">
+      <c r="BQ16" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BQ16" t="inlineStr">
+      <c r="BR16" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR16" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="BU16" t="inlineStr">
+        <is>
           <t>16.95</t>
         </is>
       </c>
-      <c r="BU16" t="inlineStr">
-        <is>
-          <t>47.34</t>
-        </is>
-      </c>
       <c r="BV16" t="inlineStr">
         <is>
+          <t>46.57</t>
+        </is>
+      </c>
+      <c r="BW16" t="inlineStr">
+        <is>
           <t>28.60%</t>
         </is>
       </c>
-      <c r="BW16" t="inlineStr">
+      <c r="BX16" t="inlineStr">
         <is>
           <t>6.85%</t>
         </is>
       </c>
-      <c r="BX16" t="inlineStr">
-        <is>
-          <t>40.81</t>
-        </is>
-      </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>65982</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
+          <t>64921</t>
+        </is>
+      </c>
+      <c r="CA16" t="inlineStr">
+        <is>
           <t>線性滑軌64.00%、滾珠螺桿20.00%、其他9.00%、機器人7.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA16" t="inlineStr">
+      <c r="CB16" t="inlineStr">
         <is>
           <t>上銀-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB16" t="inlineStr">
+      <c r="CC16" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="CC16" t="inlineStr">
-        <is>
-          <t>200.0</t>
-        </is>
-      </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>191.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
+          <t>186.5</t>
+        </is>
+      </c>
+      <c r="CH16" t="inlineStr">
+        <is>
           <t>104.05</t>
         </is>
       </c>
-      <c r="CH16" t="inlineStr">
+      <c r="CI16" t="inlineStr">
         <is>
           <t>** 電機機械 - 傳動元件** 自動化 - 工業型機器人</t>
         </is>
       </c>
-      <c r="CI16" t="inlineStr">
+      <c r="CJ16" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -7343,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3457.008</t>
+          <t>4701.928</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-6.43</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>25.67</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-8.94</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10.72</t>
+          <t>14.59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7554,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7494,57 +7574,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>204.6</t>
+          <t>201.2</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>214.72</t>
+          <t>213.98</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>215.02</t>
+          <t>214.79</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>213.92</t>
+          <t>213.72</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-237.34</t>
+          <t>-163.83</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-105.33</t>
+          <t>-109.03</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,198 +7644,203 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1328980452.88705</t>
+          <t>1328011393.327586</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>685726947.0</t>
+          <t>918324556.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>817177497.0</t>
+          <t>878838587.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>650263422.9</t>
+          <t>691621829.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>838743112.42</t>
+          <t>845368183.24</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>166914074</t>
+          <t>187216758</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-18945073.74552811</t>
-        </is>
-      </c>
-      <c r="BC17" t="n">
-        <v>28134361.9</v>
-      </c>
-      <c r="BD17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-10057429.00225778</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>38824617.085729</t>
+        </is>
+      </c>
+      <c r="BD17" t="n">
+        <v>918324556</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
           <t>219.0</t>
         </is>
       </c>
-      <c r="BF17" t="inlineStr">
+      <c r="BG17" t="inlineStr">
         <is>
           <t>2025/09/18</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>-9.36</t>
-        </is>
-      </c>
       <c r="BH17" t="inlineStr">
         <is>
+          <t>-11.87</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
           <t>上銀</t>
         </is>
       </c>
-      <c r="BI17" t="inlineStr">
+      <c r="BJ17" t="inlineStr">
         <is>
           <t>上銀</t>
         </is>
       </c>
-      <c r="BJ17" t="inlineStr">
+      <c r="BK17" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK17" t="inlineStr">
+      <c r="BL17" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL17" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
       <c r="BM17" t="inlineStr">
         <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BN17" t="inlineStr">
+        <is>
           <t>0.5246961718756727</t>
         </is>
       </c>
-      <c r="BN17" t="inlineStr">
+      <c r="BO17" t="inlineStr">
         <is>
           <t>-3.316042339543704</t>
         </is>
       </c>
-      <c r="BO17" t="inlineStr">
+      <c r="BP17" t="inlineStr">
         <is>
           <t>-1.626286550608443</t>
         </is>
       </c>
-      <c r="BP17" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ17" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR17" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="BU17" t="inlineStr">
+        <is>
           <t>16.95</t>
         </is>
       </c>
-      <c r="BU17" t="inlineStr">
-        <is>
-          <t>47.34</t>
-        </is>
-      </c>
       <c r="BV17" t="inlineStr">
         <is>
+          <t>46.57</t>
+        </is>
+      </c>
+      <c r="BW17" t="inlineStr">
+        <is>
           <t>28.60%</t>
         </is>
       </c>
-      <c r="BW17" t="inlineStr">
+      <c r="BX17" t="inlineStr">
         <is>
           <t>6.85%</t>
         </is>
       </c>
-      <c r="BX17" t="inlineStr">
-        <is>
-          <t>40.81</t>
-        </is>
-      </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>65982</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
+          <t>64921</t>
+        </is>
+      </c>
+      <c r="CA17" t="inlineStr">
+        <is>
           <t>線性滑軌64.00%、滾珠螺桿20.00%、其他9.00%、機器人7.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA17" t="inlineStr">
+      <c r="CB17" t="inlineStr">
         <is>
           <t>上銀-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB17" t="inlineStr">
+      <c r="CC17" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="CC17" t="inlineStr">
-        <is>
-          <t>195.0</t>
-        </is>
-      </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
+          <t>193.0</t>
+        </is>
+      </c>
+      <c r="CH17" t="inlineStr">
+        <is>
           <t>104.05</t>
         </is>
       </c>
-      <c r="CH17" t="inlineStr">
+      <c r="CI17" t="inlineStr">
         <is>
           <t>** 電機機械 - 傳動元件** 自動化 - 工業型機器人</t>
         </is>
       </c>
-      <c r="CI17" t="inlineStr">
+      <c r="CJ17" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -7774,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5006.119</t>
+          <t>3457.008</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-7.24</t>
+          <t>-8.17</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>25.67</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-8.94</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>10.72</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7925,57 +8010,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>207.7</t>
+          <t>204.6</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>215.3</t>
+          <t>214.72</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>215.19</t>
+          <t>215.02</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>214.13</t>
+          <t>213.92</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-511.52</t>
+          <t>-237.34</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-102.17</t>
+          <t>-105.33</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,198 +8080,203 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1328980452.88705</t>
+          <t>1328011393.327586</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>1002681628.0</t>
+          <t>685726947.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>756541012.2</t>
+          <t>817177497.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>657490336.6</t>
+          <t>650263422.9</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>837159531.8</t>
+          <t>838743112.42</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>99050675</t>
+          <t>166914074</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-27504971.13491017</t>
-        </is>
-      </c>
-      <c r="BC18" t="n">
-        <v>36778942.52</v>
-      </c>
-      <c r="BD18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-18945073.74552811</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>28134361.89607322</t>
+        </is>
+      </c>
+      <c r="BD18" t="n">
+        <v>685726947</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
           <t>219.0</t>
         </is>
       </c>
-      <c r="BF18" t="inlineStr">
+      <c r="BG18" t="inlineStr">
         <is>
           <t>2025/09/18</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr">
-        <is>
-          <t>-8.68</t>
-        </is>
-      </c>
       <c r="BH18" t="inlineStr">
         <is>
+          <t>-9.36</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
           <t>上銀</t>
         </is>
       </c>
-      <c r="BI18" t="inlineStr">
+      <c r="BJ18" t="inlineStr">
         <is>
           <t>上銀</t>
         </is>
       </c>
-      <c r="BJ18" t="inlineStr">
+      <c r="BK18" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK18" t="inlineStr">
+      <c r="BL18" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL18" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
       <c r="BM18" t="inlineStr">
         <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BN18" t="inlineStr">
+        <is>
           <t>0.5246961718756727</t>
         </is>
       </c>
-      <c r="BN18" t="inlineStr">
+      <c r="BO18" t="inlineStr">
         <is>
           <t>-3.316042339543704</t>
         </is>
       </c>
-      <c r="BO18" t="inlineStr">
+      <c r="BP18" t="inlineStr">
         <is>
           <t>-1.626286550608443</t>
         </is>
       </c>
-      <c r="BP18" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="BU18" t="inlineStr">
+        <is>
           <t>16.95</t>
         </is>
       </c>
-      <c r="BU18" t="inlineStr">
-        <is>
-          <t>47.34</t>
-        </is>
-      </c>
       <c r="BV18" t="inlineStr">
         <is>
+          <t>46.57</t>
+        </is>
+      </c>
+      <c r="BW18" t="inlineStr">
+        <is>
           <t>28.60%</t>
         </is>
       </c>
-      <c r="BW18" t="inlineStr">
+      <c r="BX18" t="inlineStr">
         <is>
           <t>6.85%</t>
         </is>
       </c>
-      <c r="BX18" t="inlineStr">
-        <is>
-          <t>40.81</t>
-        </is>
-      </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>65982</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
+          <t>64921</t>
+        </is>
+      </c>
+      <c r="CA18" t="inlineStr">
+        <is>
           <t>線性滑軌64.00%、滾珠螺桿20.00%、其他9.00%、機器人7.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA18" t="inlineStr">
+      <c r="CB18" t="inlineStr">
         <is>
           <t>上銀-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB18" t="inlineStr">
+      <c r="CC18" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="CC18" t="inlineStr">
+      <c r="CD18" t="inlineStr">
+        <is>
+          <t>195.0</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
         <is>
           <t>201.0</t>
         </is>
       </c>
-      <c r="CD18" t="inlineStr">
-        <is>
-          <t>205.0</t>
-        </is>
-      </c>
-      <c r="CE18" t="inlineStr">
-        <is>
-          <t>196.5</t>
-        </is>
-      </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
+          <t>198.5</t>
+        </is>
+      </c>
+      <c r="CH18" t="inlineStr">
+        <is>
           <t>104.05</t>
         </is>
       </c>
-      <c r="CH18" t="inlineStr">
+      <c r="CI18" t="inlineStr">
         <is>
           <t>** 電機機械 - 傳動元件** 自動化 - 工業型機器人</t>
         </is>
       </c>
-      <c r="CI18" t="inlineStr">
+      <c r="CJ18" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -8205,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5932.964</t>
+          <t>5006.119</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-9.92</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>15.06</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-5.96</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18.40</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8356,57 +8446,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>211.3</t>
+          <t>207.7</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>215.75</t>
+          <t>215.3</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>215.46</t>
+          <t>215.19</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>214.3</t>
+          <t>214.13</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-1398.14</t>
+          <t>-511.52</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-99.40</t>
+          <t>-102.17</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,198 +8516,203 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1328980452.88705</t>
+          <t>1328011393.327586</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>1219768240.0</t>
+          <t>1002681628.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>600139410.0</t>
+          <t>756541012.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>623193432.6</t>
+          <t>657490336.6</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>825475916.8</t>
+          <t>837159531.8</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-23054022</t>
+          <t>99050675</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-39192955.43611298</t>
-        </is>
-      </c>
-      <c r="BC19" t="n">
-        <v>13855379.65</v>
-      </c>
-      <c r="BD19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-27504971.13491017</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>36778942.52170527</t>
+        </is>
+      </c>
+      <c r="BD19" t="n">
+        <v>1002681628</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
           <t>219.0</t>
         </is>
       </c>
-      <c r="BF19" t="inlineStr">
+      <c r="BG19" t="inlineStr">
         <is>
           <t>2025/09/18</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr">
-        <is>
-          <t>-6.39</t>
-        </is>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
+          <t>-8.68</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
           <t>上銀</t>
         </is>
       </c>
-      <c r="BI19" t="inlineStr">
+      <c r="BJ19" t="inlineStr">
         <is>
           <t>上銀</t>
         </is>
       </c>
-      <c r="BJ19" t="inlineStr">
+      <c r="BK19" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK19" t="inlineStr">
+      <c r="BL19" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL19" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
       <c r="BM19" t="inlineStr">
         <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr">
+        <is>
           <t>0.5246961718756727</t>
         </is>
       </c>
-      <c r="BN19" t="inlineStr">
+      <c r="BO19" t="inlineStr">
         <is>
           <t>-3.316042339543704</t>
         </is>
       </c>
-      <c r="BO19" t="inlineStr">
+      <c r="BP19" t="inlineStr">
         <is>
           <t>-1.626286550608443</t>
         </is>
       </c>
-      <c r="BP19" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ19" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BR19" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="BU19" t="inlineStr">
+        <is>
           <t>16.95</t>
         </is>
       </c>
-      <c r="BU19" t="inlineStr">
-        <is>
-          <t>47.34</t>
-        </is>
-      </c>
       <c r="BV19" t="inlineStr">
         <is>
+          <t>46.57</t>
+        </is>
+      </c>
+      <c r="BW19" t="inlineStr">
+        <is>
           <t>28.60%</t>
         </is>
       </c>
-      <c r="BW19" t="inlineStr">
+      <c r="BX19" t="inlineStr">
         <is>
           <t>6.85%</t>
         </is>
       </c>
-      <c r="BX19" t="inlineStr">
-        <is>
-          <t>40.81</t>
-        </is>
-      </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>65982</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
+          <t>64921</t>
+        </is>
+      </c>
+      <c r="CA19" t="inlineStr">
+        <is>
           <t>線性滑軌64.00%、滾珠螺桿20.00%、其他9.00%、機器人7.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA19" t="inlineStr">
+      <c r="CB19" t="inlineStr">
         <is>
           <t>上銀-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB19" t="inlineStr">
+      <c r="CC19" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="CC19" t="inlineStr">
-        <is>
-          <t>209.5</t>
-        </is>
-      </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>196.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="CH19" t="inlineStr">
+        <is>
           <t>104.05</t>
         </is>
       </c>
-      <c r="CH19" t="inlineStr">
+      <c r="CI19" t="inlineStr">
         <is>
           <t>** 電機機械 - 傳動元件** 自動化 - 工業型機器人</t>
         </is>
       </c>
-      <c r="CI19" t="inlineStr">
+      <c r="CJ19" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -8636,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2678.776</t>
+          <t>5932.964</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-12.33</t>
+          <t>-11.72</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-18.01</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>-5.96</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>18.40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8787,57 +8882,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>213.8</t>
+          <t>211.3</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>215.92</t>
+          <t>215.75</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>215.67</t>
+          <t>215.46</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>214.41</t>
+          <t>214.3</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-230.30</t>
+          <t>-1398.14</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-97.28</t>
+          <t>-99.40</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,198 +8952,203 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1328980452.88705</t>
+          <t>1328011393.327586</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>567691568.0</t>
+          <t>1219768240.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>439899852.8</t>
+          <t>600139410.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>536558115.5</t>
+          <t>623193432.6</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>818287549.92</t>
+          <t>825475916.8</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-96658262</t>
+          <t>-23054022</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-48838107.26937589</t>
-        </is>
-      </c>
-      <c r="BC20" t="n">
-        <v>-42646682.16</v>
-      </c>
-      <c r="BD20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-39192955.43611298</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>13855379.64683306</t>
+        </is>
+      </c>
+      <c r="BD20" t="n">
+        <v>1219768240</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
           <t>219.0</t>
         </is>
       </c>
-      <c r="BF20" t="inlineStr">
+      <c r="BG20" t="inlineStr">
         <is>
           <t>2025/09/18</t>
         </is>
       </c>
-      <c r="BG20" t="inlineStr">
-        <is>
-          <t>-4.34</t>
-        </is>
-      </c>
       <c r="BH20" t="inlineStr">
         <is>
+          <t>-6.39</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
           <t>上銀</t>
         </is>
       </c>
-      <c r="BI20" t="inlineStr">
+      <c r="BJ20" t="inlineStr">
         <is>
           <t>上銀</t>
         </is>
       </c>
-      <c r="BJ20" t="inlineStr">
+      <c r="BK20" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK20" t="inlineStr">
+      <c r="BL20" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL20" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
       <c r="BM20" t="inlineStr">
         <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BN20" t="inlineStr">
+        <is>
           <t>0.5246961718756727</t>
         </is>
       </c>
-      <c r="BN20" t="inlineStr">
+      <c r="BO20" t="inlineStr">
         <is>
           <t>-3.316042339543704</t>
         </is>
       </c>
-      <c r="BO20" t="inlineStr">
+      <c r="BP20" t="inlineStr">
         <is>
           <t>-1.626286550608443</t>
         </is>
       </c>
-      <c r="BP20" t="inlineStr">
+      <c r="BQ20" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
-      <c r="BQ20" t="inlineStr">
+      <c r="BR20" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BR20" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="BU20" t="inlineStr">
+        <is>
           <t>16.95</t>
         </is>
       </c>
-      <c r="BU20" t="inlineStr">
-        <is>
-          <t>47.34</t>
-        </is>
-      </c>
       <c r="BV20" t="inlineStr">
         <is>
+          <t>46.57</t>
+        </is>
+      </c>
+      <c r="BW20" t="inlineStr">
+        <is>
           <t>28.60%</t>
         </is>
       </c>
-      <c r="BW20" t="inlineStr">
+      <c r="BX20" t="inlineStr">
         <is>
           <t>6.85%</t>
         </is>
       </c>
-      <c r="BX20" t="inlineStr">
-        <is>
-          <t>40.81</t>
-        </is>
-      </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>65982</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
+          <t>64921</t>
+        </is>
+      </c>
+      <c r="CA20" t="inlineStr">
+        <is>
           <t>線性滑軌64.00%、滾珠螺桿20.00%、其他9.00%、機器人7.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA20" t="inlineStr">
+      <c r="CB20" t="inlineStr">
         <is>
           <t>上銀-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB20" t="inlineStr">
+      <c r="CC20" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="CC20" t="inlineStr">
-        <is>
-          <t>211.0</t>
-        </is>
-      </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>209.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
+          <t>205.0</t>
+        </is>
+      </c>
+      <c r="CH20" t="inlineStr">
+        <is>
           <t>104.05</t>
         </is>
       </c>
-      <c r="CH20" t="inlineStr">
+      <c r="CI20" t="inlineStr">
         <is>
           <t>** 電機機械 - 傳動元件** 自動化 - 工業型機器人</t>
         </is>
       </c>
-      <c r="CI20" t="inlineStr">
+      <c r="CJ20" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -9067,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2889.254</t>
+          <t>2678.776</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>209.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-12.6</t>
+          <t>-14.17</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-18.01</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,12 +9298,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9213,62 +9313,62 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>215.3</t>
+          <t>213.8</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>216.22</t>
+          <t>215.92</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>215.78</t>
+          <t>215.67</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>214.37</t>
+          <t>214.41</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-110.18</t>
+          <t>-230.30</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-95.72</t>
+          <t>-97.28</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,198 +9388,203 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1328980452.88705</t>
+          <t>1328011393.327586</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>610019102.0</t>
+          <t>567691568.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>504405071.0</t>
+          <t>439899852.8</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>521300497.5</t>
+          <t>536558115.5</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>817903324.56</t>
+          <t>818287549.92</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-16895426</t>
+          <t>-96658262</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-49963820.92529882</t>
-        </is>
-      </c>
-      <c r="BC21" t="n">
-        <v>-51975459.81</v>
-      </c>
-      <c r="BD21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-48838107.26937589</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>-42646682.16179979</t>
+        </is>
+      </c>
+      <c r="BD21" t="n">
+        <v>567691568</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
           <t>219.0</t>
         </is>
       </c>
-      <c r="BF21" t="inlineStr">
+      <c r="BG21" t="inlineStr">
         <is>
           <t>2025/09/18</t>
         </is>
       </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>-4.11</t>
-        </is>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
+          <t>-4.34</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
           <t>上銀</t>
         </is>
       </c>
-      <c r="BI21" t="inlineStr">
+      <c r="BJ21" t="inlineStr">
         <is>
           <t>上銀</t>
         </is>
       </c>
-      <c r="BJ21" t="inlineStr">
+      <c r="BK21" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK21" t="inlineStr">
+      <c r="BL21" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL21" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
       <c r="BM21" t="inlineStr">
         <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
           <t>0.5246961718756727</t>
         </is>
       </c>
-      <c r="BN21" t="inlineStr">
+      <c r="BO21" t="inlineStr">
         <is>
           <t>-3.316042339543704</t>
         </is>
       </c>
-      <c r="BO21" t="inlineStr">
+      <c r="BP21" t="inlineStr">
         <is>
           <t>-1.626286550608443</t>
         </is>
       </c>
-      <c r="BP21" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ21" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BR21" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="BU21" t="inlineStr">
+        <is>
           <t>16.95</t>
         </is>
       </c>
-      <c r="BU21" t="inlineStr">
-        <is>
-          <t>47.34</t>
-        </is>
-      </c>
       <c r="BV21" t="inlineStr">
         <is>
+          <t>46.57</t>
+        </is>
+      </c>
+      <c r="BW21" t="inlineStr">
+        <is>
           <t>28.60%</t>
         </is>
       </c>
-      <c r="BW21" t="inlineStr">
+      <c r="BX21" t="inlineStr">
         <is>
           <t>6.85%</t>
         </is>
       </c>
-      <c r="BX21" t="inlineStr">
-        <is>
-          <t>40.81</t>
-        </is>
-      </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>65982</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
+          <t>64921</t>
+        </is>
+      </c>
+      <c r="CA21" t="inlineStr">
+        <is>
           <t>線性滑軌64.00%、滾珠螺桿20.00%、其他9.00%、機器人7.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA21" t="inlineStr">
+      <c r="CB21" t="inlineStr">
         <is>
           <t>上銀-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB21" t="inlineStr">
+      <c r="CC21" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="CC21" t="inlineStr">
-        <is>
-          <t>215.5</t>
-        </is>
-      </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>217.0</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>209.0</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>209.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
+          <t>209.5</t>
+        </is>
+      </c>
+      <c r="CH21" t="inlineStr">
+        <is>
           <t>104.05</t>
         </is>
       </c>
-      <c r="CH21" t="inlineStr">
+      <c r="CI21" t="inlineStr">
         <is>
           <t>** 電機機械 - 傳動元件** 自動化 - 工業型機器人</t>
         </is>
       </c>
-      <c r="CI21" t="inlineStr">
+      <c r="CJ21" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -9498,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1787.511</t>
+          <t>2889.254</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-14.75</t>
+          <t>-14.44</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,12 +9734,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9644,62 +9749,62 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>218.3</t>
+          <t>215.3</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>216.95</t>
+          <t>216.22</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>215.86</t>
+          <t>215.78</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>214.34</t>
+          <t>214.37</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-40.27</t>
+          <t>-110.18</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-94.54</t>
+          <t>-95.72</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,198 +9824,203 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1328980452.88705</t>
+          <t>1328011393.327586</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>382544523.0</t>
+          <t>610019102.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>483349348.8</t>
+          <t>504405071.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>525432672.9</t>
+          <t>521300497.5</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>817817970.04</t>
+          <t>817903324.56</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-42083324</t>
+          <t>-16895426</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-49598068.40058749</t>
-        </is>
-      </c>
-      <c r="BC22" t="n">
-        <v>-67981111.53</v>
-      </c>
-      <c r="BD22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-49963820.92529882</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>-51975459.81121111</t>
+        </is>
+      </c>
+      <c r="BD22" t="n">
+        <v>610019102</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
           <t>219.0</t>
         </is>
       </c>
-      <c r="BF22" t="inlineStr">
+      <c r="BG22" t="inlineStr">
         <is>
           <t>2025/09/18</t>
         </is>
       </c>
-      <c r="BG22" t="inlineStr">
-        <is>
-          <t>-2.28</t>
-        </is>
-      </c>
       <c r="BH22" t="inlineStr">
         <is>
+          <t>-4.11</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
           <t>上銀</t>
         </is>
       </c>
-      <c r="BI22" t="inlineStr">
+      <c r="BJ22" t="inlineStr">
         <is>
           <t>上銀</t>
         </is>
       </c>
-      <c r="BJ22" t="inlineStr">
+      <c r="BK22" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK22" t="inlineStr">
+      <c r="BL22" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL22" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
       <c r="BM22" t="inlineStr">
         <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BN22" t="inlineStr">
+        <is>
           <t>0.5246961718756727</t>
         </is>
       </c>
-      <c r="BN22" t="inlineStr">
+      <c r="BO22" t="inlineStr">
         <is>
           <t>-3.316042339543704</t>
         </is>
       </c>
-      <c r="BO22" t="inlineStr">
+      <c r="BP22" t="inlineStr">
         <is>
           <t>-1.626286550608443</t>
         </is>
       </c>
-      <c r="BP22" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ22" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR22" t="inlineStr">
-        <is>
-          <t>2.06</t>
-        </is>
-      </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="BU22" t="inlineStr">
+        <is>
           <t>16.95</t>
         </is>
       </c>
-      <c r="BU22" t="inlineStr">
-        <is>
-          <t>47.34</t>
-        </is>
-      </c>
       <c r="BV22" t="inlineStr">
         <is>
+          <t>46.57</t>
+        </is>
+      </c>
+      <c r="BW22" t="inlineStr">
+        <is>
           <t>28.60%</t>
         </is>
       </c>
-      <c r="BW22" t="inlineStr">
+      <c r="BX22" t="inlineStr">
         <is>
           <t>6.85%</t>
         </is>
       </c>
-      <c r="BX22" t="inlineStr">
-        <is>
-          <t>40.81</t>
-        </is>
-      </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>65982</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
+          <t>64921</t>
+        </is>
+      </c>
+      <c r="CA22" t="inlineStr">
+        <is>
           <t>線性滑軌64.00%、滾珠螺桿20.00%、其他9.00%、機器人7.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA22" t="inlineStr">
+      <c r="CB22" t="inlineStr">
         <is>
           <t>上銀-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB22" t="inlineStr">
+      <c r="CC22" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="CC22" t="inlineStr">
-        <is>
-          <t>216.5</t>
-        </is>
-      </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>216.5</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>212.5</t>
+          <t>217.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>209.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="CH22" t="inlineStr">
+        <is>
           <t>104.05</t>
         </is>
       </c>
-      <c r="CH22" t="inlineStr">
+      <c r="CI22" t="inlineStr">
         <is>
           <t>** 電機機械 - 傳動元件** 自動化 - 工業型機器人</t>
         </is>
       </c>
-      <c r="CI22" t="inlineStr">
+      <c r="CJ22" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -9929,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1014.871</t>
+          <t>1787.511</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,72 +10054,72 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>214.0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-16.62</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-4.68</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-8.01</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>220.0</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
           <t>218.0</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>-16.89</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>-4.43</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>220.0</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>218.0</t>
-        </is>
-      </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -10024,12 +10134,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,17 +10170,17 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -10080,57 +10190,57 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>220.2</t>
+          <t>218.3</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>217.68</t>
+          <t>216.95</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>215.88</t>
+          <t>215.86</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>214.24</t>
+          <t>214.34</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-40.27</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-93.99</t>
+          <t>-94.54</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,198 +10260,203 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1328980452.88705</t>
+          <t>1328011393.327586</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>220673617.0</t>
+          <t>382544523.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>558439661.0</t>
+          <t>483349348.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>552641417.0</t>
+          <t>525432672.9</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>844929542.22</t>
+          <t>817817970.04</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>5798244</t>
+          <t>-42083324</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-46255696.92225825</t>
-        </is>
-      </c>
-      <c r="BC23" t="n">
-        <v>-64046155.11</v>
-      </c>
-      <c r="BD23" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
+          <t>-49598068.40058749</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>-67981111.53139836</t>
+        </is>
+      </c>
+      <c r="BD23" t="n">
+        <v>382544523</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
           <t>219.0</t>
         </is>
       </c>
-      <c r="BF23" t="inlineStr">
+      <c r="BG23" t="inlineStr">
         <is>
           <t>2025/09/18</t>
         </is>
       </c>
-      <c r="BG23" t="inlineStr">
-        <is>
-          <t>-0.46</t>
-        </is>
-      </c>
       <c r="BH23" t="inlineStr">
         <is>
+          <t>-2.28</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
           <t>上銀</t>
         </is>
       </c>
-      <c r="BI23" t="inlineStr">
+      <c r="BJ23" t="inlineStr">
         <is>
           <t>上銀</t>
         </is>
       </c>
-      <c r="BJ23" t="inlineStr">
+      <c r="BK23" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK23" t="inlineStr">
+      <c r="BL23" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL23" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
       <c r="BM23" t="inlineStr">
         <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BN23" t="inlineStr">
+        <is>
           <t>0.5246961718756727</t>
         </is>
       </c>
-      <c r="BN23" t="inlineStr">
+      <c r="BO23" t="inlineStr">
         <is>
           <t>-3.316042339543704</t>
         </is>
       </c>
-      <c r="BO23" t="inlineStr">
+      <c r="BP23" t="inlineStr">
         <is>
           <t>-1.626286550608443</t>
         </is>
       </c>
-      <c r="BP23" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ23" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR23" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="BU23" t="inlineStr">
+        <is>
           <t>16.95</t>
         </is>
       </c>
-      <c r="BU23" t="inlineStr">
-        <is>
-          <t>47.34</t>
-        </is>
-      </c>
       <c r="BV23" t="inlineStr">
         <is>
+          <t>46.57</t>
+        </is>
+      </c>
+      <c r="BW23" t="inlineStr">
+        <is>
           <t>28.60%</t>
         </is>
       </c>
-      <c r="BW23" t="inlineStr">
+      <c r="BX23" t="inlineStr">
         <is>
           <t>6.85%</t>
         </is>
       </c>
-      <c r="BX23" t="inlineStr">
-        <is>
-          <t>40.81</t>
-        </is>
-      </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>65982</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
+          <t>64921</t>
+        </is>
+      </c>
+      <c r="CA23" t="inlineStr">
+        <is>
           <t>線性滑軌64.00%、滾珠螺桿20.00%、其他9.00%、機器人7.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA23" t="inlineStr">
+      <c r="CB23" t="inlineStr">
         <is>
           <t>上銀-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB23" t="inlineStr">
+      <c r="CC23" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="CC23" t="inlineStr">
-        <is>
-          <t>219.5</t>
-        </is>
-      </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>216.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>216.0</t>
+          <t>216.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>212.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
+          <t>214.0</t>
+        </is>
+      </c>
+      <c r="CH23" t="inlineStr">
+        <is>
           <t>104.05</t>
         </is>
       </c>
-      <c r="CH23" t="inlineStr">
+      <c r="CI23" t="inlineStr">
         <is>
           <t>** 電機機械 - 傳動元件** 自動化 - 工業型機器人</t>
         </is>
       </c>
-      <c r="CI23" t="inlineStr">
+      <c r="CJ23" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/工業型機器人.xlsx
+++ b/Result/checksun_type/工業型機器人.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>428.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-11.10</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-28.24</t>
+          <t>-26.71</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.62</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-10.02</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-7.9</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>13.29</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>641.0</t>
+          <t>631.4</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>712.35</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>773.42</t>
+          <t>772.34</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>679.24</t>
+          <t>681.75</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-44.55</t>
+          <t>-36.56</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-38.37</t>
+          <t>-39.90</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-26.55</t>
+          <t>-29.22</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-129.51</t>
+          <t>-132.48</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>411084.8333333334</t>
+          <t>410388.9211409396</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>262274.0</t>
+          <t>135802.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>287562.6</t>
+          <t>252624.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>323456.1</t>
+          <t>286992.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>664782.5</t>
+          <t>639483.2</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-35893</t>
+          <t>-34368</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-49370.81863454734</t>
+          <t>-50054.82905734108</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-46587.93819697743</t>
+          <t>-53816.8863827067</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>262274</v>
+        <v>135802</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>133.27</t>
+          <t>138.24</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.41</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>51.61</t>
+          <t>52.71</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>624.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>630.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>600.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>377.0</t>
+          <t>428.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-11.10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-28.24</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,12 +1450,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1470,57 +1470,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-10.02</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-7.9</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>657.8</t>
+          <t>641.0</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>718.95</t>
+          <t>712.35</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>774.36</t>
+          <t>773.42</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>677.44</t>
+          <t>679.24</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-46.43</t>
+          <t>-44.55</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-34.54</t>
+          <t>-38.37</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-23.59</t>
+          <t>-26.55</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-126.22</t>
+          <t>-129.51</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>411084.8333333334</t>
+          <t>410388.9211409396</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>245558.0</t>
+          <t>262274.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>296429.4</t>
+          <t>287562.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>325427.2</t>
+          <t>323456.1</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>674644.66</t>
+          <t>664782.5</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-28997</t>
+          <t>-35893</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-49876.79689592369</t>
+          <t>-49370.81863454734</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-48147.58585318638</t>
+          <t>-46587.93819697743</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>245558</v>
+        <v>262274</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>143.98</t>
+          <t>133.27</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>51.61</t>
+          <t>52.71</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>624.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>672.0</t>
+          <t>630.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>600.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>371.0</t>
+          <t>377.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.92</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-23.31</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,12 +1886,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1906,57 +1906,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>671.6</t>
+          <t>657.8</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>725.65</t>
+          <t>718.95</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>773.56</t>
+          <t>774.36</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>675.4</t>
+          <t>677.44</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-53.49</t>
+          <t>-46.43</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-32.01</t>
+          <t>-34.54</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-20.85</t>
+          <t>-23.59</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-123.18</t>
+          <t>-126.22</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>411084.8333333334</t>
+          <t>410388.9211409396</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>241508.0</t>
+          <t>245558.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>292951.6</t>
+          <t>296429.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>382000.7</t>
+          <t>325427.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>675976.12</t>
+          <t>674644.66</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-89049</t>
+          <t>-28997</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-50191.19890369411</t>
+          <t>-49876.79689592369</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-46865.09729587106</t>
+          <t>-48147.58585318638</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>241508</v>
+        <v>245558</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>51.61</t>
+          <t>52.71</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>667.0</t>
+          <t>672.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>371.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-5.9</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-22.67</t>
+          <t>-23.31</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2342,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-6.42</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>686.2</t>
+          <t>671.6</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>733.3</t>
+          <t>725.65</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>772.84</t>
+          <t>773.56</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>675.4</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-57.81</t>
+          <t>-53.49</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-28.51</t>
+          <t>-32.01</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-18.06</t>
+          <t>-20.85</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-120.08</t>
+          <t>-123.18</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>411084.8333333334</t>
+          <t>410388.9211409396</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>377978.0</t>
+          <t>241508.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>309322.6</t>
+          <t>292951.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>400021.6</t>
+          <t>382000.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>677723.46</t>
+          <t>675976.12</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-90699</t>
+          <t>-89049</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-50795.94465057103</t>
+          <t>-50191.19890369411</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-42925.28873913951</t>
+          <t>-46865.09729587106</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>377978</v>
+        <v>241508</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>147.04</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>51.61</t>
+          <t>52.71</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>693.0</t>
+          <t>667.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>456.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-10.0</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-18.05</t>
+          <t>-22.67</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-21.06</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2778,57 +2778,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-6.42</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>702.8</t>
+          <t>686.2</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>740.6</t>
+          <t>733.3</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>771.72</t>
+          <t>772.84</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>670.89</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-56.83</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-24.23</t>
+          <t>-28.51</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-18.06</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-117.18</t>
+          <t>-120.08</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>411084.8333333334</t>
+          <t>410388.9211409396</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>310495.0</t>
+          <t>377978.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>321361.4</t>
+          <t>309322.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>392151.7</t>
+          <t>400021.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>673300.18</t>
+          <t>677723.46</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-70790</t>
+          <t>-90699</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-52226.97299810403</t>
+          <t>-50795.94465057103</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-50385.73048883944</t>
+          <t>-42925.28873913951</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>310495</v>
+        <v>377978</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>156.60</t>
+          <t>147.04</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>51.61</t>
+          <t>52.71</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>699.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>444.0</t>
+          <t>456.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-13.77</t>
+          <t>-7.7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-18.05</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-18.35</t>
+          <t>-21.06</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3214,57 +3214,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>15.03</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>711.8</t>
+          <t>702.8</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>747.5</t>
+          <t>740.6</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>770.14</t>
+          <t>771.72</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>668.28</t>
+          <t>670.89</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-58.22</t>
+          <t>-56.83</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-20.97</t>
+          <t>-24.23</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-15.45</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-114.74</t>
+          <t>-117.18</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>411084.8333333334</t>
+          <t>410388.9211409396</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>306608.0</t>
+          <t>310495.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>359349.6</t>
+          <t>321361.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>389319.8</t>
+          <t>392151.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>672018.02</t>
+          <t>673300.18</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-29970</t>
+          <t>-70790</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-52561.74436342486</t>
+          <t>-52226.97299810403</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-52013.69261380937</t>
+          <t>-50385.73048883944</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>306608</v>
+        <v>310495</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>165.39</t>
+          <t>156.60</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>18.28</t>
+          <t>17.68</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>51.61</t>
+          <t>52.71</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3457,17 +3457,17 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>679.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>444.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-15.9</t>
+          <t>-11.4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-16.82</t>
+          <t>-18.35</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,62 +3645,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>15.24</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>722.4</t>
+          <t>711.8</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>754.55</t>
+          <t>747.5</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>768.06</t>
+          <t>770.14</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>665.62</t>
+          <t>668.28</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-66.42</t>
+          <t>-58.22</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-18.85</t>
+          <t>-20.97</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-112.59</t>
+          <t>-114.74</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>411084.8333333334</t>
+          <t>410388.9211409396</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>228169.0</t>
+          <t>306608.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>354425.0</t>
+          <t>359349.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>390521.3</t>
+          <t>389319.8</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>675976.46</t>
+          <t>672018.02</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-36096</t>
+          <t>-29970</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-52661.39013608223</t>
+          <t>-52561.74436342486</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-52065.25662755885</t>
+          <t>-52013.69261380937</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>228169</v>
+        <v>306608</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>170.36</t>
+          <t>165.39</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>51.61</t>
+          <t>52.71</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>699.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>679.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>448.0</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-16.89</t>
+          <t>-13.48</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-16.12</t>
+          <t>-16.82</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4086,57 +4086,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>722.4</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>760.7</t>
+          <t>754.55</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>766.1</t>
+          <t>768.06</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>662.74</t>
+          <t>665.62</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-81.98</t>
+          <t>-66.42</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-17.19</t>
+          <t>-18.85</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-110.50</t>
+          <t>-112.59</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>411084.8333333334</t>
+          <t>410388.9211409396</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>323363.0</t>
+          <t>228169.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>471049.8</t>
+          <t>354425.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>445989.1</t>
+          <t>390521.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>679269.88</t>
+          <t>675976.46</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>25060</t>
+          <t>-36096</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-52769.77804672284</t>
+          <t>-52661.39013608223</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-41875.26748193102</t>
+          <t>-52065.25662755885</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>323363</v>
+        <v>228169</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>172.66</t>
+          <t>170.36</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.62</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>51.61</t>
+          <t>52.71</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>710.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>606.0</t>
+          <t>448.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>713.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-19.51</t>
+          <t>-14.45</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-14.24</t>
+          <t>-16.12</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>15.60</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>737.8</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>765.9</t>
+          <t>760.7</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>763.84</t>
+          <t>766.1</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>659.24</t>
+          <t>662.74</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-105.47</t>
+          <t>-81.98</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-15.43</t>
+          <t>-17.19</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-7.51</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-108.35</t>
+          <t>-110.50</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>411084.8333333334</t>
+          <t>410388.9211409396</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>438172.0</t>
+          <t>323363.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>490720.6</t>
+          <t>471049.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>467960.7</t>
+          <t>445989.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>683118.66</t>
+          <t>679269.88</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>22759</t>
+          <t>25060</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-54750.59814941225</t>
+          <t>-52769.77804672284</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-36021.95200667955</t>
+          <t>-41875.26748193102</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>438172</v>
+        <v>323363</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>178.78</t>
+          <t>172.66</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.78</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>51.61</t>
+          <t>52.71</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>748.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>710.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>713.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>606.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-17.38</t>
+          <t>-17.01</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-14.24</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>18.93</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.07</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>52.47</t>
+          <t>27.16</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>735.2</t>
+          <t>737.8</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>771.95</t>
+          <t>765.9</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>761.14</t>
+          <t>763.84</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>655.4</t>
+          <t>659.24</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-163.86</t>
+          <t>-105.47</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-14.59</t>
+          <t>-15.43</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-7.51</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-106.15</t>
+          <t>-108.35</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>411084.8333333334</t>
+          <t>410388.9211409396</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>500436.0</t>
+          <t>438172.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>462942.0</t>
+          <t>490720.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>451797.8</t>
+          <t>467960.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>687666.36</t>
+          <t>683118.66</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>22759</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-58155.80653900002</t>
+          <t>-54750.59814941225</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-38674.53875608178</t>
+          <t>-36021.95200667955</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>500436</v>
+        <v>438172</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>173.80</t>
+          <t>178.78</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>51.61</t>
+          <t>52.71</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>751.0</t>
+          <t>748.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>376.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-22.46</t>
+          <t>-14.93</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-12.12</t>
+          <t>-15.76</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>57.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>59.26</t>
+          <t>52.47</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>16.13</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>740.6</t>
+          <t>735.2</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>780.25</t>
+          <t>771.95</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>759.12</t>
+          <t>761.14</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>651.25</t>
+          <t>655.4</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-267.06</t>
+          <t>-163.86</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-14.59</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-103.63</t>
+          <t>-106.15</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>411084.8333333334</t>
+          <t>410388.9211409396</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>281985.0</t>
+          <t>500436.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>419290.0</t>
+          <t>462942.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>432429.0</t>
+          <t>451797.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>696544.24</t>
+          <t>687666.36</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-13139</t>
+          <t>11144</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-61697.85522680334</t>
+          <t>-58155.80653900002</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-47753.85772822483</t>
+          <t>-38674.53875608178</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>281985</v>
+        <v>500436</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>185.66</t>
+          <t>173.80</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>51.61</t>
+          <t>52.71</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>756.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>761.0</t>
+          <t>751.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>742.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>747.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2375.624</t>
+          <t>3925.483</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>181.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-13.38</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-15.83</t>
+          <t>-16.97</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>7.37</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,12 +5810,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5830,57 +5830,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-9.85</t>
+          <t>-10.16</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>187.2</t>
+          <t>184.8</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>207.65</t>
+          <t>205.7</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>213.15</t>
+          <t>212.36</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>212.2</t>
+          <t>211.81</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-63.70</t>
+          <t>-53.22</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-8.14</t>
+          <t>-8.79</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-126.52</t>
+          <t>-130.59</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1328011393.327586</t>
+          <t>1327643364.675753</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>436343333.0</t>
+          <t>714330282.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>624341783.8</t>
+          <t>583542929.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>720759640.4</t>
+          <t>731190758.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>863704924.02</t>
+          <t>788163169.8</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-96417856</t>
+          <t>-147647829</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-5796842.170584051</t>
+          <t>-6859780.775898567</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-21936480.56422627</t>
+          <t>-12705943.10512841</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>436343333</v>
+        <v>714330282</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-16.21</t>
+          <t>-17.35</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>46.57</t>
+          <t>45.94</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>64921</t>
+          <t>64036</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>184.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>180.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>181.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3128.645</t>
+          <t>2375.624</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>186.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-13.38</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-14.45</t>
+          <t>-15.83</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>7.37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,12 +6246,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6266,57 +6266,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-9.85</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>190.2</t>
+          <t>187.2</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>209.58</t>
+          <t>207.65</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>213.6</t>
+          <t>213.15</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>212.58</t>
+          <t>212.2</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-78.19</t>
+          <t>-63.70</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-8.14</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-122.29</t>
+          <t>-126.52</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1328011393.327586</t>
+          <t>1327643364.675753</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>587620146.0</t>
+          <t>436343333.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>674218506.6</t>
+          <t>624341783.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>715379759.4</t>
+          <t>720759640.4</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>864477556.2</t>
+          <t>863704924.02</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-41161252</t>
+          <t>-96417856</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-2862362.462649101</t>
+          <t>-5796842.170584051</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-4555200.949929357</t>
+          <t>-21936480.56422627</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>587620146</v>
+        <v>436343333</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-14.84</t>
+          <t>-16.21</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,22 +6439,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>46.57</t>
+          <t>45.94</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>64921</t>
+          <t>64036</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>189.5</t>
+          <t>184.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>191.5</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>186.5</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>186.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2437.772</t>
+          <t>3128.645</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,12 +6682,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6702,57 +6702,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-8.70</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>192.9</t>
+          <t>190.2</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>211.28</t>
+          <t>209.58</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>214.03</t>
+          <t>213.6</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>212.96</t>
+          <t>212.58</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-101.13</t>
+          <t>-78.19</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-117.94</t>
+          <t>-122.29</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1328011393.327586</t>
+          <t>1327643364.675753</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>456346640.0</t>
+          <t>587620146.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>757230803.0</t>
+          <t>674218506.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>678685106.5</t>
+          <t>715379759.4</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>856936697.08</t>
+          <t>864477556.2</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>78545696</t>
+          <t>-41161252</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-2554573.646779964</t>
+          <t>-2862362.462649101</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>4229654.282992125</t>
+          <t>-4555200.949929357</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>456346640</v>
+        <v>587620146</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6875,12 +6875,12 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>46.57</t>
+          <t>45.94</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>64921</t>
+          <t>64036</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,17 +6940,17 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
+          <t>189.5</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>191.5</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
           <t>186.5</t>
-        </is>
-      </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>190.0</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>185.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3839.598</t>
+          <t>2437.772</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,12 +7118,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7138,57 +7138,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-8.70</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>196.6</t>
+          <t>192.9</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>212.75</t>
+          <t>211.28</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>214.42</t>
+          <t>214.03</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>213.34</t>
+          <t>212.96</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-130.49</t>
+          <t>-101.13</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-113.40</t>
+          <t>-117.94</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1328011393.327586</t>
+          <t>1327643364.675753</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>723074244.0</t>
+          <t>456346640.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>909915123.0</t>
+          <t>757230803.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>674907487.9</t>
+          <t>678685106.5</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>854335140.06</t>
+          <t>856936697.08</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>235007635</t>
+          <t>78545696</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-3788069.634011253</t>
+          <t>-2554573.646779964</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>30693406.89134467</t>
+          <t>4229654.282992125</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>723074244</v>
+        <v>456346640</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>46.57</t>
+          <t>45.94</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>64921</t>
+          <t>64036</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,17 +7376,17 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>191.5</t>
+          <t>190.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4701.928</t>
+          <t>3839.598</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-14.45</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14.59</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,12 +7554,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7574,57 +7574,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>201.2</t>
+          <t>196.6</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>213.98</t>
+          <t>212.75</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>214.79</t>
+          <t>214.42</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>213.72</t>
+          <t>213.34</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-163.83</t>
+          <t>-130.49</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-109.03</t>
+          <t>-113.40</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1328011393.327586</t>
+          <t>1327643364.675753</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>918324556.0</t>
+          <t>723074244.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>878838587.8</t>
+          <t>909915123.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>691621829.4</t>
+          <t>674907487.9</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>845368183.24</t>
+          <t>854335140.06</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>187216758</t>
+          <t>235007635</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-10057429.00225778</t>
+          <t>-3788069.634011253</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>38824617.085729</t>
+          <t>30693406.89134467</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>918324556</v>
+        <v>723074244</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-11.87</t>
+          <t>-14.84</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>46.57</t>
+          <t>45.94</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>64921</t>
+          <t>64036</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>191.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3457.008</t>
+          <t>4701.928</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-8.17</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>25.67</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-8.94</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10.72</t>
+          <t>14.59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8010,57 +8010,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>204.6</t>
+          <t>201.2</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>214.72</t>
+          <t>213.98</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>215.02</t>
+          <t>214.79</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>213.92</t>
+          <t>213.72</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-237.34</t>
+          <t>-163.83</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-105.33</t>
+          <t>-109.03</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1328011393.327586</t>
+          <t>1327643364.675753</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>685726947.0</t>
+          <t>918324556.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>817177497.0</t>
+          <t>878838587.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>650263422.9</t>
+          <t>691621829.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>838743112.42</t>
+          <t>845368183.24</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>166914074</t>
+          <t>187216758</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-18945073.74552811</t>
+          <t>-10057429.00225778</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>28134361.89607322</t>
+          <t>38824617.085729</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>685726947</v>
+        <v>918324556</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-11.87</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>46.57</t>
+          <t>45.94</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>64921</t>
+          <t>64036</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>195.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5006.119</t>
+          <t>3457.008</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-9.67</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>25.67</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-8.94</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>10.72</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8446,57 +8446,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>207.7</t>
+          <t>204.6</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>215.3</t>
+          <t>214.72</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>215.19</t>
+          <t>215.02</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>214.13</t>
+          <t>213.92</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-511.52</t>
+          <t>-237.34</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-102.17</t>
+          <t>-105.33</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1328011393.327586</t>
+          <t>1327643364.675753</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>1002681628.0</t>
+          <t>685726947.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>756541012.2</t>
+          <t>817177497.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>657490336.6</t>
+          <t>650263422.9</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>837159531.8</t>
+          <t>838743112.42</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>99050675</t>
+          <t>166914074</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-27504971.13491017</t>
+          <t>-18945073.74552811</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>36778942.52170527</t>
+          <t>28134361.89607322</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>1002681628</v>
+        <v>685726947</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-8.68</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,22 +8619,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>46.57</t>
+          <t>45.94</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>64921</t>
+          <t>64036</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
+          <t>195.0</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
           <t>201.0</t>
         </is>
       </c>
-      <c r="CE19" t="inlineStr">
-        <is>
-          <t>205.0</t>
-        </is>
-      </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5932.964</t>
+          <t>5006.119</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-11.72</t>
+          <t>-10.5</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>15.06</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-5.96</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18.40</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8882,57 +8882,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>211.3</t>
+          <t>207.7</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>215.75</t>
+          <t>215.3</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>215.46</t>
+          <t>215.19</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>214.3</t>
+          <t>214.13</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-1398.14</t>
+          <t>-511.52</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-99.40</t>
+          <t>-102.17</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1328011393.327586</t>
+          <t>1327643364.675753</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>1219768240.0</t>
+          <t>1002681628.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>600139410.0</t>
+          <t>756541012.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>623193432.6</t>
+          <t>657490336.6</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>825475916.8</t>
+          <t>837159531.8</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-23054022</t>
+          <t>99050675</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-39192955.43611298</t>
+          <t>-27504971.13491017</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>13855379.64683306</t>
+          <t>36778942.52170527</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>1219768240</v>
+        <v>1002681628</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-8.68</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>46.57</t>
+          <t>45.94</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>64921</t>
+          <t>64036</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>196.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2678.776</t>
+          <t>5932.964</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-14.17</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-18.01</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>-5.96</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>18.40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,12 +9298,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9318,57 +9318,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>213.8</t>
+          <t>211.3</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>215.92</t>
+          <t>215.75</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>215.67</t>
+          <t>215.46</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>214.41</t>
+          <t>214.3</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-230.30</t>
+          <t>-1398.14</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-97.28</t>
+          <t>-99.40</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1328011393.327586</t>
+          <t>1327643364.675753</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>567691568.0</t>
+          <t>1219768240.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>439899852.8</t>
+          <t>600139410.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>536558115.5</t>
+          <t>623193432.6</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>818287549.92</t>
+          <t>825475916.8</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-96658262</t>
+          <t>-23054022</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-48838107.26937589</t>
+          <t>-39192955.43611298</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-42646682.16179979</t>
+          <t>13855379.64683306</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>567691568</v>
+        <v>1219768240</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9496,17 +9496,17 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>46.57</t>
+          <t>45.94</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>64921</t>
+          <t>64036</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>209.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2889.254</t>
+          <t>2678.776</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>209.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-14.44</t>
+          <t>-15.75</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-18.01</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,12 +9734,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9749,62 +9749,62 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>215.3</t>
+          <t>213.8</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>216.22</t>
+          <t>215.92</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>215.78</t>
+          <t>215.67</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>214.37</t>
+          <t>214.41</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-110.18</t>
+          <t>-230.30</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-95.72</t>
+          <t>-97.28</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1328011393.327586</t>
+          <t>1327643364.675753</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>610019102.0</t>
+          <t>567691568.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>504405071.0</t>
+          <t>439899852.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>521300497.5</t>
+          <t>536558115.5</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>817903324.56</t>
+          <t>818287549.92</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-16895426</t>
+          <t>-96658262</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-49963820.92529882</t>
+          <t>-48838107.26937589</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-51975459.81121111</t>
+          <t>-42646682.16179979</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>610019102</v>
+        <v>567691568</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-4.11</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>46.57</t>
+          <t>45.94</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>64921</t>
+          <t>64036</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>217.0</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>209.0</t>
+          <t>209.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>209.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1787.511</t>
+          <t>2889.254</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-16.62</t>
+          <t>-16.02</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,12 +10170,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10185,62 +10185,62 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>218.3</t>
+          <t>215.3</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>216.95</t>
+          <t>216.22</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>215.86</t>
+          <t>215.78</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>214.34</t>
+          <t>214.37</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-40.27</t>
+          <t>-110.18</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-94.54</t>
+          <t>-95.72</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1328011393.327586</t>
+          <t>1327643364.675753</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>382544523.0</t>
+          <t>610019102.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>483349348.8</t>
+          <t>504405071.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>525432672.9</t>
+          <t>521300497.5</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>817817970.04</t>
+          <t>817903324.56</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-42083324</t>
+          <t>-16895426</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-49598068.40058749</t>
+          <t>-49963820.92529882</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-67981111.53139836</t>
+          <t>-51975459.81121111</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>382544523</v>
+        <v>610019102</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-4.11</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>46.57</t>
+          <t>45.94</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>64921</t>
+          <t>64036</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>216.5</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>216.5</t>
+          <t>217.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>212.5</t>
+          <t>209.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/工業型機器人.xlsx
+++ b/Result/checksun_type/工業型機器人.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>283.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-18.38</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-26.71</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>283</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>12.62</t>
+          <t>30.93</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-10.13</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-9.11</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>13.29</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>631.4</t>
+          <t>630.2</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>701.25</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>772.34</t>
+          <t>771.56</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>681.75</t>
+          <t>684.56</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-36.56</t>
+          <t>-25.78</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-39.90</t>
+          <t>-39.28</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-29.22</t>
+          <t>-31.23</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-132.48</t>
+          <t>-134.72</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>410388.9211409396</t>
+          <t>409924.9364548496</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>135802.0</t>
+          <t>181105.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>252624.0</t>
+          <t>213249.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>286992.7</t>
+          <t>261286.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>639483.2</t>
+          <t>631907.8</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-34368</t>
+          <t>-48036</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-50054.82905734108</t>
+          <t>-50682.39427208085</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-53816.8863827067</t>
+          <t>-54134.00295314955</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>135802</v>
+        <v>181105</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>138.24</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>16.41</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>52.71</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>654.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>629.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>428.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-11.10</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-28.24</t>
+          <t>-26.71</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>283</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.62</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-10.02</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-7.9</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>13.29</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>641.0</t>
+          <t>631.4</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>712.35</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>773.42</t>
+          <t>772.34</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>679.24</t>
+          <t>681.75</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-44.55</t>
+          <t>-36.56</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-38.37</t>
+          <t>-39.90</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-26.55</t>
+          <t>-29.22</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-129.51</t>
+          <t>-132.48</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>410388.9211409396</t>
+          <t>409924.9364548496</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>262274.0</t>
+          <t>135802.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>287562.6</t>
+          <t>252624.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>323456.1</t>
+          <t>286992.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>664782.5</t>
+          <t>639483.2</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-35893</t>
+          <t>-34368</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-49370.81863454734</t>
+          <t>-50054.82905734108</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-46587.93819697743</t>
+          <t>-53816.8863827067</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>262274</v>
+        <v>135802</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>133.27</t>
+          <t>138.24</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.41</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>52.71</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>624.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>630.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>600.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>377.0</t>
+          <t>428.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-11.10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-28.24</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,12 +1886,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>283</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1906,57 +1906,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-10.02</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-7.9</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>657.8</t>
+          <t>641.0</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>718.95</t>
+          <t>712.35</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>774.36</t>
+          <t>773.42</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>677.44</t>
+          <t>679.24</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-46.43</t>
+          <t>-44.55</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-34.54</t>
+          <t>-38.37</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-23.59</t>
+          <t>-26.55</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-126.22</t>
+          <t>-129.51</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>410388.9211409396</t>
+          <t>409924.9364548496</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>245558.0</t>
+          <t>262274.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>296429.4</t>
+          <t>287562.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>325427.2</t>
+          <t>323456.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>674644.66</t>
+          <t>664782.5</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-28997</t>
+          <t>-35893</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-49876.79689592369</t>
+          <t>-49370.81863454734</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-48147.58585318638</t>
+          <t>-46587.93819697743</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>245558</v>
+        <v>262274</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>143.98</t>
+          <t>133.27</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>52.71</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>624.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>672.0</t>
+          <t>630.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>600.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>371.0</t>
+          <t>377.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-23.31</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>283</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2342,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>671.6</t>
+          <t>657.8</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>725.65</t>
+          <t>718.95</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>773.56</t>
+          <t>774.36</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>675.4</t>
+          <t>677.44</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-53.49</t>
+          <t>-46.43</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-32.01</t>
+          <t>-34.54</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-20.85</t>
+          <t>-23.59</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-123.18</t>
+          <t>-126.22</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>410388.9211409396</t>
+          <t>409924.9364548496</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>241508.0</t>
+          <t>245558.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>292951.6</t>
+          <t>296429.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>382000.7</t>
+          <t>325427.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>675976.12</t>
+          <t>674644.66</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-89049</t>
+          <t>-28997</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-50191.19890369411</t>
+          <t>-49876.79689592369</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-46865.09729587106</t>
+          <t>-48147.58585318638</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>241508</v>
+        <v>245558</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>52.71</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,12 +2580,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>667.0</t>
+          <t>672.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>371.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-22.67</t>
+          <t>-23.31</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>283</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2778,57 +2778,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-6.42</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>686.2</t>
+          <t>671.6</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>733.3</t>
+          <t>725.65</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>772.84</t>
+          <t>773.56</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>675.4</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-57.81</t>
+          <t>-53.49</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-28.51</t>
+          <t>-32.01</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-18.06</t>
+          <t>-20.85</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-120.08</t>
+          <t>-123.18</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>410388.9211409396</t>
+          <t>409924.9364548496</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>377978.0</t>
+          <t>241508.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>309322.6</t>
+          <t>292951.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>400021.6</t>
+          <t>382000.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>677723.46</t>
+          <t>675976.12</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-90699</t>
+          <t>-89049</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-50795.94465057103</t>
+          <t>-50191.19890369411</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-42925.28873913951</t>
+          <t>-46865.09729587106</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>377978</v>
+        <v>241508</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>147.04</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>52.71</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>693.0</t>
+          <t>667.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>456.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-7.7</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-18.05</t>
+          <t>-22.67</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-21.06</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>283</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3214,57 +3214,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-6.42</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>702.8</t>
+          <t>686.2</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>740.6</t>
+          <t>733.3</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>771.72</t>
+          <t>772.84</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>670.89</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-56.83</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-24.23</t>
+          <t>-28.51</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-18.06</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-117.18</t>
+          <t>-120.08</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>410388.9211409396</t>
+          <t>409924.9364548496</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>310495.0</t>
+          <t>377978.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>321361.4</t>
+          <t>309322.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>392151.7</t>
+          <t>400021.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>673300.18</t>
+          <t>677723.46</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-70790</t>
+          <t>-90699</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-52226.97299810403</t>
+          <t>-50795.94465057103</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-50385.73048883944</t>
+          <t>-42925.28873913951</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>310495</v>
+        <v>377978</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>156.60</t>
+          <t>147.04</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>52.71</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>699.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>444.0</t>
+          <t>456.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-11.4</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-18.05</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-18.35</t>
+          <t>-21.06</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>283</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3650,57 +3650,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>15.03</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>711.8</t>
+          <t>702.8</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>747.5</t>
+          <t>740.6</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>770.14</t>
+          <t>771.72</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>668.28</t>
+          <t>670.89</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-58.22</t>
+          <t>-56.83</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-20.97</t>
+          <t>-24.23</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-15.45</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-114.74</t>
+          <t>-117.18</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>410388.9211409396</t>
+          <t>409924.9364548496</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>306608.0</t>
+          <t>310495.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>359349.6</t>
+          <t>321361.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>389319.8</t>
+          <t>392151.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>672018.02</t>
+          <t>673300.18</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-29970</t>
+          <t>-70790</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-52561.74436342486</t>
+          <t>-52226.97299810403</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-52013.69261380937</t>
+          <t>-50385.73048883944</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>306608</v>
+        <v>310495</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>165.39</t>
+          <t>156.60</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>18.28</t>
+          <t>17.68</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>52.71</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3893,17 +3893,17 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>679.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>444.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-13.48</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-16.82</t>
+          <t>-18.35</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>283</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4081,62 +4081,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>15.24</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>722.4</t>
+          <t>711.8</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>754.55</t>
+          <t>747.5</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>768.06</t>
+          <t>770.14</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>665.62</t>
+          <t>668.28</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-66.42</t>
+          <t>-58.22</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-18.85</t>
+          <t>-20.97</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-112.59</t>
+          <t>-114.74</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>410388.9211409396</t>
+          <t>409924.9364548496</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>228169.0</t>
+          <t>306608.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>354425.0</t>
+          <t>359349.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>390521.3</t>
+          <t>389319.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>675976.46</t>
+          <t>672018.02</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-36096</t>
+          <t>-29970</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-52661.39013608223</t>
+          <t>-52561.74436342486</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-52065.25662755885</t>
+          <t>-52013.69261380937</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>228169</v>
+        <v>306608</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>170.36</t>
+          <t>165.39</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>52.71</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>699.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>679.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>448.0</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-14.45</t>
+          <t>-10.47</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-16.12</t>
+          <t>-16.82</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>283</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4522,57 +4522,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>722.4</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>760.7</t>
+          <t>754.55</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>766.1</t>
+          <t>768.06</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>662.74</t>
+          <t>665.62</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-81.98</t>
+          <t>-66.42</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-17.19</t>
+          <t>-18.85</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-110.50</t>
+          <t>-112.59</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>410388.9211409396</t>
+          <t>409924.9364548496</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>323363.0</t>
+          <t>228169.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>471049.8</t>
+          <t>354425.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>445989.1</t>
+          <t>390521.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>679269.88</t>
+          <t>675976.46</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>25060</t>
+          <t>-36096</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-52769.77804672284</t>
+          <t>-52661.39013608223</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-41875.26748193102</t>
+          <t>-52065.25662755885</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>323363</v>
+        <v>228169</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>172.66</t>
+          <t>170.36</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,22 +4695,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.62</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>52.71</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>710.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>606.0</t>
+          <t>448.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>713.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-17.01</t>
+          <t>-11.41</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-14.24</t>
+          <t>-16.12</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>283</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>15.60</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>737.8</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>765.9</t>
+          <t>760.7</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>763.84</t>
+          <t>766.1</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>659.24</t>
+          <t>662.74</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-105.47</t>
+          <t>-81.98</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-15.43</t>
+          <t>-17.19</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-7.51</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-108.35</t>
+          <t>-110.50</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>410388.9211409396</t>
+          <t>409924.9364548496</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>438172.0</t>
+          <t>323363.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>490720.6</t>
+          <t>471049.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>467960.7</t>
+          <t>445989.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>683118.66</t>
+          <t>679269.88</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>22759</t>
+          <t>25060</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-54750.59814941225</t>
+          <t>-52769.77804672284</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-36021.95200667955</t>
+          <t>-41875.26748193102</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>438172</v>
+        <v>323363</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>178.78</t>
+          <t>172.66</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.78</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>52.71</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>748.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>710.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>713.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>606.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-14.93</t>
+          <t>-13.91</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-14.24</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>18.93</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>283</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.07</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>52.47</t>
+          <t>27.16</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>735.2</t>
+          <t>737.8</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>771.95</t>
+          <t>765.9</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>761.14</t>
+          <t>763.84</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>655.4</t>
+          <t>659.24</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-163.86</t>
+          <t>-105.47</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-14.59</t>
+          <t>-15.43</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-7.51</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-106.15</t>
+          <t>-108.35</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>410388.9211409396</t>
+          <t>409924.9364548496</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>500436.0</t>
+          <t>438172.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>462942.0</t>
+          <t>490720.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>451797.8</t>
+          <t>467960.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>687666.36</t>
+          <t>683118.66</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>22759</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-58155.80653900002</t>
+          <t>-54750.59814941225</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-38674.53875608178</t>
+          <t>-36021.95200667955</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>500436</v>
+        <v>438172</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>173.80</t>
+          <t>178.78</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>52.71</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>751.0</t>
+          <t>748.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3925.483</t>
+          <t>2724.529</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-20.19</t>
+          <t>-25.65</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-16.97</t>
+          <t>-15.60</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-10.16</t>
+          <t>-9.63</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>184.8</t>
+          <t>184.3</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>205.7</t>
+          <t>203.95</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>212.36</t>
+          <t>211.72</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>211.81</t>
+          <t>211.42</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-53.22</t>
+          <t>-40.39</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-8.79</t>
+          <t>-8.96</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-130.59</t>
+          <t>-134.02</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1327643364.675753</t>
+          <t>1326810091.560172</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>714330282.0</t>
+          <t>497345820.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>583542929.0</t>
+          <t>538397244.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>731190758.4</t>
+          <t>724156183.6</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>788163169.8</t>
+          <t>755881026.66</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-147647829</t>
+          <t>-185758939</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-6859780.775898567</t>
+          <t>-9219930.34208828</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-12705943.10512841</t>
+          <t>-22200752.9561317</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>714330282</v>
+        <v>497345820</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-17.35</t>
+          <t>-15.98</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>45.94</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>64036</t>
+          <t>65098</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>182.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>180.5</t>
+          <t>181.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2375.624</t>
+          <t>3925.483</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>181.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-13.38</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-15.83</t>
+          <t>-16.97</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>7.37</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,12 +6246,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6266,57 +6266,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-9.85</t>
+          <t>-10.16</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>187.2</t>
+          <t>184.8</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>207.65</t>
+          <t>205.7</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>213.15</t>
+          <t>212.36</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>212.2</t>
+          <t>211.81</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-63.70</t>
+          <t>-53.22</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-8.14</t>
+          <t>-8.79</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-126.52</t>
+          <t>-130.59</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1327643364.675753</t>
+          <t>1326810091.560172</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>436343333.0</t>
+          <t>714330282.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>624341783.8</t>
+          <t>583542929.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>720759640.4</t>
+          <t>731190758.4</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>863704924.02</t>
+          <t>788163169.8</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-96417856</t>
+          <t>-147647829</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-5796842.170584051</t>
+          <t>-6859780.775898567</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-21936480.56422627</t>
+          <t>-12705943.10512841</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>436343333</v>
+        <v>714330282</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-16.21</t>
+          <t>-17.35</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,22 +6439,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>45.94</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>64036</t>
+          <t>65098</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>184.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>180.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>181.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3128.645</t>
+          <t>2375.624</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>186.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-13.38</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-14.45</t>
+          <t>-15.83</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>7.37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,12 +6682,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6702,57 +6702,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-9.85</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>190.2</t>
+          <t>187.2</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>209.58</t>
+          <t>207.65</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>213.6</t>
+          <t>213.15</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>212.58</t>
+          <t>212.2</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-78.19</t>
+          <t>-63.70</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-8.14</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-122.29</t>
+          <t>-126.52</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1327643364.675753</t>
+          <t>1326810091.560172</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>587620146.0</t>
+          <t>436343333.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>674218506.6</t>
+          <t>624341783.8</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>715379759.4</t>
+          <t>720759640.4</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>864477556.2</t>
+          <t>863704924.02</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-41161252</t>
+          <t>-96417856</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-2862362.462649101</t>
+          <t>-5796842.170584051</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-4555200.949929357</t>
+          <t>-21936480.56422627</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>587620146</v>
+        <v>436343333</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-14.84</t>
+          <t>-16.21</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>45.94</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>64036</t>
+          <t>65098</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>189.5</t>
+          <t>184.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>191.5</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>186.5</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>186.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2437.772</t>
+          <t>3128.645</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,12 +7118,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7138,57 +7138,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-8.70</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>192.9</t>
+          <t>190.2</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>211.28</t>
+          <t>209.58</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>214.03</t>
+          <t>213.6</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>212.96</t>
+          <t>212.58</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-101.13</t>
+          <t>-78.19</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-117.94</t>
+          <t>-122.29</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1327643364.675753</t>
+          <t>1326810091.560172</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>456346640.0</t>
+          <t>587620146.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>757230803.0</t>
+          <t>674218506.6</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>678685106.5</t>
+          <t>715379759.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>856936697.08</t>
+          <t>864477556.2</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>78545696</t>
+          <t>-41161252</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-2554573.646779964</t>
+          <t>-2862362.462649101</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>4229654.282992125</t>
+          <t>-4555200.949929357</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>456346640</v>
+        <v>587620146</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7311,12 +7311,12 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>45.94</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>64036</t>
+          <t>65098</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,17 +7376,17 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
+          <t>189.5</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
+          <t>191.5</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
           <t>186.5</t>
-        </is>
-      </c>
-      <c r="CE16" t="inlineStr">
-        <is>
-          <t>190.0</t>
-        </is>
-      </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>185.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3839.598</t>
+          <t>2437.772</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,12 +7554,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7574,57 +7574,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-8.70</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>196.6</t>
+          <t>192.9</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>212.75</t>
+          <t>211.28</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>214.42</t>
+          <t>214.03</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>213.34</t>
+          <t>212.96</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-130.49</t>
+          <t>-101.13</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-113.40</t>
+          <t>-117.94</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1327643364.675753</t>
+          <t>1326810091.560172</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>723074244.0</t>
+          <t>456346640.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>909915123.0</t>
+          <t>757230803.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>674907487.9</t>
+          <t>678685106.5</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>854335140.06</t>
+          <t>856936697.08</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>235007635</t>
+          <t>78545696</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-3788069.634011253</t>
+          <t>-2554573.646779964</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>30693406.89134467</t>
+          <t>4229654.282992125</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>723074244</v>
+        <v>456346640</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>45.94</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>64036</t>
+          <t>65098</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,17 +7812,17 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>191.5</t>
+          <t>190.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4701.928</t>
+          <t>3839.598</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-14.45</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14.59</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8010,57 +8010,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>201.2</t>
+          <t>196.6</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>213.98</t>
+          <t>212.75</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>214.79</t>
+          <t>214.42</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>213.72</t>
+          <t>213.34</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-163.83</t>
+          <t>-130.49</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-109.03</t>
+          <t>-113.40</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1327643364.675753</t>
+          <t>1326810091.560172</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>918324556.0</t>
+          <t>723074244.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>878838587.8</t>
+          <t>909915123.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>691621829.4</t>
+          <t>674907487.9</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>845368183.24</t>
+          <t>854335140.06</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>187216758</t>
+          <t>235007635</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-10057429.00225778</t>
+          <t>-3788069.634011253</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>38824617.085729</t>
+          <t>30693406.89134467</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>918324556</v>
+        <v>723074244</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-11.87</t>
+          <t>-14.84</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>45.94</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>64036</t>
+          <t>65098</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>191.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3457.008</t>
+          <t>4701.928</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-9.67</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>25.67</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-8.94</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10.72</t>
+          <t>14.59</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8446,57 +8446,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>204.6</t>
+          <t>201.2</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>214.72</t>
+          <t>213.98</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>215.02</t>
+          <t>214.79</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>213.92</t>
+          <t>213.72</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-237.34</t>
+          <t>-163.83</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-105.33</t>
+          <t>-109.03</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1327643364.675753</t>
+          <t>1326810091.560172</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>685726947.0</t>
+          <t>918324556.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>817177497.0</t>
+          <t>878838587.8</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>650263422.9</t>
+          <t>691621829.4</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>838743112.42</t>
+          <t>845368183.24</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>166914074</t>
+          <t>187216758</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-18945073.74552811</t>
+          <t>-10057429.00225778</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>28134361.89607322</t>
+          <t>38824617.085729</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>685726947</v>
+        <v>918324556</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-11.87</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>45.94</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>64036</t>
+          <t>65098</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>195.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5006.119</t>
+          <t>3457.008</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-10.5</t>
+          <t>-7.88</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>25.67</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-8.94</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>10.72</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8882,57 +8882,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>207.7</t>
+          <t>204.6</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>215.3</t>
+          <t>214.72</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>215.19</t>
+          <t>215.02</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>214.13</t>
+          <t>213.92</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-511.52</t>
+          <t>-237.34</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-102.17</t>
+          <t>-105.33</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1327643364.675753</t>
+          <t>1326810091.560172</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>1002681628.0</t>
+          <t>685726947.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>756541012.2</t>
+          <t>817177497.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>657490336.6</t>
+          <t>650263422.9</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>837159531.8</t>
+          <t>838743112.42</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>99050675</t>
+          <t>166914074</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-27504971.13491017</t>
+          <t>-18945073.74552811</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>36778942.52170527</t>
+          <t>28134361.89607322</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>1002681628</v>
+        <v>685726947</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-8.68</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,22 +9055,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>45.94</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>64036</t>
+          <t>65098</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
+          <t>195.0</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
           <t>201.0</t>
         </is>
       </c>
-      <c r="CE20" t="inlineStr">
-        <is>
-          <t>205.0</t>
-        </is>
-      </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5932.964</t>
+          <t>5006.119</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-8.7</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>15.06</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-5.96</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18.40</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,12 +9298,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9318,57 +9318,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>211.3</t>
+          <t>207.7</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>215.75</t>
+          <t>215.3</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>215.46</t>
+          <t>215.19</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>214.3</t>
+          <t>214.13</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-1398.14</t>
+          <t>-511.52</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-99.40</t>
+          <t>-102.17</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1327643364.675753</t>
+          <t>1326810091.560172</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>1219768240.0</t>
+          <t>1002681628.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>600139410.0</t>
+          <t>756541012.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>623193432.6</t>
+          <t>657490336.6</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>825475916.8</t>
+          <t>837159531.8</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-23054022</t>
+          <t>99050675</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-39192955.43611298</t>
+          <t>-27504971.13491017</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>13855379.64683306</t>
+          <t>36778942.52170527</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>1219768240</v>
+        <v>1002681628</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-8.68</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>45.94</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>64036</t>
+          <t>65098</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>196.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2678.776</t>
+          <t>5932.964</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-15.75</t>
+          <t>-11.41</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-18.01</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>-5.96</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>18.40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,12 +9734,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9754,57 +9754,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>213.8</t>
+          <t>211.3</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>215.92</t>
+          <t>215.75</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>215.67</t>
+          <t>215.46</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>214.41</t>
+          <t>214.3</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-230.30</t>
+          <t>-1398.14</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-97.28</t>
+          <t>-99.40</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1327643364.675753</t>
+          <t>1326810091.560172</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>567691568.0</t>
+          <t>1219768240.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>439899852.8</t>
+          <t>600139410.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>536558115.5</t>
+          <t>623193432.6</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>818287549.92</t>
+          <t>825475916.8</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-96658262</t>
+          <t>-23054022</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-48838107.26937589</t>
+          <t>-39192955.43611298</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-42646682.16179979</t>
+          <t>13855379.64683306</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>567691568</v>
+        <v>1219768240</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>45.94</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>64036</t>
+          <t>65098</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>209.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2889.254</t>
+          <t>2678.776</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>209.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-16.02</t>
+          <t>-13.86</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-18.01</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,12 +10170,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10185,62 +10185,62 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>215.3</t>
+          <t>213.8</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>216.22</t>
+          <t>215.92</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>215.78</t>
+          <t>215.67</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>214.37</t>
+          <t>214.41</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-110.18</t>
+          <t>-230.30</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-95.72</t>
+          <t>-97.28</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1327643364.675753</t>
+          <t>1326810091.560172</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>610019102.0</t>
+          <t>567691568.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>504405071.0</t>
+          <t>439899852.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>521300497.5</t>
+          <t>536558115.5</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>817903324.56</t>
+          <t>818287549.92</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-16895426</t>
+          <t>-96658262</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-49963820.92529882</t>
+          <t>-48838107.26937589</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-51975459.81121111</t>
+          <t>-42646682.16179979</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>610019102</v>
+        <v>567691568</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-4.11</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>45.94</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>64036</t>
+          <t>65098</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>217.0</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>209.0</t>
+          <t>209.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>209.5</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/工業型機器人.xlsx
+++ b/Result/checksun_type/工業型機器人.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>283.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-18.38</t>
+          <t>-22.82</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,22 +1014,22 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>149</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>30.93</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -1039,17 +1039,17 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-10.13</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-9.11</t>
+          <t>-9.86</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>701.25</t>
+          <t>694.75</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>771.56</t>
+          <t>770.74</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>684.56</t>
+          <t>687.31</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-25.78</t>
+          <t>-17.45</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-39.28</t>
+          <t>-38.35</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-31.23</t>
+          <t>-32.65</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-134.72</t>
+          <t>-136.30</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>409924.9364548496</t>
+          <t>409037.0750000001</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>213249.4</t>
+          <t>184090.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>261286.0</t>
+          <t>238520.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>631907.8</t>
+          <t>625496.02</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-48036</t>
+          <t>-54430</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-50682.39427208085</t>
+          <t>-52024.66968847315</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-54134.00295314955</t>
+          <t>-59407.18447863078</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>181105</v>
+        <v>95711</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1272,17 +1272,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>629.0</t>
+          <t>636.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>283.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-18.38</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-26.71</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>149</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>12.62</t>
+          <t>30.93</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-10.13</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-9.11</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>13.29</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>631.4</t>
+          <t>630.2</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>701.25</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>772.34</t>
+          <t>771.56</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>681.75</t>
+          <t>684.56</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-36.56</t>
+          <t>-25.78</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-39.90</t>
+          <t>-39.28</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-29.22</t>
+          <t>-31.23</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-132.48</t>
+          <t>-134.72</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>409924.9364548496</t>
+          <t>409037.0750000001</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>135802.0</t>
+          <t>181105.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>252624.0</t>
+          <t>213249.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>286992.7</t>
+          <t>261286.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>639483.2</t>
+          <t>631907.8</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-34368</t>
+          <t>-48036</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-50054.82905734108</t>
+          <t>-50682.39427208085</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-53816.8863827067</t>
+          <t>-54134.00295314955</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>135802</v>
+        <v>181105</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>138.24</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,17 +1643,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>16.41</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>654.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>629.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>428.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-11.10</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-28.24</t>
+          <t>-26.71</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>149</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.62</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-10.02</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-7.9</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>13.29</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>641.0</t>
+          <t>631.4</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>712.35</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>773.42</t>
+          <t>772.34</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>679.24</t>
+          <t>681.75</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-44.55</t>
+          <t>-36.56</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-38.37</t>
+          <t>-39.90</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-26.55</t>
+          <t>-29.22</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-129.51</t>
+          <t>-132.48</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>409924.9364548496</t>
+          <t>409037.0750000001</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>262274.0</t>
+          <t>135802.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>287562.6</t>
+          <t>252624.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>323456.1</t>
+          <t>286992.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>664782.5</t>
+          <t>639483.2</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-35893</t>
+          <t>-34368</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-49370.81863454734</t>
+          <t>-50054.82905734108</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-46587.93819697743</t>
+          <t>-53816.8863827067</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>262274</v>
+        <v>135802</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>133.27</t>
+          <t>138.24</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,17 +2079,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.41</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>624.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>630.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>600.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>377.0</t>
+          <t>428.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-11.10</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-28.24</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>149</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2342,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-10.02</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-7.9</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>657.8</t>
+          <t>641.0</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>718.95</t>
+          <t>712.35</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>774.36</t>
+          <t>773.42</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>677.44</t>
+          <t>679.24</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-46.43</t>
+          <t>-44.55</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-34.54</t>
+          <t>-38.37</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-23.59</t>
+          <t>-26.55</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-126.22</t>
+          <t>-129.51</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>409924.9364548496</t>
+          <t>409037.0750000001</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>245558.0</t>
+          <t>262274.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>296429.4</t>
+          <t>287562.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>325427.2</t>
+          <t>323456.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>674644.66</t>
+          <t>664782.5</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-28997</t>
+          <t>-35893</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-49876.79689592369</t>
+          <t>-49370.81863454734</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-48147.58585318638</t>
+          <t>-46587.93819697743</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>245558</v>
+        <v>262274</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>143.98</t>
+          <t>133.27</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,17 +2515,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>624.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>672.0</t>
+          <t>630.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>600.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>371.0</t>
+          <t>377.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-23.31</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>149</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2778,57 +2778,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>671.6</t>
+          <t>657.8</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>725.65</t>
+          <t>718.95</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>773.56</t>
+          <t>774.36</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>675.4</t>
+          <t>677.44</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-53.49</t>
+          <t>-46.43</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-32.01</t>
+          <t>-34.54</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-20.85</t>
+          <t>-23.59</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-123.18</t>
+          <t>-126.22</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>409924.9364548496</t>
+          <t>409037.0750000001</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>241508.0</t>
+          <t>245558.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>292951.6</t>
+          <t>296429.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>382000.7</t>
+          <t>325427.2</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>675976.12</t>
+          <t>674644.66</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-89049</t>
+          <t>-28997</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-50191.19890369411</t>
+          <t>-49876.79689592369</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-46865.09729587106</t>
+          <t>-48147.58585318638</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>241508</v>
+        <v>245558</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>667.0</t>
+          <t>672.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>371.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-22.67</t>
+          <t>-23.31</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>149</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3214,57 +3214,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-6.42</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>686.2</t>
+          <t>671.6</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>733.3</t>
+          <t>725.65</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>772.84</t>
+          <t>773.56</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>675.4</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-57.81</t>
+          <t>-53.49</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-28.51</t>
+          <t>-32.01</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-18.06</t>
+          <t>-20.85</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-120.08</t>
+          <t>-123.18</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>409924.9364548496</t>
+          <t>409037.0750000001</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>377978.0</t>
+          <t>241508.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>309322.6</t>
+          <t>292951.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>400021.6</t>
+          <t>382000.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>677723.46</t>
+          <t>675976.12</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-90699</t>
+          <t>-89049</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-50795.94465057103</t>
+          <t>-50191.19890369411</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-42925.28873913951</t>
+          <t>-46865.09729587106</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>377978</v>
+        <v>241508</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>147.04</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>693.0</t>
+          <t>667.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>456.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-18.05</t>
+          <t>-22.67</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-21.06</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>149</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3650,57 +3650,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-6.42</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>702.8</t>
+          <t>686.2</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>740.6</t>
+          <t>733.3</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>771.72</t>
+          <t>772.84</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>670.89</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-56.83</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-24.23</t>
+          <t>-28.51</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-18.06</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-117.18</t>
+          <t>-120.08</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>409924.9364548496</t>
+          <t>409037.0750000001</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>310495.0</t>
+          <t>377978.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>321361.4</t>
+          <t>309322.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>392151.7</t>
+          <t>400021.6</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>673300.18</t>
+          <t>677723.46</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-70790</t>
+          <t>-90699</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-52226.97299810403</t>
+          <t>-50795.94465057103</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-50385.73048883944</t>
+          <t>-42925.28873913951</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>310495</v>
+        <v>377978</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>156.60</t>
+          <t>147.04</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>699.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>444.0</t>
+          <t>456.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-18.05</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-18.35</t>
+          <t>-21.06</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>149</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4086,57 +4086,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>15.03</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>711.8</t>
+          <t>702.8</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>747.5</t>
+          <t>740.6</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>770.14</t>
+          <t>771.72</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>668.28</t>
+          <t>670.89</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-58.22</t>
+          <t>-56.83</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-20.97</t>
+          <t>-24.23</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-15.45</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-114.74</t>
+          <t>-117.18</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>409924.9364548496</t>
+          <t>409037.0750000001</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>306608.0</t>
+          <t>310495.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>359349.6</t>
+          <t>321361.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>389319.8</t>
+          <t>392151.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>672018.02</t>
+          <t>673300.18</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-29970</t>
+          <t>-70790</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-52561.74436342486</t>
+          <t>-52226.97299810403</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-52013.69261380937</t>
+          <t>-50385.73048883944</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>306608</v>
+        <v>310495</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>165.39</t>
+          <t>156.60</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>18.28</t>
+          <t>17.68</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4329,17 +4329,17 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>679.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>444.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-10.47</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-16.82</t>
+          <t>-18.35</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>149</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4517,62 +4517,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>15.24</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>722.4</t>
+          <t>711.8</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>754.55</t>
+          <t>747.5</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>768.06</t>
+          <t>770.14</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>665.62</t>
+          <t>668.28</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-66.42</t>
+          <t>-58.22</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-18.85</t>
+          <t>-20.97</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-112.59</t>
+          <t>-114.74</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>409924.9364548496</t>
+          <t>409037.0750000001</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>228169.0</t>
+          <t>306608.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>354425.0</t>
+          <t>359349.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>390521.3</t>
+          <t>389319.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>675976.46</t>
+          <t>672018.02</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-36096</t>
+          <t>-29970</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-52661.39013608223</t>
+          <t>-52561.74436342486</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-52065.25662755885</t>
+          <t>-52013.69261380937</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>228169</v>
+        <v>306608</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>170.36</t>
+          <t>165.39</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,17 +4695,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>699.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>679.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>448.0</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-11.41</t>
+          <t>-10.47</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-16.12</t>
+          <t>-16.82</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>149</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4958,57 +4958,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>722.4</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>760.7</t>
+          <t>754.55</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>766.1</t>
+          <t>768.06</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>662.74</t>
+          <t>665.62</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-81.98</t>
+          <t>-66.42</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-17.19</t>
+          <t>-18.85</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-110.50</t>
+          <t>-112.59</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>409924.9364548496</t>
+          <t>409037.0750000001</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>323363.0</t>
+          <t>228169.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>471049.8</t>
+          <t>354425.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>445989.1</t>
+          <t>390521.3</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>679269.88</t>
+          <t>675976.46</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>25060</t>
+          <t>-36096</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-52769.77804672284</t>
+          <t>-52661.39013608223</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-41875.26748193102</t>
+          <t>-52065.25662755885</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>323363</v>
+        <v>228169</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>172.66</t>
+          <t>170.36</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.62</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>710.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>606.0</t>
+          <t>448.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>713.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-13.91</t>
+          <t>-11.41</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-14.24</t>
+          <t>-16.12</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>149</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>15.60</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>737.8</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>765.9</t>
+          <t>760.7</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>763.84</t>
+          <t>766.1</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>659.24</t>
+          <t>662.74</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-105.47</t>
+          <t>-81.98</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-15.43</t>
+          <t>-17.19</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-7.51</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-108.35</t>
+          <t>-110.50</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>409924.9364548496</t>
+          <t>409037.0750000001</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>438172.0</t>
+          <t>323363.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>490720.6</t>
+          <t>471049.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>467960.7</t>
+          <t>445989.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>683118.66</t>
+          <t>679269.88</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>22759</t>
+          <t>25060</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-54750.59814941225</t>
+          <t>-52769.77804672284</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-36021.95200667955</t>
+          <t>-41875.26748193102</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>438172</v>
+        <v>323363</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>178.78</t>
+          <t>172.66</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.78</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>748.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>710.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>713.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2724.529</t>
+          <t>2044.942</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-25.65</t>
+          <t>-18.26</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-15.60</t>
+          <t>-13.76</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2725</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-9.63</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>184.3</t>
+          <t>184.6</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>203.95</t>
+          <t>202.38</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>211.72</t>
+          <t>211.26</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>211.42</t>
+          <t>211.12</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-40.39</t>
+          <t>-26.76</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-8.96</t>
+          <t>-8.67</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-134.02</t>
+          <t>-136.46</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1326810091.560172</t>
+          <t>1325730314.156652</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>497345820.0</t>
+          <t>381363791.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>538397244.2</t>
+          <t>523400674.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>724156183.6</t>
+          <t>640315738.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>755881026.66</t>
+          <t>746361854.7</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-185758939</t>
+          <t>-116915064</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-9219930.34208828</t>
+          <t>-13492364.62837173</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-22200752.9561317</t>
+          <t>-36990753.20293069</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>497345820</v>
+        <v>381363791</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-15.98</t>
+          <t>-14.16</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>47.72</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>65098</t>
+          <t>66513</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>182.5</t>
+          <t>184.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>184.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3925.483</t>
+          <t>2724.529</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-20.19</t>
+          <t>-25.65</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-16.97</t>
+          <t>-15.60</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2725</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-10.16</t>
+          <t>-9.63</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>184.8</t>
+          <t>184.3</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>205.7</t>
+          <t>203.95</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>212.36</t>
+          <t>211.72</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>211.81</t>
+          <t>211.42</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-53.22</t>
+          <t>-40.39</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-8.79</t>
+          <t>-8.96</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-130.59</t>
+          <t>-134.02</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1326810091.560172</t>
+          <t>1325730314.156652</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>714330282.0</t>
+          <t>497345820.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>583542929.0</t>
+          <t>538397244.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>731190758.4</t>
+          <t>724156183.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>788163169.8</t>
+          <t>755881026.66</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-147647829</t>
+          <t>-185758939</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-6859780.775898567</t>
+          <t>-9219930.34208828</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-12705943.10512841</t>
+          <t>-22200752.9561317</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>714330282</v>
+        <v>497345820</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-17.35</t>
+          <t>-15.98</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6439,22 +6439,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>47.72</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>65098</t>
+          <t>66513</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>182.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>180.5</t>
+          <t>181.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2375.624</t>
+          <t>3925.483</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>181.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-13.38</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-15.83</t>
+          <t>-16.97</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>7.37</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,12 +6682,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2725</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6702,57 +6702,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-9.85</t>
+          <t>-10.16</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>187.2</t>
+          <t>184.8</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>207.65</t>
+          <t>205.7</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>213.15</t>
+          <t>212.36</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>212.2</t>
+          <t>211.81</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-63.70</t>
+          <t>-53.22</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-8.14</t>
+          <t>-8.79</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-126.52</t>
+          <t>-130.59</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1326810091.560172</t>
+          <t>1325730314.156652</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>436343333.0</t>
+          <t>714330282.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>624341783.8</t>
+          <t>583542929.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>720759640.4</t>
+          <t>731190758.4</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>863704924.02</t>
+          <t>788163169.8</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-96417856</t>
+          <t>-147647829</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-5796842.170584051</t>
+          <t>-6859780.775898567</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-21936480.56422627</t>
+          <t>-12705943.10512841</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>436343333</v>
+        <v>714330282</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-16.21</t>
+          <t>-17.35</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>47.72</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>65098</t>
+          <t>66513</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>184.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>180.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>181.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3128.645</t>
+          <t>2375.624</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>186.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-13.38</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-14.45</t>
+          <t>-15.83</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>7.37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,12 +7118,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2725</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7138,57 +7138,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-9.85</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>190.2</t>
+          <t>187.2</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>209.58</t>
+          <t>207.65</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>213.6</t>
+          <t>213.15</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>212.58</t>
+          <t>212.2</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-78.19</t>
+          <t>-63.70</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-8.14</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-122.29</t>
+          <t>-126.52</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1326810091.560172</t>
+          <t>1325730314.156652</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>587620146.0</t>
+          <t>436343333.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>674218506.6</t>
+          <t>624341783.8</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>715379759.4</t>
+          <t>720759640.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>864477556.2</t>
+          <t>863704924.02</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-41161252</t>
+          <t>-96417856</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-2862362.462649101</t>
+          <t>-5796842.170584051</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-4555200.949929357</t>
+          <t>-21936480.56422627</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>587620146</v>
+        <v>436343333</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-14.84</t>
+          <t>-16.21</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>47.72</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>65098</t>
+          <t>66513</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>189.5</t>
+          <t>184.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>191.5</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>186.5</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>186.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2437.772</t>
+          <t>3128.645</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,12 +7554,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2725</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7574,57 +7574,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-8.70</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>192.9</t>
+          <t>190.2</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>211.28</t>
+          <t>209.58</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>214.03</t>
+          <t>213.6</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>212.96</t>
+          <t>212.58</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-101.13</t>
+          <t>-78.19</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-117.94</t>
+          <t>-122.29</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1326810091.560172</t>
+          <t>1325730314.156652</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>456346640.0</t>
+          <t>587620146.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>757230803.0</t>
+          <t>674218506.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>678685106.5</t>
+          <t>715379759.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>856936697.08</t>
+          <t>864477556.2</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>78545696</t>
+          <t>-41161252</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-2554573.646779964</t>
+          <t>-2862362.462649101</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>4229654.282992125</t>
+          <t>-4555200.949929357</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>456346640</v>
+        <v>587620146</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>47.72</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>65098</t>
+          <t>66513</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,17 +7812,17 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
+          <t>189.5</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
+          <t>191.5</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
           <t>186.5</t>
-        </is>
-      </c>
-      <c r="CE17" t="inlineStr">
-        <is>
-          <t>190.0</t>
-        </is>
-      </c>
-      <c r="CF17" t="inlineStr">
-        <is>
-          <t>185.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3839.598</t>
+          <t>2437.772</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2725</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8010,57 +8010,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-8.70</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>196.6</t>
+          <t>192.9</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>212.75</t>
+          <t>211.28</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>214.42</t>
+          <t>214.03</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>213.34</t>
+          <t>212.96</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-130.49</t>
+          <t>-101.13</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-113.40</t>
+          <t>-117.94</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1326810091.560172</t>
+          <t>1325730314.156652</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>723074244.0</t>
+          <t>456346640.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>909915123.0</t>
+          <t>757230803.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>674907487.9</t>
+          <t>678685106.5</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>854335140.06</t>
+          <t>856936697.08</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>235007635</t>
+          <t>78545696</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-3788069.634011253</t>
+          <t>-2554573.646779964</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>30693406.89134467</t>
+          <t>4229654.282992125</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>723074244</v>
+        <v>456346640</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>47.72</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>65098</t>
+          <t>66513</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,17 +8248,17 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>191.5</t>
+          <t>190.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4701.928</t>
+          <t>3839.598</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-14.45</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14.59</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2725</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8446,57 +8446,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>201.2</t>
+          <t>196.6</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>213.98</t>
+          <t>212.75</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>214.79</t>
+          <t>214.42</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>213.72</t>
+          <t>213.34</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-163.83</t>
+          <t>-130.49</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-109.03</t>
+          <t>-113.40</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1326810091.560172</t>
+          <t>1325730314.156652</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>918324556.0</t>
+          <t>723074244.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>878838587.8</t>
+          <t>909915123.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>691621829.4</t>
+          <t>674907487.9</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>845368183.24</t>
+          <t>854335140.06</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>187216758</t>
+          <t>235007635</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-10057429.00225778</t>
+          <t>-3788069.634011253</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>38824617.085729</t>
+          <t>30693406.89134467</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>918324556</v>
+        <v>723074244</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-11.87</t>
+          <t>-14.84</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>47.72</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>65098</t>
+          <t>66513</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>191.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3457.008</t>
+          <t>4701.928</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-7.88</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>25.67</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-8.94</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10.72</t>
+          <t>14.59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2725</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8882,57 +8882,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>204.6</t>
+          <t>201.2</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>214.72</t>
+          <t>213.98</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>215.02</t>
+          <t>214.79</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>213.92</t>
+          <t>213.72</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-237.34</t>
+          <t>-163.83</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-105.33</t>
+          <t>-109.03</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1326810091.560172</t>
+          <t>1325730314.156652</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>685726947.0</t>
+          <t>918324556.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>817177497.0</t>
+          <t>878838587.8</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>650263422.9</t>
+          <t>691621829.4</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>838743112.42</t>
+          <t>845368183.24</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>166914074</t>
+          <t>187216758</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-18945073.74552811</t>
+          <t>-10057429.00225778</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>28134361.89607322</t>
+          <t>38824617.085729</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>685726947</v>
+        <v>918324556</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-11.87</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>47.72</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>65098</t>
+          <t>66513</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>195.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5006.119</t>
+          <t>3457.008</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-8.7</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>25.67</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-8.94</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>10.72</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,12 +9298,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2725</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9318,57 +9318,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>207.7</t>
+          <t>204.6</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>215.3</t>
+          <t>214.72</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>215.19</t>
+          <t>215.02</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>214.13</t>
+          <t>213.92</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-511.52</t>
+          <t>-237.34</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-102.17</t>
+          <t>-105.33</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1326810091.560172</t>
+          <t>1325730314.156652</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>1002681628.0</t>
+          <t>685726947.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>756541012.2</t>
+          <t>817177497.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>657490336.6</t>
+          <t>650263422.9</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>837159531.8</t>
+          <t>838743112.42</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>99050675</t>
+          <t>166914074</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-27504971.13491017</t>
+          <t>-18945073.74552811</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>36778942.52170527</t>
+          <t>28134361.89607322</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>1002681628</v>
+        <v>685726947</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-8.68</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>47.72</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>65098</t>
+          <t>66513</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
+          <t>195.0</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
+        <is>
           <t>201.0</t>
         </is>
       </c>
-      <c r="CE21" t="inlineStr">
-        <is>
-          <t>205.0</t>
-        </is>
-      </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5932.964</t>
+          <t>5006.119</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-11.41</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>15.06</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-5.96</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18.40</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,12 +9734,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2725</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9754,57 +9754,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>211.3</t>
+          <t>207.7</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>215.75</t>
+          <t>215.3</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>215.46</t>
+          <t>215.19</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>214.3</t>
+          <t>214.13</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-1398.14</t>
+          <t>-511.52</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-99.40</t>
+          <t>-102.17</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1326810091.560172</t>
+          <t>1325730314.156652</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>1219768240.0</t>
+          <t>1002681628.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>600139410.0</t>
+          <t>756541012.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>623193432.6</t>
+          <t>657490336.6</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>825475916.8</t>
+          <t>837159531.8</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-23054022</t>
+          <t>99050675</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-39192955.43611298</t>
+          <t>-27504971.13491017</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>13855379.64683306</t>
+          <t>36778942.52170527</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>1219768240</v>
+        <v>1002681628</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-8.68</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>47.72</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>65098</t>
+          <t>66513</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>196.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2678.776</t>
+          <t>5932.964</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-13.86</t>
+          <t>-9.04</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-18.01</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>-5.96</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>18.40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,12 +10170,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2725</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10190,57 +10190,57 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>213.8</t>
+          <t>211.3</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>215.92</t>
+          <t>215.75</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>215.67</t>
+          <t>215.46</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>214.41</t>
+          <t>214.3</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-230.30</t>
+          <t>-1398.14</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-97.28</t>
+          <t>-99.40</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1326810091.560172</t>
+          <t>1325730314.156652</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>567691568.0</t>
+          <t>1219768240.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>439899852.8</t>
+          <t>600139410.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>536558115.5</t>
+          <t>623193432.6</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>818287549.92</t>
+          <t>825475916.8</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-96658262</t>
+          <t>-23054022</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-48838107.26937589</t>
+          <t>-39192955.43611298</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-42646682.16179979</t>
+          <t>13855379.64683306</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>567691568</v>
+        <v>1219768240</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>47.72</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>65098</t>
+          <t>66513</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>209.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/工業型機器人.xlsx
+++ b/Result/checksun_type/工業型機器人.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>630.2</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>694.75</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>770.74</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>694.75</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>770.74</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>95711.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>184090.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>184090</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>238520.8</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>625496.02</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>625496.02</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-59407.18447863078</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>95711</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>95711.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>630.2</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>701.25</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>771.56</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>701.25</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>771.5599999999999</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>181105.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>213249.4</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>213249.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>261286.0</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>631907.8</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>631907.8</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-54134.00295314955</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>181105</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>181105.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>631.4</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>706.0</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>772.34</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>706</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>772.34</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>135802.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>252624.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>252624</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>286992.7</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>639483.2</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>639483.2</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-53816.8863827067</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>135802</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>135802.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>641.0</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>712.35</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>773.42</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>712.35</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>773.42</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>262274.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>287562.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>287562.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>323456.1</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>664782.5</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>664782.5</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-46587.93819697743</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>262274</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>262274.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>657.8</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>718.95</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>774.36</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>718.95</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>774.36</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>245558.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>296429.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>296429.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>325427.2</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>674644.66</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>674644.66</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-48147.58585318638</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>245558</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>245558.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>671.6</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>725.65</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>773.56</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>725.65</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>773.5599999999999</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>241508.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>292951.6</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>292951.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>382000.7</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>675976.12</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>675976.12</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-46865.09729587106</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>241508</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>241508.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>686.2</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>733.3</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>772.84</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>733.3</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>772.84</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>377978.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>309322.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>309322.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>400021.6</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>677723.46</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>677723.46</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-42925.28873913951</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>377978</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>377978.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>702.8</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>740.6</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>771.72</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>740.6</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>771.72</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>310495.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>321361.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>321361.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>392151.7</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>673300.18</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>673300.1800000001</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-50385.73048883944</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>310495</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>310495.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>711.8</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>747.5</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>770.14</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>747.5</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>770.14</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>306608.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>359349.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>359349.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>389319.8</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>672018.02</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>672018.02</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-52013.69261380937</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>306608</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>306608.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>722.4</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>754.55</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>768.06</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>754.55</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>768.0599999999999</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>228169.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>354425.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>354425</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>390521.3</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>675976.46</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>675976.46</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-52065.25662755885</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>228169</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>228169.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>735.0</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>760.7</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>766.1</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>760.7</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>766.1</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>323363.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>471049.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>471049.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>445989.1</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>679269.88</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>679269.88</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-41875.26748193102</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>323363</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>323363.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>184.6</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>202.38</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>211.26</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>202.38</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>211.26</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>381363791.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>523400674.4</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>523400674.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>640315738.7</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>746361854.7</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>746361854.7</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-36990753.20293069</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>381363791</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>381363791.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>184.3</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>203.95</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>211.72</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>203.95</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>211.72</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>497345820.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>538397244.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>538397244.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>724156183.6</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>755881026.66</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>755881026.66</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-22200752.9561317</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>497345820</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>497345820.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>184.8</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>205.7</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>212.36</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>205.7</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>212.36</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>714330282.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>583542929.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>583542929</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>731190758.4</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>788163169.8</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>788163169.8</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-12705943.10512841</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>714330282</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>714330282.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>187.2</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>207.65</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>213.15</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>207.65</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>213.15</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>436343333.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>624341783.8</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>624341783.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>720759640.4</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>863704924.02</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>863704924.02</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-21936480.56422627</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>436343333</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>436343333.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>190.2</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>209.58</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>213.6</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>209.58</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>213.6</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>587620146.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>674218506.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>674218506.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>715379759.4</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>864477556.2</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>864477556.2</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-4555200.949929357</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>587620146</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>587620146.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>192.9</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>211.28</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>214.03</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>211.28</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>214.03</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>456346640.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>757230803.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>757230803</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>678685106.5</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>856936697.08</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>856936697.08</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>4229654.282992125</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>456346640</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>456346640.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>196.6</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>212.75</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>214.42</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>212.75</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>214.42</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>723074244.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>909915123.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>909915123</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>674907487.9</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>854335140.06</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>854335140.0599999</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>30693406.89134467</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>723074244</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>723074244.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>201.2</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>213.98</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>214.79</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>213.98</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>214.79</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>918324556.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>878838587.8</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>878838587.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>691621829.4</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>845368183.24</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>845368183.24</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>38824617.085729</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>918324556</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>918324556.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>204.6</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>214.72</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>215.02</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>214.72</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>215.02</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>685726947.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>817177497.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>817177497</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>650263422.9</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>838743112.42</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>838743112.42</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>28134361.89607322</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>685726947</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>685726947.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>207.7</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>215.3</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>215.19</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>215.3</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>215.19</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>1002681628.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>756541012.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>756541012.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>657490336.6</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>837159531.8</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>837159531.8</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>36778942.52170527</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>1002681628</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>1002681628.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>211.3</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>215.75</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>215.46</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>215.75</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>215.46</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>1219768240.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>600139410.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>600139410</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>623193432.6</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>825475916.8</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>825475916.8</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>13855379.64683306</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>1219768240</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>1219768240.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>

--- a/Result/checksun_type/工業型機器人.xlsx
+++ b/Result/checksun_type/工業型機器人.xlsx
@@ -883,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-0.31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>247.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>638.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>149.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>640.0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-22.82</t>
+          <t>-27.97</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,42 +1014,42 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>37.51</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-9.86</t>
+          <t>-10.5</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>12.14</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1058,29 +1058,29 @@
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>694.75</v>
+        <v>688.8</v>
       </c>
       <c r="AN2" t="n">
-        <v>770.74</v>
+        <v>769.62</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>687.31</t>
+          <t>690.04</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-17.45</t>
+          <t>-11.17</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-38.35</t>
+          <t>-37.34</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-32.65</t>
+          <t>-33.59</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-136.30</t>
+          <t>-137.34</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>409037.0750000001</t>
+          <t>408472.0116279069</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>184090</v>
+        <v>166838.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>238520.8</t>
+          <t>231634.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>625496.02</v>
+        <v>622148.62</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-54430</t>
+          <t>-64795</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-52024.66968847315</t>
+          <t>-52766.09080324681</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-59407.18447863078</t>
+          <t>-56843.90693450192</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>651.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>658.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>636.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>283.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-18.38</t>
+          <t>-22.82</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,22 +1444,22 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>30.93</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -1469,17 +1469,17 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-10.13</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-9.11</t>
+          <t>-9.86</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1488,29 +1488,29 @@
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>701.25</v>
+        <v>694.75</v>
       </c>
       <c r="AN3" t="n">
-        <v>771.5599999999999</v>
+        <v>770.74</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>684.56</t>
+          <t>687.31</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-25.78</t>
+          <t>-17.45</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-39.28</t>
+          <t>-38.35</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-31.23</t>
+          <t>-32.65</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-134.72</t>
+          <t>-136.30</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>409037.0750000001</t>
+          <t>408472.0116279069</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>213249.4</v>
+        <v>184090</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>261286.0</t>
+          <t>238520.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>631907.8</v>
+        <v>625496.02</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-48036</t>
+          <t>-54430</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-50682.39427208085</t>
+          <t>-52024.66968847315</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-54134.00295314955</t>
+          <t>-59407.18447863078</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,17 +1696,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>629.0</t>
+          <t>636.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>283.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-18.38</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-26.71</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>12.62</t>
+          <t>30.93</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-10.13</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-9.11</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>13.29</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>631.4</t>
+          <t>630.2</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>706</v>
+        <v>701.25</v>
       </c>
       <c r="AN4" t="n">
-        <v>772.34</v>
+        <v>771.5599999999999</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>681.75</t>
+          <t>684.56</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-36.56</t>
+          <t>-25.78</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-39.90</t>
+          <t>-39.28</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-29.22</t>
+          <t>-31.23</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-132.48</t>
+          <t>-134.72</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>409037.0750000001</t>
+          <t>408472.0116279069</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>135802.0</t>
+          <t>181105.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>252624</v>
+        <v>213249.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>286992.7</t>
+          <t>261286.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>639483.2</v>
+        <v>631907.8</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-34368</t>
+          <t>-48036</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-50054.82905734108</t>
+          <t>-50682.39427208085</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-53816.8863827067</t>
+          <t>-54134.00295314955</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>135802.0</t>
+          <t>181105.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>138.24</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>16.41</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>654.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>629.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>428.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-11.10</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-28.24</t>
+          <t>-26.71</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.62</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-10.02</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-7.9</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>13.29</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>641.0</t>
+          <t>631.4</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>712.35</v>
+        <v>706</v>
       </c>
       <c r="AN5" t="n">
-        <v>773.42</v>
+        <v>772.34</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>679.24</t>
+          <t>681.75</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-44.55</t>
+          <t>-36.56</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-38.37</t>
+          <t>-39.90</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-26.55</t>
+          <t>-29.22</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-129.51</t>
+          <t>-132.48</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>409037.0750000001</t>
+          <t>408472.0116279069</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>262274.0</t>
+          <t>135802.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>287562.6</v>
+        <v>252624</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>323456.1</t>
+          <t>286992.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>664782.5</v>
+        <v>639483.2</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-35893</t>
+          <t>-34368</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-49370.81863454734</t>
+          <t>-50054.82905734108</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-46587.93819697743</t>
+          <t>-53816.8863827067</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>262274.0</t>
+          <t>135802.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>133.27</t>
+          <t>138.24</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.41</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>624.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>630.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>600.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>377.0</t>
+          <t>428.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-11.10</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-28.24</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2754,53 +2754,53 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-10.02</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-7.9</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>657.8</t>
+          <t>641.0</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>718.95</v>
+        <v>712.35</v>
       </c>
       <c r="AN6" t="n">
-        <v>774.36</v>
+        <v>773.42</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>677.44</t>
+          <t>679.24</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-46.43</t>
+          <t>-44.55</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-34.54</t>
+          <t>-38.37</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-23.59</t>
+          <t>-26.55</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-126.22</t>
+          <t>-129.51</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>409037.0750000001</t>
+          <t>408472.0116279069</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>245558.0</t>
+          <t>262274.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>296429.4</v>
+        <v>287562.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>325427.2</t>
+          <t>323456.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>674644.66</v>
+        <v>664782.5</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-28997</t>
+          <t>-35893</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-49876.79689592369</t>
+          <t>-49370.81863454734</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-48147.58585318638</t>
+          <t>-46587.93819697743</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>245558.0</t>
+          <t>262274.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>143.98</t>
+          <t>133.27</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>624.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>672.0</t>
+          <t>630.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>600.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>371.0</t>
+          <t>377.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-23.31</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3184,53 +3184,53 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>671.6</t>
+          <t>657.8</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>725.65</v>
+        <v>718.95</v>
       </c>
       <c r="AN7" t="n">
-        <v>773.5599999999999</v>
+        <v>774.36</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>675.4</t>
+          <t>677.44</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-53.49</t>
+          <t>-46.43</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-32.01</t>
+          <t>-34.54</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-20.85</t>
+          <t>-23.59</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-123.18</t>
+          <t>-126.22</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>409037.0750000001</t>
+          <t>408472.0116279069</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>241508.0</t>
+          <t>245558.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>292951.6</v>
+        <v>296429.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>382000.7</t>
+          <t>325427.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>675976.12</v>
+        <v>674644.66</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-89049</t>
+          <t>-28997</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-50191.19890369411</t>
+          <t>-49876.79689592369</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-46865.09729587106</t>
+          <t>-48147.58585318638</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>241508.0</t>
+          <t>245558.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>667.0</t>
+          <t>672.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>371.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-22.67</t>
+          <t>-23.31</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-6.42</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>686.2</t>
+          <t>671.6</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>733.3</v>
+        <v>725.65</v>
       </c>
       <c r="AN8" t="n">
-        <v>772.84</v>
+        <v>773.5599999999999</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>675.4</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-57.81</t>
+          <t>-53.49</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-28.51</t>
+          <t>-32.01</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-18.06</t>
+          <t>-20.85</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-120.08</t>
+          <t>-123.18</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>409037.0750000001</t>
+          <t>408472.0116279069</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>377978.0</t>
+          <t>241508.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>309322.6</v>
+        <v>292951.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>400021.6</t>
+          <t>382000.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>677723.46</v>
+        <v>675976.12</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-90699</t>
+          <t>-89049</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-50795.94465057103</t>
+          <t>-50191.19890369411</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-42925.28873913951</t>
+          <t>-46865.09729587106</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>377978.0</t>
+          <t>241508.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>147.04</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>693.0</t>
+          <t>667.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>456.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-18.05</t>
+          <t>-22.67</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-21.06</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-6.42</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>702.8</t>
+          <t>686.2</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>740.6</v>
+        <v>733.3</v>
       </c>
       <c r="AN9" t="n">
-        <v>771.72</v>
+        <v>772.84</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>670.89</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-56.83</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-24.23</t>
+          <t>-28.51</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-18.06</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-117.18</t>
+          <t>-120.08</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>409037.0750000001</t>
+          <t>408472.0116279069</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>310495.0</t>
+          <t>377978.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>321361.4</v>
+        <v>309322.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>392151.7</t>
+          <t>400021.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>673300.1800000001</v>
+        <v>677723.46</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-70790</t>
+          <t>-90699</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-52226.97299810403</t>
+          <t>-50795.94465057103</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-50385.73048883944</t>
+          <t>-42925.28873913951</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>310495.0</t>
+          <t>377978.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>156.60</t>
+          <t>147.04</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>699.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>444.0</t>
+          <t>456.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-5.17</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-18.05</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-18.35</t>
+          <t>-21.06</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>15.03</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>711.8</t>
+          <t>702.8</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>747.5</v>
+        <v>740.6</v>
       </c>
       <c r="AN10" t="n">
-        <v>770.14</v>
+        <v>771.72</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>668.28</t>
+          <t>670.89</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-58.22</t>
+          <t>-56.83</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-20.97</t>
+          <t>-24.23</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-15.45</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-114.74</t>
+          <t>-117.18</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>409037.0750000001</t>
+          <t>408472.0116279069</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>306608.0</t>
+          <t>310495.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>359349.6</v>
+        <v>321361.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>389319.8</t>
+          <t>392151.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>672018.02</v>
+        <v>673300.1800000001</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-29970</t>
+          <t>-70790</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-52561.74436342486</t>
+          <t>-52226.97299810403</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-52013.69261380937</t>
+          <t>-50385.73048883944</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>306608.0</t>
+          <t>310495.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>165.39</t>
+          <t>156.60</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>18.28</t>
+          <t>17.68</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4711,17 +4711,17 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>679.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>444.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-10.47</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-16.82</t>
+          <t>-18.35</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,58 +4899,58 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>15.24</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>722.4</t>
+          <t>711.8</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>754.55</v>
+        <v>747.5</v>
       </c>
       <c r="AN11" t="n">
-        <v>768.0599999999999</v>
+        <v>770.14</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>665.62</t>
+          <t>668.28</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-66.42</t>
+          <t>-58.22</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-18.85</t>
+          <t>-20.97</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-112.59</t>
+          <t>-114.74</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>409037.0750000001</t>
+          <t>408472.0116279069</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>228169.0</t>
+          <t>306608.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>354425</v>
+        <v>359349.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>390521.3</t>
+          <t>389319.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>675976.46</v>
+        <v>672018.02</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-36096</t>
+          <t>-29970</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-52661.39013608223</t>
+          <t>-52561.74436342486</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-52065.25662755885</t>
+          <t>-52013.69261380937</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>228169.0</t>
+          <t>306608.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>170.36</t>
+          <t>165.39</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>699.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>679.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>448.0</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-11.41</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-16.12</t>
+          <t>-16.82</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>722.4</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>760.7</v>
+        <v>754.55</v>
       </c>
       <c r="AN12" t="n">
-        <v>766.1</v>
+        <v>768.0599999999999</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>662.74</t>
+          <t>665.62</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-81.98</t>
+          <t>-66.42</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-17.19</t>
+          <t>-18.85</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-110.50</t>
+          <t>-112.59</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>409037.0750000001</t>
+          <t>408472.0116279069</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>323363.0</t>
+          <t>228169.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>471049.8</v>
+        <v>354425</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>445989.1</t>
+          <t>390521.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>679269.88</v>
+        <v>675976.46</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>25060</t>
+          <t>-36096</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-52769.77804672284</t>
+          <t>-52661.39013608223</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-41875.26748193102</t>
+          <t>-52065.25662755885</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>323363.0</t>
+          <t>228169.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>172.66</t>
+          <t>170.36</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.62</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>710.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>713.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2044.942</t>
+          <t>1993.031</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>188.0</t>
+          <t>189.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-18.26</t>
+          <t>-16.73</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-13.76</t>
+          <t>-13.30</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-7.82</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>184.6</t>
+          <t>185.1</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>202.38</v>
+        <v>200.8</v>
       </c>
       <c r="AN13" t="n">
-        <v>211.26</v>
+        <v>210.69</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>211.12</t>
+          <t>210.82</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-26.76</t>
+          <t>-16.00</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-8.67</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-136.46</t>
+          <t>-137.98</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1325730314.156652</t>
+          <t>1324641204.394286</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>381363791.0</t>
+          <t>375568987.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>523400674.4</v>
+        <v>480990442.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>640315738.7</t>
+          <t>577604474.6</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>746361854.7</v>
+        <v>723589723.38</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-116915064</t>
+          <t>-96614032</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-13492364.62837173</t>
+          <t>-18624861.58487097</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-36990753.20293069</t>
+          <t>-46853594.84561682</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>381363791.0</t>
+          <t>375568987.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-14.16</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,22 +5931,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>47.72</t>
+          <t>47.97</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>66513</t>
+          <t>66867</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>184.5</t>
+          <t>189.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>188.0</t>
+          <t>190.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>184.5</t>
+          <t>187.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>188.0</t>
+          <t>189.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2724.529</t>
+          <t>2044.942</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-25.65</t>
+          <t>-18.26</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-15.60</t>
+          <t>-13.76</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-9.63</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>184.3</t>
+          <t>184.6</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>203.95</v>
+        <v>202.38</v>
       </c>
       <c r="AN14" t="n">
-        <v>211.72</v>
+        <v>211.26</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>211.42</t>
+          <t>211.12</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-40.39</t>
+          <t>-26.76</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-8.96</t>
+          <t>-8.67</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-134.02</t>
+          <t>-136.46</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1325730314.156652</t>
+          <t>1324641204.394286</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>497345820.0</t>
+          <t>381363791.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>538397244.2</v>
+        <v>523400674.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>724156183.6</t>
+          <t>640315738.7</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>755881026.66</v>
+        <v>746361854.7</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-185758939</t>
+          <t>-116915064</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-9219930.34208828</t>
+          <t>-13492364.62837173</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-22200752.9561317</t>
+          <t>-36990753.20293069</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>497345820.0</t>
+          <t>381363791.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-15.98</t>
+          <t>-14.16</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,22 +6361,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>47.72</t>
+          <t>47.97</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>66513</t>
+          <t>66867</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>182.5</t>
+          <t>184.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>184.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3925.483</t>
+          <t>2724.529</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-20.19</t>
+          <t>-25.65</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-16.97</t>
+          <t>-15.60</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-10.16</t>
+          <t>-9.63</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>184.8</t>
+          <t>184.3</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>205.7</v>
+        <v>203.95</v>
       </c>
       <c r="AN15" t="n">
-        <v>212.36</v>
+        <v>211.72</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>211.81</t>
+          <t>211.42</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-53.22</t>
+          <t>-40.39</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-8.79</t>
+          <t>-8.96</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-130.59</t>
+          <t>-134.02</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1325730314.156652</t>
+          <t>1324641204.394286</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>714330282.0</t>
+          <t>497345820.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>583542929</v>
+        <v>538397244.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>731190758.4</t>
+          <t>724156183.6</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>788163169.8</v>
+        <v>755881026.66</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-147647829</t>
+          <t>-185758939</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-6859780.775898567</t>
+          <t>-9219930.34208828</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-12705943.10512841</t>
+          <t>-22200752.9561317</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>714330282.0</t>
+          <t>497345820.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-17.35</t>
+          <t>-15.98</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>47.72</t>
+          <t>47.97</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>66513</t>
+          <t>66867</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>182.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>180.5</t>
+          <t>181.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2375.624</t>
+          <t>3925.483</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>181.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-13.38</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-15.83</t>
+          <t>-16.97</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>7.37</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,12 +7034,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7054,53 +7054,53 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-9.85</t>
+          <t>-10.16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>187.2</t>
+          <t>184.8</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>207.65</v>
+        <v>205.7</v>
       </c>
       <c r="AN16" t="n">
-        <v>213.15</v>
+        <v>212.36</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>212.2</t>
+          <t>211.81</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-63.70</t>
+          <t>-53.22</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-8.14</t>
+          <t>-8.79</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-126.52</t>
+          <t>-130.59</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1325730314.156652</t>
+          <t>1324641204.394286</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>436343333.0</t>
+          <t>714330282.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>624341783.8</v>
+        <v>583542929</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>720759640.4</t>
+          <t>731190758.4</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>863704924.02</v>
+        <v>788163169.8</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-96417856</t>
+          <t>-147647829</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-5796842.170584051</t>
+          <t>-6859780.775898567</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-21936480.56422627</t>
+          <t>-12705943.10512841</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>436343333.0</t>
+          <t>714330282.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-16.21</t>
+          <t>-17.35</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>47.72</t>
+          <t>47.97</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>66513</t>
+          <t>66867</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>184.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>180.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>181.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3128.645</t>
+          <t>2375.624</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>186.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-13.38</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-14.45</t>
+          <t>-15.83</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>7.37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,12 +7464,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7484,53 +7484,53 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-9.85</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>190.2</t>
+          <t>187.2</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>209.58</v>
+        <v>207.65</v>
       </c>
       <c r="AN17" t="n">
-        <v>213.6</v>
+        <v>213.15</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>212.58</t>
+          <t>212.2</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-78.19</t>
+          <t>-63.70</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-8.14</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-122.29</t>
+          <t>-126.52</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1325730314.156652</t>
+          <t>1324641204.394286</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>587620146.0</t>
+          <t>436343333.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>674218506.6</v>
+        <v>624341783.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>715379759.4</t>
+          <t>720759640.4</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>864477556.2</v>
+        <v>863704924.02</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-41161252</t>
+          <t>-96417856</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-2862362.462649101</t>
+          <t>-5796842.170584051</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-4555200.949929357</t>
+          <t>-21936480.56422627</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>587620146.0</t>
+          <t>436343333.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-14.84</t>
+          <t>-16.21</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>47.72</t>
+          <t>47.97</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>66513</t>
+          <t>66867</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>189.5</t>
+          <t>184.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>191.5</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>186.5</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>186.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2437.772</t>
+          <t>3128.645</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,12 +7894,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7914,53 +7914,53 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-8.70</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>192.9</t>
+          <t>190.2</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>211.28</v>
+        <v>209.58</v>
       </c>
       <c r="AN18" t="n">
-        <v>214.03</v>
+        <v>213.6</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>212.96</t>
+          <t>212.58</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-101.13</t>
+          <t>-78.19</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-117.94</t>
+          <t>-122.29</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1325730314.156652</t>
+          <t>1324641204.394286</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>456346640.0</t>
+          <t>587620146.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>757230803</v>
+        <v>674218506.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>678685106.5</t>
+          <t>715379759.4</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>856936697.08</v>
+        <v>864477556.2</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>78545696</t>
+          <t>-41161252</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-2554573.646779964</t>
+          <t>-2862362.462649101</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>4229654.282992125</t>
+          <t>-4555200.949929357</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>456346640.0</t>
+          <t>587620146.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,12 +8081,12 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>47.72</t>
+          <t>47.97</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>66513</t>
+          <t>66867</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,17 +8146,17 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
+          <t>189.5</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
+          <t>191.5</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
           <t>186.5</t>
-        </is>
-      </c>
-      <c r="CE18" t="inlineStr">
-        <is>
-          <t>190.0</t>
-        </is>
-      </c>
-      <c r="CF18" t="inlineStr">
-        <is>
-          <t>185.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3839.598</t>
+          <t>2437.772</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,12 +8324,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8344,53 +8344,53 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-8.70</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>196.6</t>
+          <t>192.9</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>212.75</v>
+        <v>211.28</v>
       </c>
       <c r="AN19" t="n">
-        <v>214.42</v>
+        <v>214.03</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>213.34</t>
+          <t>212.96</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-130.49</t>
+          <t>-101.13</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-113.40</t>
+          <t>-117.94</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1325730314.156652</t>
+          <t>1324641204.394286</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>723074244.0</t>
+          <t>456346640.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>909915123</v>
+        <v>757230803</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>674907487.9</t>
+          <t>678685106.5</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>854335140.0599999</v>
+        <v>856936697.08</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>235007635</t>
+          <t>78545696</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-3788069.634011253</t>
+          <t>-2554573.646779964</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>30693406.89134467</t>
+          <t>4229654.282992125</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>723074244.0</t>
+          <t>456346640.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>47.72</t>
+          <t>47.97</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>66513</t>
+          <t>66867</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,17 +8576,17 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>191.5</t>
+          <t>190.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4701.928</t>
+          <t>3839.598</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-14.45</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14.59</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>201.2</t>
+          <t>196.6</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>213.98</v>
+        <v>212.75</v>
       </c>
       <c r="AN20" t="n">
-        <v>214.79</v>
+        <v>214.42</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>213.72</t>
+          <t>213.34</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-163.83</t>
+          <t>-130.49</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-109.03</t>
+          <t>-113.40</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1325730314.156652</t>
+          <t>1324641204.394286</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>918324556.0</t>
+          <t>723074244.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>878838587.8</v>
+        <v>909915123</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>691621829.4</t>
+          <t>674907487.9</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>845368183.24</v>
+        <v>854335140.0599999</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>187216758</t>
+          <t>235007635</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-10057429.00225778</t>
+          <t>-3788069.634011253</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>38824617.085729</t>
+          <t>30693406.89134467</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>918324556.0</t>
+          <t>723074244.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-11.87</t>
+          <t>-14.84</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>47.72</t>
+          <t>47.97</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>66513</t>
+          <t>66867</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>191.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3457.008</t>
+          <t>4701.928</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>25.67</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-8.94</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10.72</t>
+          <t>14.59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>204.6</t>
+          <t>201.2</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>214.72</v>
+        <v>213.98</v>
       </c>
       <c r="AN21" t="n">
-        <v>215.02</v>
+        <v>214.79</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>213.92</t>
+          <t>213.72</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-237.34</t>
+          <t>-163.83</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-105.33</t>
+          <t>-109.03</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1325730314.156652</t>
+          <t>1324641204.394286</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>685726947.0</t>
+          <t>918324556.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>817177497</v>
+        <v>878838587.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>650263422.9</t>
+          <t>691621829.4</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>838743112.42</v>
+        <v>845368183.24</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>166914074</t>
+          <t>187216758</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-18945073.74552811</t>
+          <t>-10057429.00225778</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>28134361.89607322</t>
+          <t>38824617.085729</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>685726947.0</t>
+          <t>918324556.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-11.87</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>47.72</t>
+          <t>47.97</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>66513</t>
+          <t>66867</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>195.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9473,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5006.119</t>
+          <t>3457.008</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-5.03</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>25.67</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-8.94</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>10.72</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>207.7</t>
+          <t>204.6</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>215.3</v>
+        <v>214.72</v>
       </c>
       <c r="AN22" t="n">
-        <v>215.19</v>
+        <v>215.02</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>214.13</t>
+          <t>213.92</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-511.52</t>
+          <t>-237.34</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-102.17</t>
+          <t>-105.33</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1325730314.156652</t>
+          <t>1324641204.394286</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>1002681628.0</t>
+          <t>685726947.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>756541012.2</v>
+        <v>817177497</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>657490336.6</t>
+          <t>650263422.9</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>837159531.8</v>
+        <v>838743112.42</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>99050675</t>
+          <t>166914074</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-27504971.13491017</t>
+          <t>-18945073.74552811</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>36778942.52170527</t>
+          <t>28134361.89607322</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>1002681628.0</t>
+          <t>685726947.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-8.68</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>47.72</t>
+          <t>47.97</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>66513</t>
+          <t>66867</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
+          <t>195.0</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
+        <is>
           <t>201.0</t>
         </is>
       </c>
-      <c r="CE22" t="inlineStr">
-        <is>
-          <t>205.0</t>
-        </is>
-      </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5932.964</t>
+          <t>5006.119</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-9.04</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>15.06</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-5.96</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18.40</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,53 +10064,53 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>211.3</t>
+          <t>207.7</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>215.75</v>
+        <v>215.3</v>
       </c>
       <c r="AN23" t="n">
-        <v>215.46</v>
+        <v>215.19</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>214.3</t>
+          <t>214.13</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-1398.14</t>
+          <t>-511.52</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-99.40</t>
+          <t>-102.17</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1325730314.156652</t>
+          <t>1324641204.394286</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>1219768240.0</t>
+          <t>1002681628.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>600139410</v>
+        <v>756541012.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>623193432.6</t>
+          <t>657490336.6</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>825475916.8</v>
+        <v>837159531.8</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-23054022</t>
+          <t>99050675</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-39192955.43611298</t>
+          <t>-27504971.13491017</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>13855379.64683306</t>
+          <t>36778942.52170527</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>1219768240.0</t>
+          <t>1002681628.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-8.68</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>47.72</t>
+          <t>47.97</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>66513</t>
+          <t>66867</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>196.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/工業型機器人.xlsx
+++ b/Result/checksun_type/工業型機器人.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>247.0</t>
+          <t>249.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-27.97</t>
+          <t>-32.45</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-22.94</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>249</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>37.51</t>
+          <t>60.54</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-6.43</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-10.5</t>
+          <t>-11.22</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>630.2</t>
+          <t>639.2</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>688.8</v>
+        <v>683.15</v>
       </c>
       <c r="AN2" t="n">
-        <v>769.62</v>
+        <v>769.46</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>690.04</t>
+          <t>692.9</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-11.17</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-37.34</t>
+          <t>-34.77</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-33.59</t>
+          <t>-33.83</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-137.34</t>
+          <t>-137.60</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>408472.0116279069</t>
+          <t>407921.3592715232</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>159302.0</t>
+          <t>161450.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>166838.8</v>
+        <v>146674</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>231634.1</t>
+          <t>217118.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>622148.62</v>
+        <v>615716.62</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-64795</t>
+          <t>-70444</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-52766.09080324681</t>
+          <t>-52873.98683047794</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-56843.90693450192</t>
+          <t>-53467.41498024913</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>159302.0</t>
+          <t>161450.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>143.98</t>
+          <t>150.48</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>55.41</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>651.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>658.0</t>
+          <t>656.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>247.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-22.82</t>
+          <t>-27.97</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,42 +1444,42 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>249</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>37.51</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-9.86</t>
+          <t>-10.5</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>12.14</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1488,29 +1488,29 @@
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>694.75</v>
+        <v>688.8</v>
       </c>
       <c r="AN3" t="n">
-        <v>770.74</v>
+        <v>769.62</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>687.31</t>
+          <t>690.04</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-17.45</t>
+          <t>-11.17</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-38.35</t>
+          <t>-37.34</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-32.65</t>
+          <t>-33.59</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-136.30</t>
+          <t>-137.34</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>408472.0116279069</t>
+          <t>407921.3592715232</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>184090</v>
+        <v>166838.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>238520.8</t>
+          <t>231634.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>625496.02</v>
+        <v>622148.62</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-54430</t>
+          <t>-64795</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-52024.66968847315</t>
+          <t>-52766.09080324681</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-59407.18447863078</t>
+          <t>-56843.90693450192</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>55.41</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>651.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>658.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>636.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>283.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-18.38</t>
+          <t>-22.82</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,22 +1874,22 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>249</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>30.93</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -1899,17 +1899,17 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-10.13</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-9.11</t>
+          <t>-9.86</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1918,29 +1918,29 @@
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>701.25</v>
+        <v>694.75</v>
       </c>
       <c r="AN4" t="n">
-        <v>771.5599999999999</v>
+        <v>770.74</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>684.56</t>
+          <t>687.31</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-25.78</t>
+          <t>-17.45</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-39.28</t>
+          <t>-38.35</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-31.23</t>
+          <t>-32.65</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-134.72</t>
+          <t>-136.30</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>408472.0116279069</t>
+          <t>407921.3592715232</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>213249.4</v>
+        <v>184090</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>261286.0</t>
+          <t>238520.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>631907.8</v>
+        <v>625496.02</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-48036</t>
+          <t>-54430</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-50682.39427208085</t>
+          <t>-52024.66968847315</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-54134.00295314955</t>
+          <t>-59407.18447863078</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>55.41</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>629.0</t>
+          <t>636.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>283.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-18.38</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-26.71</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>249</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>12.62</t>
+          <t>30.93</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-10.13</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-9.11</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>13.29</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>631.4</t>
+          <t>630.2</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>706</v>
+        <v>701.25</v>
       </c>
       <c r="AN5" t="n">
-        <v>772.34</v>
+        <v>771.5599999999999</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>681.75</t>
+          <t>684.56</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-36.56</t>
+          <t>-25.78</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-39.90</t>
+          <t>-39.28</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-29.22</t>
+          <t>-31.23</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-132.48</t>
+          <t>-134.72</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>408472.0116279069</t>
+          <t>407921.3592715232</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>135802.0</t>
+          <t>181105.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>252624</v>
+        <v>213249.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>286992.7</t>
+          <t>261286.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>639483.2</v>
+        <v>631907.8</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-34368</t>
+          <t>-48036</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-50054.82905734108</t>
+          <t>-50682.39427208085</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-53816.8863827067</t>
+          <t>-54134.00295314955</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>135802.0</t>
+          <t>181105.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>138.24</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>16.41</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>55.41</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>654.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>629.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>428.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-11.10</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-28.24</t>
+          <t>-26.71</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>249</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.62</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-10.02</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-7.9</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>13.29</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>641.0</t>
+          <t>631.4</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>712.35</v>
+        <v>706</v>
       </c>
       <c r="AN6" t="n">
-        <v>773.42</v>
+        <v>772.34</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>679.24</t>
+          <t>681.75</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-44.55</t>
+          <t>-36.56</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-38.37</t>
+          <t>-39.90</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-26.55</t>
+          <t>-29.22</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-129.51</t>
+          <t>-132.48</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>408472.0116279069</t>
+          <t>407921.3592715232</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>262274.0</t>
+          <t>135802.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>287562.6</v>
+        <v>252624</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>323456.1</t>
+          <t>286992.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>664782.5</v>
+        <v>639483.2</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-35893</t>
+          <t>-34368</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-49370.81863454734</t>
+          <t>-50054.82905734108</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-46587.93819697743</t>
+          <t>-53816.8863827067</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>262274.0</t>
+          <t>135802.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>133.27</t>
+          <t>138.24</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.41</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>55.41</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>624.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>630.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>600.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>377.0</t>
+          <t>428.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-11.10</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-28.24</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>249</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3184,53 +3184,53 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-10.02</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-7.9</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>657.8</t>
+          <t>641.0</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>718.95</v>
+        <v>712.35</v>
       </c>
       <c r="AN7" t="n">
-        <v>774.36</v>
+        <v>773.42</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>677.44</t>
+          <t>679.24</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-46.43</t>
+          <t>-44.55</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-34.54</t>
+          <t>-38.37</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-23.59</t>
+          <t>-26.55</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-126.22</t>
+          <t>-129.51</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>408472.0116279069</t>
+          <t>407921.3592715232</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>245558.0</t>
+          <t>262274.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>296429.4</v>
+        <v>287562.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>325427.2</t>
+          <t>323456.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>674644.66</v>
+        <v>664782.5</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-28997</t>
+          <t>-35893</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-49876.79689592369</t>
+          <t>-49370.81863454734</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-48147.58585318638</t>
+          <t>-46587.93819697743</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>245558.0</t>
+          <t>262274.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>143.98</t>
+          <t>133.27</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>55.41</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>624.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>672.0</t>
+          <t>630.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>600.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>371.0</t>
+          <t>377.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-23.31</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>249</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>671.6</t>
+          <t>657.8</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>725.65</v>
+        <v>718.95</v>
       </c>
       <c r="AN8" t="n">
-        <v>773.5599999999999</v>
+        <v>774.36</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>675.4</t>
+          <t>677.44</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-53.49</t>
+          <t>-46.43</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-32.01</t>
+          <t>-34.54</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-20.85</t>
+          <t>-23.59</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-123.18</t>
+          <t>-126.22</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>408472.0116279069</t>
+          <t>407921.3592715232</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>241508.0</t>
+          <t>245558.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>292951.6</v>
+        <v>296429.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>382000.7</t>
+          <t>325427.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>675976.12</v>
+        <v>674644.66</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-89049</t>
+          <t>-28997</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-50191.19890369411</t>
+          <t>-49876.79689592369</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-46865.09729587106</t>
+          <t>-48147.58585318638</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>241508.0</t>
+          <t>245558.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>55.41</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>667.0</t>
+          <t>672.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>371.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-22.67</t>
+          <t>-23.31</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>249</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-6.42</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>686.2</t>
+          <t>671.6</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>733.3</v>
+        <v>725.65</v>
       </c>
       <c r="AN9" t="n">
-        <v>772.84</v>
+        <v>773.5599999999999</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>675.4</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-57.81</t>
+          <t>-53.49</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-28.51</t>
+          <t>-32.01</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-18.06</t>
+          <t>-20.85</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-120.08</t>
+          <t>-123.18</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>408472.0116279069</t>
+          <t>407921.3592715232</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>377978.0</t>
+          <t>241508.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>309322.6</v>
+        <v>292951.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>400021.6</t>
+          <t>382000.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>677723.46</v>
+        <v>675976.12</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-90699</t>
+          <t>-89049</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-50795.94465057103</t>
+          <t>-50191.19890369411</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-42925.28873913951</t>
+          <t>-46865.09729587106</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>377978.0</t>
+          <t>241508.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>147.04</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>55.41</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>693.0</t>
+          <t>667.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>456.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-18.05</t>
+          <t>-22.67</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-21.06</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>249</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-6.42</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>702.8</t>
+          <t>686.2</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>740.6</v>
+        <v>733.3</v>
       </c>
       <c r="AN10" t="n">
-        <v>771.72</v>
+        <v>772.84</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>670.89</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-56.83</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-24.23</t>
+          <t>-28.51</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-18.06</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-117.18</t>
+          <t>-120.08</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>408472.0116279069</t>
+          <t>407921.3592715232</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>310495.0</t>
+          <t>377978.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>321361.4</v>
+        <v>309322.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>392151.7</t>
+          <t>400021.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>673300.1800000001</v>
+        <v>677723.46</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-70790</t>
+          <t>-90699</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-52226.97299810403</t>
+          <t>-50795.94465057103</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-50385.73048883944</t>
+          <t>-42925.28873913951</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>310495.0</t>
+          <t>377978.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>156.60</t>
+          <t>147.04</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>55.41</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>699.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>444.0</t>
+          <t>456.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-18.05</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-18.35</t>
+          <t>-21.06</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>249</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>15.03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>711.8</t>
+          <t>702.8</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>747.5</v>
+        <v>740.6</v>
       </c>
       <c r="AN11" t="n">
-        <v>770.14</v>
+        <v>771.72</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>668.28</t>
+          <t>670.89</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-58.22</t>
+          <t>-56.83</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-20.97</t>
+          <t>-24.23</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-15.45</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-114.74</t>
+          <t>-117.18</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>408472.0116279069</t>
+          <t>407921.3592715232</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>306608.0</t>
+          <t>310495.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>359349.6</v>
+        <v>321361.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>389319.8</t>
+          <t>392151.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>672018.02</v>
+        <v>673300.1800000001</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-29970</t>
+          <t>-70790</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-52561.74436342486</t>
+          <t>-52226.97299810403</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-52013.69261380937</t>
+          <t>-50385.73048883944</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>306608.0</t>
+          <t>310495.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>165.39</t>
+          <t>156.60</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>18.28</t>
+          <t>17.68</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>55.41</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>679.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>444.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-16.82</t>
+          <t>-18.35</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>249</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>15.24</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>722.4</t>
+          <t>711.8</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>754.55</v>
+        <v>747.5</v>
       </c>
       <c r="AN12" t="n">
-        <v>768.0599999999999</v>
+        <v>770.14</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>665.62</t>
+          <t>668.28</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-66.42</t>
+          <t>-58.22</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-18.85</t>
+          <t>-20.97</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-13.26</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-112.59</t>
+          <t>-114.74</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>408472.0116279069</t>
+          <t>407921.3592715232</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>228169.0</t>
+          <t>306608.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>354425</v>
+        <v>359349.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>390521.3</t>
+          <t>389319.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>675976.46</v>
+        <v>672018.02</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-36096</t>
+          <t>-29970</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-52661.39013608223</t>
+          <t>-52561.74436342486</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-52065.25662755885</t>
+          <t>-52013.69261380937</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>228169.0</t>
+          <t>306608.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>170.36</t>
+          <t>165.39</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>55.41</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>699.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>679.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1993.031</t>
+          <t>1593.532</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>189.0</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-16.73</t>
+          <t>-15.71</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-13.30</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>1594</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>68.89</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-7.82</t>
+          <t>-6.16</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-5.23</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>185.1</t>
+          <t>187.0</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>200.8</v>
+        <v>199.28</v>
       </c>
       <c r="AN13" t="n">
-        <v>210.69</v>
+        <v>210.27</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>210.82</t>
+          <t>210.61</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-16.00</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-137.98</t>
+          <t>-138.42</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1324641204.394286</t>
+          <t>1323404754.243937</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>375568987.0</t>
+          <t>305259766.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>480990442.6</v>
+        <v>454773729.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>577604474.6</t>
+          <t>539557756.5</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>723589723.38</v>
+        <v>713839519.5</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-96614032</t>
+          <t>-84784027</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-18624861.58487097</t>
+          <t>-24660949.91017646</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-46853594.84561682</t>
+          <t>-57859435.69935668</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>375568987.0</t>
+          <t>305259766.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-11.87</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>47.97</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>66867</t>
+          <t>68282</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
+          <t>189.5</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>193.0</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
           <t>189.0</t>
         </is>
       </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>190.5</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>187.0</t>
-        </is>
-      </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>189.0</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2044.942</t>
+          <t>1993.031</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>188.0</t>
+          <t>189.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-18.26</t>
+          <t>-16.73</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-13.76</t>
+          <t>-13.30</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>1594</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-7.82</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>184.6</t>
+          <t>185.1</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>202.38</v>
+        <v>200.8</v>
       </c>
       <c r="AN14" t="n">
-        <v>211.26</v>
+        <v>210.69</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>211.12</t>
+          <t>210.82</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-26.76</t>
+          <t>-16.00</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-8.67</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-136.46</t>
+          <t>-137.98</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1324641204.394286</t>
+          <t>1323404754.243937</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>381363791.0</t>
+          <t>375568987.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>523400674.4</v>
+        <v>480990442.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>640315738.7</t>
+          <t>577604474.6</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>746361854.7</v>
+        <v>723589723.38</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-116915064</t>
+          <t>-96614032</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-13492364.62837173</t>
+          <t>-18624861.58487097</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-36990753.20293069</t>
+          <t>-46853594.84561682</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>381363791.0</t>
+          <t>375568987.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-14.16</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,22 +6361,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>47.97</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>66867</t>
+          <t>68282</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>184.5</t>
+          <t>189.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>188.0</t>
+          <t>190.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>184.5</t>
+          <t>187.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>188.0</t>
+          <t>189.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2724.529</t>
+          <t>2044.942</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-25.65</t>
+          <t>-18.26</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-15.60</t>
+          <t>-13.76</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>1594</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-9.63</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>184.3</t>
+          <t>184.6</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>203.95</v>
+        <v>202.38</v>
       </c>
       <c r="AN15" t="n">
-        <v>211.72</v>
+        <v>211.26</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>211.42</t>
+          <t>211.12</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-40.39</t>
+          <t>-26.76</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-8.96</t>
+          <t>-8.67</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-134.02</t>
+          <t>-136.46</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1324641204.394286</t>
+          <t>1323404754.243937</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>497345820.0</t>
+          <t>381363791.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>538397244.2</v>
+        <v>523400674.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>724156183.6</t>
+          <t>640315738.7</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>755881026.66</v>
+        <v>746361854.7</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-185758939</t>
+          <t>-116915064</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-9219930.34208828</t>
+          <t>-13492364.62837173</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-22200752.9561317</t>
+          <t>-36990753.20293069</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>497345820.0</t>
+          <t>381363791.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-15.98</t>
+          <t>-14.16</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>47.97</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>66867</t>
+          <t>68282</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>182.5</t>
+          <t>184.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>184.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3925.483</t>
+          <t>2724.529</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-20.19</t>
+          <t>-25.65</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-16.97</t>
+          <t>-15.60</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>1594</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-10.16</t>
+          <t>-9.63</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>184.8</t>
+          <t>184.3</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>205.7</v>
+        <v>203.95</v>
       </c>
       <c r="AN16" t="n">
-        <v>212.36</v>
+        <v>211.72</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>211.81</t>
+          <t>211.42</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-53.22</t>
+          <t>-40.39</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-8.79</t>
+          <t>-8.96</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-130.59</t>
+          <t>-134.02</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1324641204.394286</t>
+          <t>1323404754.243937</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>714330282.0</t>
+          <t>497345820.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>583542929</v>
+        <v>538397244.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>731190758.4</t>
+          <t>724156183.6</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>788163169.8</v>
+        <v>755881026.66</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-147647829</t>
+          <t>-185758939</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-6859780.775898567</t>
+          <t>-9219930.34208828</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-12705943.10512841</t>
+          <t>-22200752.9561317</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>714330282.0</t>
+          <t>497345820.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-17.35</t>
+          <t>-15.98</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>47.97</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>66867</t>
+          <t>68282</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>182.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>180.5</t>
+          <t>181.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2375.624</t>
+          <t>3925.483</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>181.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-13.38</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-15.83</t>
+          <t>-16.97</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>7.37</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,12 +7464,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>1594</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7484,53 +7484,53 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-9.85</t>
+          <t>-10.16</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>187.2</t>
+          <t>184.8</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>207.65</v>
+        <v>205.7</v>
       </c>
       <c r="AN17" t="n">
-        <v>213.15</v>
+        <v>212.36</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>212.2</t>
+          <t>211.81</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-63.70</t>
+          <t>-53.22</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-8.14</t>
+          <t>-8.79</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-126.52</t>
+          <t>-130.59</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1324641204.394286</t>
+          <t>1323404754.243937</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>436343333.0</t>
+          <t>714330282.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>624341783.8</v>
+        <v>583542929</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>720759640.4</t>
+          <t>731190758.4</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>863704924.02</v>
+        <v>788163169.8</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-96417856</t>
+          <t>-147647829</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-5796842.170584051</t>
+          <t>-6859780.775898567</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-21936480.56422627</t>
+          <t>-12705943.10512841</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>436343333.0</t>
+          <t>714330282.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-16.21</t>
+          <t>-17.35</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>47.97</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>66867</t>
+          <t>68282</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>184.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>180.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>181.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3128.645</t>
+          <t>2375.624</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>186.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-13.38</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-14.45</t>
+          <t>-15.83</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>7.37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,12 +7894,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>1594</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7914,53 +7914,53 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-9.85</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>190.2</t>
+          <t>187.2</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>209.58</v>
+        <v>207.65</v>
       </c>
       <c r="AN18" t="n">
-        <v>213.6</v>
+        <v>213.15</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>212.58</t>
+          <t>212.2</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-78.19</t>
+          <t>-63.70</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-8.14</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-122.29</t>
+          <t>-126.52</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1324641204.394286</t>
+          <t>1323404754.243937</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>587620146.0</t>
+          <t>436343333.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>674218506.6</v>
+        <v>624341783.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>715379759.4</t>
+          <t>720759640.4</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>864477556.2</v>
+        <v>863704924.02</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-41161252</t>
+          <t>-96417856</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-2862362.462649101</t>
+          <t>-5796842.170584051</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-4555200.949929357</t>
+          <t>-21936480.56422627</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>587620146.0</t>
+          <t>436343333.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-14.84</t>
+          <t>-16.21</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>47.97</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>66867</t>
+          <t>68282</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>189.5</t>
+          <t>184.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>191.5</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>186.5</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>186.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2437.772</t>
+          <t>3128.645</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,12 +8324,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>1594</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8344,53 +8344,53 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-8.70</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>192.9</t>
+          <t>190.2</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>211.28</v>
+        <v>209.58</v>
       </c>
       <c r="AN19" t="n">
-        <v>214.03</v>
+        <v>213.6</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>212.96</t>
+          <t>212.58</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-101.13</t>
+          <t>-78.19</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-117.94</t>
+          <t>-122.29</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1324641204.394286</t>
+          <t>1323404754.243937</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>456346640.0</t>
+          <t>587620146.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>757230803</v>
+        <v>674218506.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>678685106.5</t>
+          <t>715379759.4</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>856936697.08</v>
+        <v>864477556.2</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>78545696</t>
+          <t>-41161252</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-2554573.646779964</t>
+          <t>-2862362.462649101</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>4229654.282992125</t>
+          <t>-4555200.949929357</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>456346640.0</t>
+          <t>587620146.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>47.97</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>66867</t>
+          <t>68282</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,17 +8576,17 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
+          <t>189.5</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
+          <t>191.5</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
           <t>186.5</t>
-        </is>
-      </c>
-      <c r="CE19" t="inlineStr">
-        <is>
-          <t>190.0</t>
-        </is>
-      </c>
-      <c r="CF19" t="inlineStr">
-        <is>
-          <t>185.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3839.598</t>
+          <t>2437.772</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>1594</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-8.70</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>196.6</t>
+          <t>192.9</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>212.75</v>
+        <v>211.28</v>
       </c>
       <c r="AN20" t="n">
-        <v>214.42</v>
+        <v>214.03</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>213.34</t>
+          <t>212.96</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-130.49</t>
+          <t>-101.13</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-113.40</t>
+          <t>-117.94</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1324641204.394286</t>
+          <t>1323404754.243937</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>723074244.0</t>
+          <t>456346640.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>909915123</v>
+        <v>757230803</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>674907487.9</t>
+          <t>678685106.5</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>854335140.0599999</v>
+        <v>856936697.08</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>235007635</t>
+          <t>78545696</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-3788069.634011253</t>
+          <t>-2554573.646779964</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>30693406.89134467</t>
+          <t>4229654.282992125</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>723074244.0</t>
+          <t>456346640.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>47.97</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>66867</t>
+          <t>68282</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,17 +9006,17 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>191.5</t>
+          <t>190.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4701.928</t>
+          <t>3839.598</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-14.45</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14.59</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>1594</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>201.2</t>
+          <t>196.6</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>213.98</v>
+        <v>212.75</v>
       </c>
       <c r="AN21" t="n">
-        <v>214.79</v>
+        <v>214.42</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>213.72</t>
+          <t>213.34</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-163.83</t>
+          <t>-130.49</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-109.03</t>
+          <t>-113.40</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1324641204.394286</t>
+          <t>1323404754.243937</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>918324556.0</t>
+          <t>723074244.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>878838587.8</v>
+        <v>909915123</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>691621829.4</t>
+          <t>674907487.9</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>845368183.24</v>
+        <v>854335140.0599999</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>187216758</t>
+          <t>235007635</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-10057429.00225778</t>
+          <t>-3788069.634011253</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>38824617.085729</t>
+          <t>30693406.89134467</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>918324556.0</t>
+          <t>723074244.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-11.87</t>
+          <t>-14.84</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>47.97</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>66867</t>
+          <t>68282</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>191.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3457.008</t>
+          <t>4701.928</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-5.03</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>25.67</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-8.94</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10.72</t>
+          <t>14.59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>1594</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>204.6</t>
+          <t>201.2</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>214.72</v>
+        <v>213.98</v>
       </c>
       <c r="AN22" t="n">
-        <v>215.02</v>
+        <v>214.79</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>213.92</t>
+          <t>213.72</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-237.34</t>
+          <t>-163.83</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-105.33</t>
+          <t>-109.03</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1324641204.394286</t>
+          <t>1323404754.243937</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>685726947.0</t>
+          <t>918324556.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>817177497</v>
+        <v>878838587.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>650263422.9</t>
+          <t>691621829.4</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>838743112.42</v>
+        <v>845368183.24</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>166914074</t>
+          <t>187216758</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-18945073.74552811</t>
+          <t>-10057429.00225778</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>28134361.89607322</t>
+          <t>38824617.085729</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>685726947.0</t>
+          <t>918324556.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-11.87</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>47.97</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>66867</t>
+          <t>68282</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>195.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9903,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5006.119</t>
+          <t>3457.008</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>25.67</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-8.94</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>10.72</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>1594</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,53 +10064,53 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>207.7</t>
+          <t>204.6</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>215.3</v>
+        <v>214.72</v>
       </c>
       <c r="AN23" t="n">
-        <v>215.19</v>
+        <v>215.02</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>214.13</t>
+          <t>213.92</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-511.52</t>
+          <t>-237.34</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-102.17</t>
+          <t>-105.33</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1324641204.394286</t>
+          <t>1323404754.243937</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>1002681628.0</t>
+          <t>685726947.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>756541012.2</v>
+        <v>817177497</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>657490336.6</t>
+          <t>650263422.9</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>837159531.8</v>
+        <v>838743112.42</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>99050675</t>
+          <t>166914074</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-27504971.13491017</t>
+          <t>-18945073.74552811</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>36778942.52170527</t>
+          <t>28134361.89607322</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>1002681628.0</t>
+          <t>685726947.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-8.68</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>47.97</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>66867</t>
+          <t>68282</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
+          <t>195.0</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
           <t>201.0</t>
         </is>
       </c>
-      <c r="CE23" t="inlineStr">
-        <is>
-          <t>205.0</t>
-        </is>
-      </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>198.5</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/工業型機器人.xlsx
+++ b/Result/checksun_type/工業型機器人.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>249.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-32.45</t>
+          <t>-27.56</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-22.94</t>
+          <t>-23.88</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.22</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>60.54</t>
+          <t>76.04</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-6.43</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.22</t>
+          <t>-11.65</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>639.2</t>
+          <t>644.0</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>683.15</v>
+        <v>678.35</v>
       </c>
       <c r="AN2" t="n">
-        <v>769.46</v>
+        <v>767.8200000000001</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>692.9</t>
+          <t>695.44</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-34.77</t>
+          <t>-33.00</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-33.83</t>
+          <t>-33.66</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,53 +1090,53 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-137.60</t>
+          <t>-137.42</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/09/08</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>407921.3592715232</t>
+          <t>407167.6386138613</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>161450.0</t>
+          <t>119696.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>146674</v>
+        <v>143452.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>217118.3</t>
+          <t>198038.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>615716.62</v>
+        <v>598609.88</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-70444</t>
+          <t>-54585</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-52873.98683047794</t>
+          <t>-52877.79427775302</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-53467.41498024913</t>
+          <t>-52898.73523776597</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>161450.0</t>
+          <t>119696.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>150.48</t>
+          <t>147.42</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>55.41</t>
+          <t>54.74</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>656.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>247.0</t>
+          <t>249.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-27.97</t>
+          <t>-32.45</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-22.94</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>37.51</t>
+          <t>60.54</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-6.43</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-10.5</t>
+          <t>-11.22</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>630.2</t>
+          <t>639.2</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>688.8</v>
+        <v>683.15</v>
       </c>
       <c r="AN3" t="n">
-        <v>769.62</v>
+        <v>769.46</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>690.04</t>
+          <t>692.9</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-11.17</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-37.34</t>
+          <t>-34.77</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-33.59</t>
+          <t>-33.83</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,53 +1520,53 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-137.34</t>
+          <t>-137.60</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/09/08</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>407921.3592715232</t>
+          <t>407167.6386138613</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>159302.0</t>
+          <t>161450.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>166838.8</v>
+        <v>146674</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>231634.1</t>
+          <t>217118.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>622148.62</v>
+        <v>615716.62</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-64795</t>
+          <t>-70444</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-52766.09080324681</t>
+          <t>-52873.98683047794</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-56843.90693450192</t>
+          <t>-53467.41498024913</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>159302.0</t>
+          <t>161450.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>143.98</t>
+          <t>150.48</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>55.41</t>
+          <t>54.74</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,12 +1696,12 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>651.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>658.0</t>
+          <t>656.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>247.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-22.82</t>
+          <t>-27.97</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,42 +1874,42 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>37.51</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-9.86</t>
+          <t>-10.5</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>12.14</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1918,29 +1918,29 @@
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>694.75</v>
+        <v>688.8</v>
       </c>
       <c r="AN4" t="n">
-        <v>770.74</v>
+        <v>769.62</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>687.31</t>
+          <t>690.04</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-17.45</t>
+          <t>-11.17</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-38.35</t>
+          <t>-37.34</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-32.65</t>
+          <t>-33.59</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,53 +1950,53 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-136.30</t>
+          <t>-137.34</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/09/08</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>407921.3592715232</t>
+          <t>407167.6386138613</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>184090</v>
+        <v>166838.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>238520.8</t>
+          <t>231634.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>625496.02</v>
+        <v>622148.62</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-54430</t>
+          <t>-64795</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-52024.66968847315</t>
+          <t>-52766.09080324681</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-59407.18447863078</t>
+          <t>-56843.90693450192</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>55.41</t>
+          <t>54.74</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>651.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>658.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>636.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>283.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-18.38</t>
+          <t>-22.82</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,22 +2304,22 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>30.93</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
@@ -2329,17 +2329,17 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-10.13</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-9.11</t>
+          <t>-9.86</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -2348,29 +2348,29 @@
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>701.25</v>
+        <v>694.75</v>
       </c>
       <c r="AN5" t="n">
-        <v>771.5599999999999</v>
+        <v>770.74</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>684.56</t>
+          <t>687.31</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-25.78</t>
+          <t>-17.45</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-39.28</t>
+          <t>-38.35</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-31.23</t>
+          <t>-32.65</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,53 +2380,53 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-134.72</t>
+          <t>-136.30</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/09/08</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>407921.3592715232</t>
+          <t>407167.6386138613</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>213249.4</v>
+        <v>184090</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>261286.0</t>
+          <t>238520.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>631907.8</v>
+        <v>625496.02</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-48036</t>
+          <t>-54430</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-50682.39427208085</t>
+          <t>-52024.66968847315</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-54134.00295314955</t>
+          <t>-59407.18447863078</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>55.41</t>
+          <t>54.74</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,17 +2556,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>629.0</t>
+          <t>636.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>283.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-18.38</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-26.71</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>12.62</t>
+          <t>30.93</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-10.13</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-9.11</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>13.29</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>631.4</t>
+          <t>630.2</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>706</v>
+        <v>701.25</v>
       </c>
       <c r="AN6" t="n">
-        <v>772.34</v>
+        <v>771.5599999999999</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>681.75</t>
+          <t>684.56</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-36.56</t>
+          <t>-25.78</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-39.90</t>
+          <t>-39.28</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-29.22</t>
+          <t>-31.23</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,53 +2810,53 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-132.48</t>
+          <t>-134.72</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/09/08</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>407921.3592715232</t>
+          <t>407167.6386138613</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>135802.0</t>
+          <t>181105.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>252624</v>
+        <v>213249.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>286992.7</t>
+          <t>261286.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>639483.2</v>
+        <v>631907.8</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-34368</t>
+          <t>-48036</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-50054.82905734108</t>
+          <t>-50682.39427208085</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-53816.8863827067</t>
+          <t>-54134.00295314955</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>135802.0</t>
+          <t>181105.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>138.24</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>16.41</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>55.41</t>
+          <t>54.74</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>654.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>629.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>428.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-11.10</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-28.24</t>
+          <t>-26.71</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.62</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-10.02</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-7.9</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>13.29</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>641.0</t>
+          <t>631.4</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>712.35</v>
+        <v>706</v>
       </c>
       <c r="AN7" t="n">
-        <v>773.42</v>
+        <v>772.34</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>679.24</t>
+          <t>681.75</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-44.55</t>
+          <t>-36.56</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-38.37</t>
+          <t>-39.90</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-26.55</t>
+          <t>-29.22</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,53 +3240,53 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-129.51</t>
+          <t>-132.48</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/09/08</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>407921.3592715232</t>
+          <t>407167.6386138613</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>262274.0</t>
+          <t>135802.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>287562.6</v>
+        <v>252624</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>323456.1</t>
+          <t>286992.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>664782.5</v>
+        <v>639483.2</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-35893</t>
+          <t>-34368</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-49370.81863454734</t>
+          <t>-50054.82905734108</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-46587.93819697743</t>
+          <t>-53816.8863827067</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>262274.0</t>
+          <t>135802.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>133.27</t>
+          <t>138.24</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.41</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>55.41</t>
+          <t>54.74</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>624.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>630.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>600.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>377.0</t>
+          <t>428.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-11.10</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-28.24</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-10.02</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-7.9</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>657.8</t>
+          <t>641.0</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>718.95</v>
+        <v>712.35</v>
       </c>
       <c r="AN8" t="n">
-        <v>774.36</v>
+        <v>773.42</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>677.44</t>
+          <t>679.24</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-46.43</t>
+          <t>-44.55</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-34.54</t>
+          <t>-38.37</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-23.59</t>
+          <t>-26.55</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,53 +3670,53 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-126.22</t>
+          <t>-129.51</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/09/08</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>407921.3592715232</t>
+          <t>407167.6386138613</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>245558.0</t>
+          <t>262274.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>296429.4</v>
+        <v>287562.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>325427.2</t>
+          <t>323456.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>674644.66</v>
+        <v>664782.5</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-28997</t>
+          <t>-35893</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-49876.79689592369</t>
+          <t>-49370.81863454734</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-48147.58585318638</t>
+          <t>-46587.93819697743</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>245558.0</t>
+          <t>262274.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>143.98</t>
+          <t>133.27</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>55.41</t>
+          <t>54.74</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>624.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>672.0</t>
+          <t>630.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>600.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>371.0</t>
+          <t>377.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-23.31</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>671.6</t>
+          <t>657.8</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>725.65</v>
+        <v>718.95</v>
       </c>
       <c r="AN9" t="n">
-        <v>773.5599999999999</v>
+        <v>774.36</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>675.4</t>
+          <t>677.44</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-53.49</t>
+          <t>-46.43</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-32.01</t>
+          <t>-34.54</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-20.85</t>
+          <t>-23.59</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,53 +4100,53 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-123.18</t>
+          <t>-126.22</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/09/08</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>407921.3592715232</t>
+          <t>407167.6386138613</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>241508.0</t>
+          <t>245558.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>292951.6</v>
+        <v>296429.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>382000.7</t>
+          <t>325427.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>675976.12</v>
+        <v>674644.66</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-89049</t>
+          <t>-28997</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-50191.19890369411</t>
+          <t>-49876.79689592369</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-46865.09729587106</t>
+          <t>-48147.58585318638</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>241508.0</t>
+          <t>245558.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>55.41</t>
+          <t>54.74</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,12 +4276,12 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>667.0</t>
+          <t>672.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>371.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-22.67</t>
+          <t>-23.31</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-6.42</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>686.2</t>
+          <t>671.6</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>733.3</v>
+        <v>725.65</v>
       </c>
       <c r="AN10" t="n">
-        <v>772.84</v>
+        <v>773.5599999999999</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>675.4</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-57.81</t>
+          <t>-53.49</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-28.51</t>
+          <t>-32.01</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-18.06</t>
+          <t>-20.85</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,53 +4530,53 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-120.08</t>
+          <t>-123.18</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/09/08</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>407921.3592715232</t>
+          <t>407167.6386138613</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>377978.0</t>
+          <t>241508.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>309322.6</v>
+        <v>292951.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>400021.6</t>
+          <t>382000.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>677723.46</v>
+        <v>675976.12</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-90699</t>
+          <t>-89049</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-50795.94465057103</t>
+          <t>-50191.19890369411</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-42925.28873913951</t>
+          <t>-46865.09729587106</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>377978.0</t>
+          <t>241508.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>147.04</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>55.41</t>
+          <t>54.74</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>693.0</t>
+          <t>667.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>456.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-18.05</t>
+          <t>-22.67</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-21.06</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-6.42</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>702.8</t>
+          <t>686.2</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>740.6</v>
+        <v>733.3</v>
       </c>
       <c r="AN11" t="n">
-        <v>771.72</v>
+        <v>772.84</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>670.89</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-56.83</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-24.23</t>
+          <t>-28.51</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-18.06</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,53 +4960,53 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-117.18</t>
+          <t>-120.08</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/09/08</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>407921.3592715232</t>
+          <t>407167.6386138613</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>310495.0</t>
+          <t>377978.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>321361.4</v>
+        <v>309322.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>392151.7</t>
+          <t>400021.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>673300.1800000001</v>
+        <v>677723.46</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-70790</t>
+          <t>-90699</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-52226.97299810403</t>
+          <t>-50795.94465057103</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-50385.73048883944</t>
+          <t>-42925.28873913951</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>310495.0</t>
+          <t>377978.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>156.60</t>
+          <t>147.04</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>55.41</t>
+          <t>54.74</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>699.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>444.0</t>
+          <t>456.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-18.05</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-18.35</t>
+          <t>-21.06</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>15.03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>711.8</t>
+          <t>702.8</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>747.5</v>
+        <v>740.6</v>
       </c>
       <c r="AN12" t="n">
-        <v>770.14</v>
+        <v>771.72</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>668.28</t>
+          <t>670.89</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-58.22</t>
+          <t>-56.83</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-20.97</t>
+          <t>-24.23</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-15.45</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,53 +5390,53 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-114.74</t>
+          <t>-117.18</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/09/08</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>407921.3592715232</t>
+          <t>407167.6386138613</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>306608.0</t>
+          <t>310495.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>359349.6</v>
+        <v>321361.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>389319.8</t>
+          <t>392151.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>672018.02</v>
+        <v>673300.1800000001</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-29970</t>
+          <t>-70790</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-52561.74436342486</t>
+          <t>-52226.97299810403</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-52013.69261380937</t>
+          <t>-50385.73048883944</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>306608.0</t>
+          <t>310495.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>165.39</t>
+          <t>156.60</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>18.28</t>
+          <t>17.68</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>55.41</t>
+          <t>54.74</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5571,17 +5571,17 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>679.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5603,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1593.532</t>
+          <t>1854.297</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>191.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-15.71</t>
+          <t>-20.75</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>68.89</t>
+          <t>84.72</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-6.16</t>
+          <t>-4.30</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.23</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>187.0</t>
+          <t>189.1</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>199.28</v>
+        <v>197.6</v>
       </c>
       <c r="AN13" t="n">
-        <v>210.27</v>
+        <v>209.8</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>210.61</t>
+          <t>210.36</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-6.99</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,53 +5820,53 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-138.42</t>
+          <t>-138.19</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1323404754.243937</t>
+          <t>1322278574.850427</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>305259766.0</t>
+          <t>355217880.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>454773729.2</v>
+        <v>382951248.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>539557756.5</t>
+          <t>483247088.9</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>713839519.5</v>
+        <v>710756274.2</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-84784027</t>
+          <t>-100295840</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-24660949.91017646</t>
+          <t>-30154677.59391711</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-57859435.69935668</t>
+          <t>-60370179.85449064</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>305259766.0</t>
+          <t>355217880.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-11.87</t>
+          <t>-12.56</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>68282</t>
+          <t>67751</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>189.5</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>195.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>191.5</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1993.031</t>
+          <t>1593.532</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>189.0</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-16.73</t>
+          <t>-15.71</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-13.30</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,239 +6174,239 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
+          <t>68.89</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>-6.16</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>-5.23</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>-0.16</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>187.0</t>
+        </is>
+      </c>
+      <c r="AM14" t="n">
+        <v>199.28</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>210.27</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>210.61</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>-4.54</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>-7.53</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>-7.20</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>-138.42</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>1322278574.850427</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>305259766.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="n">
+        <v>454773729.2</v>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>539557756.5</t>
+        </is>
+      </c>
+      <c r="AZ14" t="n">
+        <v>713839519.5</v>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>-84784027</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>-24660949.91017646</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>-57859435.69935668</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>305259766.0</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>219.0</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>2025/09/18</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>-11.87</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>上銀</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>上銀</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>0.5246961718756727</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>-3.316042339543704</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr">
+        <is>
+          <t>-1.626286550608443</t>
+        </is>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="BU14" t="inlineStr">
+        <is>
+          <t>16.95</t>
+        </is>
+      </c>
+      <c r="BV14" t="inlineStr">
+        <is>
+          <t>48.6</t>
+        </is>
+      </c>
+      <c r="BW14" t="inlineStr">
+        <is>
+          <t>28.60%</t>
+        </is>
+      </c>
+      <c r="BX14" t="inlineStr">
+        <is>
+          <t>6.85%</t>
+        </is>
+      </c>
+      <c r="BY14" t="inlineStr">
+        <is>
           <t>40.82</t>
         </is>
       </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>-7.82</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>-4.69</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>185.1</t>
-        </is>
-      </c>
-      <c r="AM14" t="n">
-        <v>200.8</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>210.69</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>210.82</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>-16.00</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>-8.26</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>-7.12</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>18.75</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>-137.98</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>2025/10/23</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>1323404754.243937</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>375568987.0</t>
-        </is>
-      </c>
-      <c r="AX14" t="n">
-        <v>480990442.6</v>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>577604474.6</t>
-        </is>
-      </c>
-      <c r="AZ14" t="n">
-        <v>723589723.38</v>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>-96614032</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>-18624861.58487097</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>-46853594.84561682</t>
-        </is>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>375568987.0</t>
-        </is>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>219.0</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>2025/09/18</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>-13.70</t>
-        </is>
-      </c>
-      <c r="BI14" t="inlineStr">
-        <is>
-          <t>上銀</t>
-        </is>
-      </c>
-      <c r="BJ14" t="inlineStr">
-        <is>
-          <t>上銀</t>
-        </is>
-      </c>
-      <c r="BK14" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="BL14" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM14" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="BN14" t="inlineStr">
-        <is>
-          <t>0.5246961718756727</t>
-        </is>
-      </c>
-      <c r="BO14" t="inlineStr">
-        <is>
-          <t>-3.316042339543704</t>
-        </is>
-      </c>
-      <c r="BP14" t="inlineStr">
-        <is>
-          <t>-1.626286550608443</t>
-        </is>
-      </c>
-      <c r="BQ14" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR14" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS14" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
-      <c r="BT14" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="BU14" t="inlineStr">
-        <is>
-          <t>16.95</t>
-        </is>
-      </c>
-      <c r="BV14" t="inlineStr">
-        <is>
-          <t>48.98</t>
-        </is>
-      </c>
-      <c r="BW14" t="inlineStr">
-        <is>
-          <t>28.60%</t>
-        </is>
-      </c>
-      <c r="BX14" t="inlineStr">
-        <is>
-          <t>6.85%</t>
-        </is>
-      </c>
-      <c r="BY14" t="inlineStr">
-        <is>
-          <t>41.28</t>
-        </is>
-      </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>68282</t>
+          <t>67751</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
+          <t>189.5</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>193.0</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
           <t>189.0</t>
         </is>
       </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>190.5</t>
-        </is>
-      </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>187.0</t>
-        </is>
-      </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>189.0</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2044.942</t>
+          <t>1993.031</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>188.0</t>
+          <t>189.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-18.26</t>
+          <t>-16.73</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-13.76</t>
+          <t>-13.30</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-7.82</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>184.6</t>
+          <t>185.1</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>202.38</v>
+        <v>200.8</v>
       </c>
       <c r="AN15" t="n">
-        <v>211.26</v>
+        <v>210.69</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>211.12</t>
+          <t>210.82</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-26.76</t>
+          <t>-16.00</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-8.67</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,53 +6680,53 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-136.46</t>
+          <t>-137.98</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1323404754.243937</t>
+          <t>1322278574.850427</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>381363791.0</t>
+          <t>375568987.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>523400674.4</v>
+        <v>480990442.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>640315738.7</t>
+          <t>577604474.6</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>746361854.7</v>
+        <v>723589723.38</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-116915064</t>
+          <t>-96614032</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-13492364.62837173</t>
+          <t>-18624861.58487097</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-36990753.20293069</t>
+          <t>-46853594.84561682</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>381363791.0</t>
+          <t>375568987.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-14.16</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>68282</t>
+          <t>67751</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>184.5</t>
+          <t>189.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>188.0</t>
+          <t>190.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>184.5</t>
+          <t>187.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>188.0</t>
+          <t>189.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2724.529</t>
+          <t>2044.942</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-25.65</t>
+          <t>-18.26</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-15.60</t>
+          <t>-13.76</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-9.63</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>184.3</t>
+          <t>184.6</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>203.95</v>
+        <v>202.38</v>
       </c>
       <c r="AN16" t="n">
-        <v>211.72</v>
+        <v>211.26</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>211.42</t>
+          <t>211.12</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-40.39</t>
+          <t>-26.76</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-8.96</t>
+          <t>-8.67</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,53 +7110,53 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-134.02</t>
+          <t>-136.46</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1323404754.243937</t>
+          <t>1322278574.850427</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>497345820.0</t>
+          <t>381363791.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>538397244.2</v>
+        <v>523400674.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>724156183.6</t>
+          <t>640315738.7</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>755881026.66</v>
+        <v>746361854.7</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-185758939</t>
+          <t>-116915064</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-9219930.34208828</t>
+          <t>-13492364.62837173</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-22200752.9561317</t>
+          <t>-36990753.20293069</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>497345820.0</t>
+          <t>381363791.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-15.98</t>
+          <t>-14.16</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>68282</t>
+          <t>67751</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>182.5</t>
+          <t>184.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>184.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3925.483</t>
+          <t>2724.529</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-20.19</t>
+          <t>-25.65</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-16.97</t>
+          <t>-15.60</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-10.16</t>
+          <t>-9.63</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>184.8</t>
+          <t>184.3</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>205.7</v>
+        <v>203.95</v>
       </c>
       <c r="AN17" t="n">
-        <v>212.36</v>
+        <v>211.72</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>211.81</t>
+          <t>211.42</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-53.22</t>
+          <t>-40.39</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-8.79</t>
+          <t>-8.96</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,53 +7540,53 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-130.59</t>
+          <t>-134.02</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1323404754.243937</t>
+          <t>1322278574.850427</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>714330282.0</t>
+          <t>497345820.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>583542929</v>
+        <v>538397244.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>731190758.4</t>
+          <t>724156183.6</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>788163169.8</v>
+        <v>755881026.66</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-147647829</t>
+          <t>-185758939</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-6859780.775898567</t>
+          <t>-9219930.34208828</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-12705943.10512841</t>
+          <t>-22200752.9561317</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>714330282.0</t>
+          <t>497345820.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-17.35</t>
+          <t>-15.98</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>68282</t>
+          <t>67751</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>182.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>180.5</t>
+          <t>181.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2375.624</t>
+          <t>3925.483</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>181.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-13.38</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-15.83</t>
+          <t>-16.97</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>7.37</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,12 +7894,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7914,53 +7914,53 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-9.85</t>
+          <t>-10.16</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>187.2</t>
+          <t>184.8</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>207.65</v>
+        <v>205.7</v>
       </c>
       <c r="AN18" t="n">
-        <v>213.15</v>
+        <v>212.36</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>212.2</t>
+          <t>211.81</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-63.70</t>
+          <t>-53.22</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-8.14</t>
+          <t>-8.79</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,53 +7970,53 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-126.52</t>
+          <t>-130.59</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1323404754.243937</t>
+          <t>1322278574.850427</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>436343333.0</t>
+          <t>714330282.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>624341783.8</v>
+        <v>583542929</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>720759640.4</t>
+          <t>731190758.4</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>863704924.02</v>
+        <v>788163169.8</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-96417856</t>
+          <t>-147647829</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-5796842.170584051</t>
+          <t>-6859780.775898567</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-21936480.56422627</t>
+          <t>-12705943.10512841</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>436343333.0</t>
+          <t>714330282.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-16.21</t>
+          <t>-17.35</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>68282</t>
+          <t>67751</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>184.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>180.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>181.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3128.645</t>
+          <t>2375.624</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>186.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-13.38</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-14.45</t>
+          <t>-15.83</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>7.37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,12 +8324,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8344,53 +8344,53 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-9.85</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>190.2</t>
+          <t>187.2</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>209.58</v>
+        <v>207.65</v>
       </c>
       <c r="AN19" t="n">
-        <v>213.6</v>
+        <v>213.15</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>212.58</t>
+          <t>212.2</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-78.19</t>
+          <t>-63.70</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-8.14</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,53 +8400,53 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-122.29</t>
+          <t>-126.52</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1323404754.243937</t>
+          <t>1322278574.850427</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>587620146.0</t>
+          <t>436343333.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>674218506.6</v>
+        <v>624341783.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>715379759.4</t>
+          <t>720759640.4</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>864477556.2</v>
+        <v>863704924.02</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-41161252</t>
+          <t>-96417856</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-2862362.462649101</t>
+          <t>-5796842.170584051</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-4555200.949929357</t>
+          <t>-21936480.56422627</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>587620146.0</t>
+          <t>436343333.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-14.84</t>
+          <t>-16.21</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>68282</t>
+          <t>67751</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>189.5</t>
+          <t>184.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>191.5</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>186.5</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>186.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2437.772</t>
+          <t>3128.645</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-8.70</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>192.9</t>
+          <t>190.2</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>211.28</v>
+        <v>209.58</v>
       </c>
       <c r="AN20" t="n">
-        <v>214.03</v>
+        <v>213.6</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>212.96</t>
+          <t>212.58</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-101.13</t>
+          <t>-78.19</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,53 +8830,53 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-117.94</t>
+          <t>-122.29</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1323404754.243937</t>
+          <t>1322278574.850427</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>456346640.0</t>
+          <t>587620146.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>757230803</v>
+        <v>674218506.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>678685106.5</t>
+          <t>715379759.4</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>856936697.08</v>
+        <v>864477556.2</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>78545696</t>
+          <t>-41161252</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-2554573.646779964</t>
+          <t>-2862362.462649101</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>4229654.282992125</t>
+          <t>-4555200.949929357</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>456346640.0</t>
+          <t>587620146.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8941,12 +8941,12 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>68282</t>
+          <t>67751</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,17 +9006,17 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
+          <t>189.5</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
+          <t>191.5</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
           <t>186.5</t>
-        </is>
-      </c>
-      <c r="CE20" t="inlineStr">
-        <is>
-          <t>190.0</t>
-        </is>
-      </c>
-      <c r="CF20" t="inlineStr">
-        <is>
-          <t>185.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3839.598</t>
+          <t>2437.772</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-8.70</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>196.6</t>
+          <t>192.9</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>212.75</v>
+        <v>211.28</v>
       </c>
       <c r="AN21" t="n">
-        <v>214.42</v>
+        <v>214.03</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>213.34</t>
+          <t>212.96</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-130.49</t>
+          <t>-101.13</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,53 +9260,53 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-113.40</t>
+          <t>-117.94</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1323404754.243937</t>
+          <t>1322278574.850427</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>723074244.0</t>
+          <t>456346640.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>909915123</v>
+        <v>757230803</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>674907487.9</t>
+          <t>678685106.5</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>854335140.0599999</v>
+        <v>856936697.08</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>235007635</t>
+          <t>78545696</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-3788069.634011253</t>
+          <t>-2554573.646779964</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>30693406.89134467</t>
+          <t>4229654.282992125</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>723074244.0</t>
+          <t>456346640.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>68282</t>
+          <t>67751</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,17 +9436,17 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>191.5</t>
+          <t>190.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4701.928</t>
+          <t>3839.598</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-14.45</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14.59</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>201.2</t>
+          <t>196.6</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>213.98</v>
+        <v>212.75</v>
       </c>
       <c r="AN22" t="n">
-        <v>214.79</v>
+        <v>214.42</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>213.72</t>
+          <t>213.34</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-163.83</t>
+          <t>-130.49</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,53 +9690,53 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-109.03</t>
+          <t>-113.40</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1323404754.243937</t>
+          <t>1322278574.850427</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>918324556.0</t>
+          <t>723074244.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>878838587.8</v>
+        <v>909915123</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>691621829.4</t>
+          <t>674907487.9</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>845368183.24</v>
+        <v>854335140.0599999</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>187216758</t>
+          <t>235007635</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-10057429.00225778</t>
+          <t>-3788069.634011253</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>38824617.085729</t>
+          <t>30693406.89134467</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>918324556.0</t>
+          <t>723074244.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-11.87</t>
+          <t>-14.84</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>68282</t>
+          <t>67751</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>191.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3457.008</t>
+          <t>4701.928</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>25.67</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-8.94</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10.72</t>
+          <t>14.59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,53 +10064,53 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>204.6</t>
+          <t>201.2</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>214.72</v>
+        <v>213.98</v>
       </c>
       <c r="AN23" t="n">
-        <v>215.02</v>
+        <v>214.79</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>213.92</t>
+          <t>213.72</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-237.34</t>
+          <t>-163.83</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,53 +10120,53 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-105.33</t>
+          <t>-109.03</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1323404754.243937</t>
+          <t>1322278574.850427</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>685726947.0</t>
+          <t>918324556.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>817177497</v>
+        <v>878838587.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>650263422.9</t>
+          <t>691621829.4</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>838743112.42</v>
+        <v>845368183.24</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>166914074</t>
+          <t>187216758</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-18945073.74552811</t>
+          <t>-10057429.00225778</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>28134361.89607322</t>
+          <t>38824617.085729</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>685726947.0</t>
+          <t>918324556.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-11.87</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>68282</t>
+          <t>67751</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>195.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>198.5</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/工業型機器人.xlsx
+++ b/Result/checksun_type/工業型機器人.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-27.56</t>
+          <t>-22.34</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-23.88</t>
+          <t>-23.29</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,274 +1014,274 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>215</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>82.22</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>76.04</t>
+          <t>91.85</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.65</t>
+          <t>-11.96</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
+          <t>646.4</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>675.15</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>766.86</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>697.59</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>6.83</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>-30.84</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-33.10</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>89.95</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-136.79</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>406522.3519736843</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>140667.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>135365.2</v>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>174307.3</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>574226.34</v>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-38942</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-52374.34377918849</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-49605.36603708362</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>140667.0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>261.5</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2025/05/15</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>149.33</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>5.417317991953463</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>102.0481335952849</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>95.34284575725091</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>17.18</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>9.59</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>55.16</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>66.48%</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>53.80%</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>45.09</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>15166</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>竹陞科技-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>647.0</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>669.0</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>644.0</t>
         </is>
       </c>
-      <c r="AM2" t="n">
-        <v>678.35</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>767.8200000000001</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>695.44</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-33.00</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-33.66</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>89.95</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-137.42</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>407167.6386138613</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>119696.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>143452.8</v>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>198038.4</t>
-        </is>
-      </c>
-      <c r="AZ2" t="n">
-        <v>598609.88</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-54585</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-52877.79427775302</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>-52898.73523776597</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>119696.0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>261.5</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>2025/05/15</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>147.42</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>5.417317991953463</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>102.0481335952849</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>95.34284575725091</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>17.04</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>0.77</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>9.59</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>54.74</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>66.48%</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>53.80%</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>44.93</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>15050</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>竹陞科技-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>663.0</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>663.0</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>637.0</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>249.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-32.45</t>
+          <t>-27.56</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-22.94</t>
+          <t>-23.88</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>215</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.22</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>60.54</t>
+          <t>76.04</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-6.43</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.22</t>
+          <t>-11.65</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>639.2</t>
+          <t>644.0</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>683.15</v>
+        <v>678.35</v>
       </c>
       <c r="AN3" t="n">
-        <v>769.46</v>
+        <v>767.8200000000001</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>692.9</t>
+          <t>695.44</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-34.77</t>
+          <t>-33.00</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-33.83</t>
+          <t>-33.66</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-137.60</t>
+          <t>-137.42</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>407167.6386138613</t>
+          <t>406522.3519736843</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>161450.0</t>
+          <t>119696.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>146674</v>
+        <v>143452.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>217118.3</t>
+          <t>198038.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>615716.62</v>
+        <v>598609.88</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-70444</t>
+          <t>-54585</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-52873.98683047794</t>
+          <t>-52877.79427775302</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-53467.41498024913</t>
+          <t>-52898.73523776597</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>161450.0</t>
+          <t>119696.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>150.48</t>
+          <t>147.42</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>54.74</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>15166</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>656.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>247.0</t>
+          <t>249.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-27.97</t>
+          <t>-32.45</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-22.94</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>215</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>37.51</t>
+          <t>60.54</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-6.43</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-10.5</t>
+          <t>-11.22</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>630.2</t>
+          <t>639.2</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>688.8</v>
+        <v>683.15</v>
       </c>
       <c r="AN4" t="n">
-        <v>769.62</v>
+        <v>769.46</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>690.04</t>
+          <t>692.9</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-11.17</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-37.34</t>
+          <t>-34.77</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-33.59</t>
+          <t>-33.83</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-137.34</t>
+          <t>-137.60</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>407167.6386138613</t>
+          <t>406522.3519736843</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>159302.0</t>
+          <t>161450.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>166838.8</v>
+        <v>146674</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>231634.1</t>
+          <t>217118.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>622148.62</v>
+        <v>615716.62</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-64795</t>
+          <t>-70444</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-52766.09080324681</t>
+          <t>-52873.98683047794</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-56843.90693450192</t>
+          <t>-53467.41498024913</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>159302.0</t>
+          <t>161450.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>143.98</t>
+          <t>150.48</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>54.74</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>15166</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>651.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>658.0</t>
+          <t>656.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>247.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-22.82</t>
+          <t>-27.97</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,42 +2304,42 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>215</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>37.51</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-9.86</t>
+          <t>-10.5</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>12.14</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -2348,29 +2348,29 @@
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>694.75</v>
+        <v>688.8</v>
       </c>
       <c r="AN5" t="n">
-        <v>770.74</v>
+        <v>769.62</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>687.31</t>
+          <t>690.04</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-17.45</t>
+          <t>-11.17</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-38.35</t>
+          <t>-37.34</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-32.65</t>
+          <t>-33.59</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-136.30</t>
+          <t>-137.34</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>407167.6386138613</t>
+          <t>406522.3519736843</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>184090</v>
+        <v>166838.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>238520.8</t>
+          <t>231634.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>625496.02</v>
+        <v>622148.62</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-54430</t>
+          <t>-64795</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-52024.66968847315</t>
+          <t>-52766.09080324681</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-59407.18447863078</t>
+          <t>-56843.90693450192</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>54.74</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>15166</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>651.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>658.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>636.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>283.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-18.38</t>
+          <t>-22.82</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,22 +2734,22 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>215</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>30.93</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -2759,17 +2759,17 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-10.13</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-9.11</t>
+          <t>-9.86</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2778,29 +2778,29 @@
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>701.25</v>
+        <v>694.75</v>
       </c>
       <c r="AN6" t="n">
-        <v>771.5599999999999</v>
+        <v>770.74</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>684.56</t>
+          <t>687.31</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-25.78</t>
+          <t>-17.45</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-39.28</t>
+          <t>-38.35</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-31.23</t>
+          <t>-32.65</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-134.72</t>
+          <t>-136.30</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>407167.6386138613</t>
+          <t>406522.3519736843</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>213249.4</v>
+        <v>184090</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>261286.0</t>
+          <t>238520.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>631907.8</v>
+        <v>625496.02</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-48036</t>
+          <t>-54430</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-50682.39427208085</t>
+          <t>-52024.66968847315</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-54134.00295314955</t>
+          <t>-59407.18447863078</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>54.74</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>15166</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>629.0</t>
+          <t>636.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>283.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-18.38</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-26.71</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>215</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>12.62</t>
+          <t>30.93</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-10.13</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-9.11</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>13.29</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>631.4</t>
+          <t>630.2</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>706</v>
+        <v>701.25</v>
       </c>
       <c r="AN7" t="n">
-        <v>772.34</v>
+        <v>771.5599999999999</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>681.75</t>
+          <t>684.56</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-36.56</t>
+          <t>-25.78</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-39.90</t>
+          <t>-39.28</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-29.22</t>
+          <t>-31.23</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-132.48</t>
+          <t>-134.72</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>407167.6386138613</t>
+          <t>406522.3519736843</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>135802.0</t>
+          <t>181105.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>252624</v>
+        <v>213249.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>286992.7</t>
+          <t>261286.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>639483.2</v>
+        <v>631907.8</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-34368</t>
+          <t>-48036</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-50054.82905734108</t>
+          <t>-50682.39427208085</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-53816.8863827067</t>
+          <t>-54134.00295314955</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>135802.0</t>
+          <t>181105.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>138.24</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>16.41</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>54.74</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>15166</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>639.0</t>
+          <t>654.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>629.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>428.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-11.10</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-28.24</t>
+          <t>-26.71</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>215</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.62</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-10.02</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-7.9</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>13.29</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>641.0</t>
+          <t>631.4</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>712.35</v>
+        <v>706</v>
       </c>
       <c r="AN8" t="n">
-        <v>773.42</v>
+        <v>772.34</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>679.24</t>
+          <t>681.75</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-44.55</t>
+          <t>-36.56</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-38.37</t>
+          <t>-39.90</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-26.55</t>
+          <t>-29.22</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-129.51</t>
+          <t>-132.48</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>407167.6386138613</t>
+          <t>406522.3519736843</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>262274.0</t>
+          <t>135802.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>287562.6</v>
+        <v>252624</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>323456.1</t>
+          <t>286992.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>664782.5</v>
+        <v>639483.2</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-35893</t>
+          <t>-34368</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-49370.81863454734</t>
+          <t>-50054.82905734108</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-46587.93819697743</t>
+          <t>-53816.8863827067</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>262274.0</t>
+          <t>135802.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>133.27</t>
+          <t>138.24</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.41</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>54.74</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>15166</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>624.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>630.0</t>
+          <t>639.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>600.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>377.0</t>
+          <t>428.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-11.10</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-28.24</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>215</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-10.02</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-7.9</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>657.8</t>
+          <t>641.0</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>718.95</v>
+        <v>712.35</v>
       </c>
       <c r="AN9" t="n">
-        <v>774.36</v>
+        <v>773.42</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>677.44</t>
+          <t>679.24</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-46.43</t>
+          <t>-44.55</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-34.54</t>
+          <t>-38.37</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-23.59</t>
+          <t>-26.55</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-126.22</t>
+          <t>-129.51</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>407167.6386138613</t>
+          <t>406522.3519736843</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>245558.0</t>
+          <t>262274.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>296429.4</v>
+        <v>287562.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>325427.2</t>
+          <t>323456.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>674644.66</v>
+        <v>664782.5</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-28997</t>
+          <t>-35893</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-49876.79689592369</t>
+          <t>-49370.81863454734</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-48147.58585318638</t>
+          <t>-46587.93819697743</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>245558.0</t>
+          <t>262274.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>143.98</t>
+          <t>133.27</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>54.74</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>15166</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>624.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>672.0</t>
+          <t>630.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>600.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>371.0</t>
+          <t>377.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-23.31</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>215</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>671.6</t>
+          <t>657.8</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>725.65</v>
+        <v>718.95</v>
       </c>
       <c r="AN10" t="n">
-        <v>773.5599999999999</v>
+        <v>774.36</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>675.4</t>
+          <t>677.44</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-53.49</t>
+          <t>-46.43</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-32.01</t>
+          <t>-34.54</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-20.85</t>
+          <t>-23.59</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-123.18</t>
+          <t>-126.22</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>407167.6386138613</t>
+          <t>406522.3519736843</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>241508.0</t>
+          <t>245558.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>292951.6</v>
+        <v>296429.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>382000.7</t>
+          <t>325427.2</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>675976.12</v>
+        <v>674644.66</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-89049</t>
+          <t>-28997</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-50191.19890369411</t>
+          <t>-49876.79689592369</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-46865.09729587106</t>
+          <t>-48147.58585318638</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>241508.0</t>
+          <t>245558.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>54.74</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>15166</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>664.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>667.0</t>
+          <t>672.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>371.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-22.67</t>
+          <t>-23.31</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>215</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-6.42</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>686.2</t>
+          <t>671.6</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>733.3</v>
+        <v>725.65</v>
       </c>
       <c r="AN11" t="n">
-        <v>772.84</v>
+        <v>773.5599999999999</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>675.4</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-57.81</t>
+          <t>-53.49</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-28.51</t>
+          <t>-32.01</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-18.06</t>
+          <t>-20.85</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-120.08</t>
+          <t>-123.18</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>407167.6386138613</t>
+          <t>406522.3519736843</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>377978.0</t>
+          <t>241508.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>309322.6</v>
+        <v>292951.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>400021.6</t>
+          <t>382000.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>677723.46</v>
+        <v>675976.12</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-90699</t>
+          <t>-89049</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-50795.94465057103</t>
+          <t>-50191.19890369411</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-42925.28873913951</t>
+          <t>-46865.09729587106</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>377978.0</t>
+          <t>241508.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>147.04</t>
+          <t>144.74</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>54.74</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>15166</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>693.0</t>
+          <t>667.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>456.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-18.05</t>
+          <t>-22.67</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-21.06</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>215</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-6.42</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>702.8</t>
+          <t>686.2</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>740.6</v>
+        <v>733.3</v>
       </c>
       <c r="AN12" t="n">
-        <v>771.72</v>
+        <v>772.84</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>670.89</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-56.83</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-24.23</t>
+          <t>-28.51</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-18.06</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-117.18</t>
+          <t>-120.08</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>407167.6386138613</t>
+          <t>406522.3519736843</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>310495.0</t>
+          <t>377978.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>321361.4</v>
+        <v>309322.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>392151.7</t>
+          <t>400021.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>673300.1800000001</v>
+        <v>677723.46</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-70790</t>
+          <t>-90699</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-52226.97299810403</t>
+          <t>-50795.94465057103</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-50385.73048883944</t>
+          <t>-42925.28873913951</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>310495.0</t>
+          <t>377978.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>156.60</t>
+          <t>147.04</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>54.74</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>15166</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>699.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>646.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1854.297</t>
+          <t>814.019</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>191.5</t>
+          <t>192.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-20.75</t>
+          <t>-26.22</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.70</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>814</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>95.83</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>84.72</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-4.30</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>189.1</t>
+          <t>190.8</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>197.6</v>
+        <v>196.38</v>
       </c>
       <c r="AN13" t="n">
-        <v>209.8</v>
+        <v>209.33</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>210.36</t>
+          <t>210.15</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-6.99</t>
+          <t>-6.41</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-7.01</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-138.19</t>
+          <t>-137.39</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1322278574.850427</t>
+          <t>1320731018.272404</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>355217880.0</t>
+          <t>156230867.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>382951248.8</v>
+        <v>314728258.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>483247088.9</t>
+          <t>426562751.2</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>710756274.2</v>
+        <v>700938521.76</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-100295840</t>
+          <t>-111834493</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-30154677.59391711</t>
+          <t>-37137415.23204096</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-60370179.85449064</t>
+          <t>-75542472.24172217</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>355217880.0</t>
+          <t>156230867.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-12.56</t>
+          <t>-12.10</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.86</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>67751</t>
+          <t>68105</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>190.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>195.5</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>189.0</t>
+          <t>190.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>191.5</t>
+          <t>192.5</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6033,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1593.532</t>
+          <t>1854.297</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>191.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-15.71</t>
+          <t>-20.75</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>814</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>68.89</t>
+          <t>84.72</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-6.16</t>
+          <t>-4.30</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-5.23</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>187.0</t>
+          <t>189.1</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>199.28</v>
+        <v>197.6</v>
       </c>
       <c r="AN14" t="n">
-        <v>210.27</v>
+        <v>209.8</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>210.61</t>
+          <t>210.36</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-6.99</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-138.42</t>
+          <t>-138.19</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1322278574.850427</t>
+          <t>1320731018.272404</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>305259766.0</t>
+          <t>355217880.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>454773729.2</v>
+        <v>382951248.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>539557756.5</t>
+          <t>483247088.9</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>713839519.5</v>
+        <v>710756274.2</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-84784027</t>
+          <t>-100295840</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-24660949.91017646</t>
+          <t>-30154677.59391711</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-57859435.69935668</t>
+          <t>-60370179.85449064</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>305259766.0</t>
+          <t>355217880.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-11.87</t>
+          <t>-12.56</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.86</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>67751</t>
+          <t>68105</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>189.5</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>195.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>191.5</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1993.031</t>
+          <t>1593.532</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>189.0</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-16.73</t>
+          <t>-15.71</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-13.30</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>814</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>68.89</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-7.82</t>
+          <t>-6.16</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-5.23</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>185.1</t>
+          <t>187.0</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>200.8</v>
+        <v>199.28</v>
       </c>
       <c r="AN15" t="n">
-        <v>210.69</v>
+        <v>210.27</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>210.82</t>
+          <t>210.61</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-16.00</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-137.98</t>
+          <t>-138.42</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1322278574.850427</t>
+          <t>1320731018.272404</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>375568987.0</t>
+          <t>305259766.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>480990442.6</v>
+        <v>454773729.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>577604474.6</t>
+          <t>539557756.5</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>723589723.38</v>
+        <v>713839519.5</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-96614032</t>
+          <t>-84784027</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-18624861.58487097</t>
+          <t>-24660949.91017646</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-46853594.84561682</t>
+          <t>-57859435.69935668</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>375568987.0</t>
+          <t>305259766.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-11.87</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.86</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>67751</t>
+          <t>68105</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
+          <t>189.5</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>193.0</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
           <t>189.0</t>
         </is>
       </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>190.5</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>187.0</t>
-        </is>
-      </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>189.0</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2044.942</t>
+          <t>1993.031</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>188.0</t>
+          <t>189.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-18.26</t>
+          <t>-16.73</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-13.76</t>
+          <t>-13.30</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>814</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-7.82</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>184.6</t>
+          <t>185.1</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>202.38</v>
+        <v>200.8</v>
       </c>
       <c r="AN16" t="n">
-        <v>211.26</v>
+        <v>210.69</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>211.12</t>
+          <t>210.82</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-26.76</t>
+          <t>-16.00</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-8.67</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-6.84</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-136.46</t>
+          <t>-137.98</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1322278574.850427</t>
+          <t>1320731018.272404</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>381363791.0</t>
+          <t>375568987.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>523400674.4</v>
+        <v>480990442.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>640315738.7</t>
+          <t>577604474.6</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>746361854.7</v>
+        <v>723589723.38</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-116915064</t>
+          <t>-96614032</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-13492364.62837173</t>
+          <t>-18624861.58487097</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-36990753.20293069</t>
+          <t>-46853594.84561682</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>381363791.0</t>
+          <t>375568987.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-14.16</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,17 +7221,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.86</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>67751</t>
+          <t>68105</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>184.5</t>
+          <t>189.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>188.0</t>
+          <t>190.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>184.5</t>
+          <t>187.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>188.0</t>
+          <t>189.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2724.529</t>
+          <t>2044.942</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-25.65</t>
+          <t>-18.26</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-15.60</t>
+          <t>-13.76</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>814</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-9.63</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>184.3</t>
+          <t>184.6</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>203.95</v>
+        <v>202.38</v>
       </c>
       <c r="AN17" t="n">
-        <v>211.72</v>
+        <v>211.26</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>211.42</t>
+          <t>211.12</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-40.39</t>
+          <t>-26.76</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-8.96</t>
+          <t>-8.67</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-134.02</t>
+          <t>-136.46</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1322278574.850427</t>
+          <t>1320731018.272404</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>497345820.0</t>
+          <t>381363791.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>538397244.2</v>
+        <v>523400674.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>724156183.6</t>
+          <t>640315738.7</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>755881026.66</v>
+        <v>746361854.7</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-185758939</t>
+          <t>-116915064</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-9219930.34208828</t>
+          <t>-13492364.62837173</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-22200752.9561317</t>
+          <t>-36990753.20293069</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>497345820.0</t>
+          <t>381363791.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-15.98</t>
+          <t>-14.16</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.86</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>67751</t>
+          <t>68105</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>182.5</t>
+          <t>184.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>184.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3925.483</t>
+          <t>2724.529</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-20.19</t>
+          <t>-25.65</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-16.97</t>
+          <t>-15.60</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>814</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-10.16</t>
+          <t>-9.63</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>184.8</t>
+          <t>184.3</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>205.7</v>
+        <v>203.95</v>
       </c>
       <c r="AN18" t="n">
-        <v>212.36</v>
+        <v>211.72</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>211.81</t>
+          <t>211.42</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-53.22</t>
+          <t>-40.39</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-8.79</t>
+          <t>-8.96</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-130.59</t>
+          <t>-134.02</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1322278574.850427</t>
+          <t>1320731018.272404</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>714330282.0</t>
+          <t>497345820.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>583542929</v>
+        <v>538397244.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>731190758.4</t>
+          <t>724156183.6</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>788163169.8</v>
+        <v>755881026.66</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-147647829</t>
+          <t>-185758939</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-6859780.775898567</t>
+          <t>-9219930.34208828</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-12705943.10512841</t>
+          <t>-22200752.9561317</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>714330282.0</t>
+          <t>497345820.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-17.35</t>
+          <t>-15.98</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,17 +8081,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.86</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>67751</t>
+          <t>68105</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>182.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>180.5</t>
+          <t>181.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2375.624</t>
+          <t>3925.483</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>181.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-13.38</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-15.83</t>
+          <t>-16.97</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>7.37</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,12 +8324,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>814</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8344,53 +8344,53 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-9.85</t>
+          <t>-10.16</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>187.2</t>
+          <t>184.8</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>207.65</v>
+        <v>205.7</v>
       </c>
       <c r="AN19" t="n">
-        <v>213.15</v>
+        <v>212.36</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>212.2</t>
+          <t>211.81</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-63.70</t>
+          <t>-53.22</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-8.14</t>
+          <t>-8.79</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-126.52</t>
+          <t>-130.59</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1322278574.850427</t>
+          <t>1320731018.272404</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>436343333.0</t>
+          <t>714330282.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>624341783.8</v>
+        <v>583542929</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>720759640.4</t>
+          <t>731190758.4</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>863704924.02</v>
+        <v>788163169.8</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-96417856</t>
+          <t>-147647829</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-5796842.170584051</t>
+          <t>-6859780.775898567</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-21936480.56422627</t>
+          <t>-12705943.10512841</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>436343333.0</t>
+          <t>714330282.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-16.21</t>
+          <t>-17.35</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,17 +8511,17 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.86</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>67751</t>
+          <t>68105</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>184.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>180.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>181.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3128.645</t>
+          <t>2375.624</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>186.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-13.38</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-14.45</t>
+          <t>-15.83</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>7.37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>814</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-9.24</t>
+          <t>-9.85</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>190.2</t>
+          <t>187.2</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>209.58</v>
+        <v>207.65</v>
       </c>
       <c r="AN20" t="n">
-        <v>213.6</v>
+        <v>213.15</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>212.58</t>
+          <t>212.2</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-78.19</t>
+          <t>-63.70</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-8.14</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-122.29</t>
+          <t>-126.52</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1322278574.850427</t>
+          <t>1320731018.272404</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>587620146.0</t>
+          <t>436343333.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>674218506.6</v>
+        <v>624341783.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>715379759.4</t>
+          <t>720759640.4</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>864477556.2</v>
+        <v>863704924.02</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-41161252</t>
+          <t>-96417856</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-2862362.462649101</t>
+          <t>-5796842.170584051</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-4555200.949929357</t>
+          <t>-21936480.56422627</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>587620146.0</t>
+          <t>436343333.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-14.84</t>
+          <t>-16.21</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,17 +8941,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.86</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>67751</t>
+          <t>68105</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>189.5</t>
+          <t>184.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>191.5</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>186.5</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>186.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2437.772</t>
+          <t>3128.645</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>814</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-8.70</t>
+          <t>-9.24</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>192.9</t>
+          <t>190.2</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>211.28</v>
+        <v>209.58</v>
       </c>
       <c r="AN21" t="n">
-        <v>214.03</v>
+        <v>213.6</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>212.96</t>
+          <t>212.58</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-101.13</t>
+          <t>-78.19</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-7.45</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-117.94</t>
+          <t>-122.29</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1322278574.850427</t>
+          <t>1320731018.272404</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>456346640.0</t>
+          <t>587620146.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>757230803</v>
+        <v>674218506.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>678685106.5</t>
+          <t>715379759.4</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>856936697.08</v>
+        <v>864477556.2</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>78545696</t>
+          <t>-41161252</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-2554573.646779964</t>
+          <t>-2862362.462649101</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>4229654.282992125</t>
+          <t>-4555200.949929357</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>456346640.0</t>
+          <t>587620146.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9371,12 +9371,12 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.86</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>67751</t>
+          <t>68105</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,17 +9436,17 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
+          <t>189.5</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
+        <is>
+          <t>191.5</t>
+        </is>
+      </c>
+      <c r="CF21" t="inlineStr">
+        <is>
           <t>186.5</t>
-        </is>
-      </c>
-      <c r="CE21" t="inlineStr">
-        <is>
-          <t>190.0</t>
-        </is>
-      </c>
-      <c r="CF21" t="inlineStr">
-        <is>
-          <t>185.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3839.598</t>
+          <t>2437.772</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>814</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-8.70</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>196.6</t>
+          <t>192.9</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>212.75</v>
+        <v>211.28</v>
       </c>
       <c r="AN22" t="n">
-        <v>214.42</v>
+        <v>214.03</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>213.34</t>
+          <t>212.96</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-130.49</t>
+          <t>-101.13</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-113.40</t>
+          <t>-117.94</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1322278574.850427</t>
+          <t>1320731018.272404</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>723074244.0</t>
+          <t>456346640.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>909915123</v>
+        <v>757230803</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>674907487.9</t>
+          <t>678685106.5</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>854335140.0599999</v>
+        <v>856936697.08</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>235007635</t>
+          <t>78545696</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-3788069.634011253</t>
+          <t>-2554573.646779964</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>30693406.89134467</t>
+          <t>4229654.282992125</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>723074244.0</t>
+          <t>456346640.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.86</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>67751</t>
+          <t>68105</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,17 +9866,17 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>191.5</t>
+          <t>190.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4701.928</t>
+          <t>3839.598</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-14.45</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14.59</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>814</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,53 +10064,53 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>201.2</t>
+          <t>196.6</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>213.98</v>
+        <v>212.75</v>
       </c>
       <c r="AN23" t="n">
-        <v>214.79</v>
+        <v>214.42</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>213.72</t>
+          <t>213.34</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-163.83</t>
+          <t>-130.49</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-109.03</t>
+          <t>-113.40</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1322278574.850427</t>
+          <t>1320731018.272404</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>918324556.0</t>
+          <t>723074244.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>878838587.8</v>
+        <v>909915123</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>691621829.4</t>
+          <t>674907487.9</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>845368183.24</v>
+        <v>854335140.0599999</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>187216758</t>
+          <t>235007635</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-10057429.00225778</t>
+          <t>-3788069.634011253</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>38824617.085729</t>
+          <t>30693406.89134467</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>918324556.0</t>
+          <t>723074244.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-11.87</t>
+          <t>-14.84</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.86</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>67751</t>
+          <t>68105</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>191.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>193.0</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/工業型機器人.xlsx
+++ b/Result/checksun_type/工業型機器人.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>696.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-22.34</t>
+          <t>7.34</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-23.29</t>
+          <t>-15.65</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1034,53 +1034,53 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>8.34</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.96</t>
+          <t>-12.0</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>646.4</t>
+          <t>661.8</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>675.15</v>
+        <v>674.65</v>
       </c>
       <c r="AN2" t="n">
-        <v>766.86</v>
+        <v>766.6799999999999</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>697.59</t>
+          <t>700.39</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-30.84</t>
+          <t>-23.61</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-33.10</t>
+          <t>-31.20</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-136.79</t>
+          <t>-134.68</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>406522.3519736843</t>
+          <t>407575.7262295082</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>140667.0</t>
+          <t>485201.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>135365.2</v>
+        <v>213263.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>174307.3</t>
+          <t>198676.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>574226.34</v>
+        <v>573003.24</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-38942</t>
+          <t>14586</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-52374.34377918849</t>
+          <t>-47427.49449711009</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-49605.36603708362</t>
+          <t>-20219.82344567886</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>140667.0</t>
+          <t>485201.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>149.33</t>
+          <t>174.19</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>658.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>669.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>644.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>186.0</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-27.56</t>
+          <t>-22.34</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-23.88</t>
+          <t>-23.29</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,7 +1444,7 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1454,264 +1454,264 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>82.22</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>76.04</t>
+          <t>91.85</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.65</t>
+          <t>-11.96</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
+          <t>646.4</t>
+        </is>
+      </c>
+      <c r="AM3" t="n">
+        <v>675.15</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>766.86</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>697.59</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>6.83</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>-30.84</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>-33.10</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>89.95</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-136.79</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>407575.7262295082</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>140667.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
+        <v>135365.2</v>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>174307.3</t>
+        </is>
+      </c>
+      <c r="AZ3" t="n">
+        <v>574226.34</v>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>-38942</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-52374.34377918849</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-49605.36603708362</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>140667.0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>261.5</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2025/05/15</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>149.33</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>5.417317991953463</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>102.0481335952849</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>95.34284575725091</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>17.18</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>9.59</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>55.16</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>66.48%</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>53.80%</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>45.09</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>15166</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>竹陞科技-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>647.0</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>669.0</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>644.0</t>
         </is>
       </c>
-      <c r="AM3" t="n">
-        <v>678.35</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>767.8200000000001</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>695.44</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-33.00</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-33.66</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>89.95</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-137.42</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>406522.3519736843</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>119696.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="n">
-        <v>143452.8</v>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>198038.4</t>
-        </is>
-      </c>
-      <c r="AZ3" t="n">
-        <v>598609.88</v>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>-54585</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-52877.79427775302</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>-52898.73523776597</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>119696.0</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>261.5</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>2025/05/15</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>147.42</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>5.417317991953463</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>102.0481335952849</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>95.34284575725091</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>17.04</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>0.77</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>9.59</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>55.16</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>66.48%</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>53.80%</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>45.09</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>15166</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>智能自動操作系統(AI)47.21%、製程數據採集系統(IOT)38.72%、智能化(GoVision)13.88%、其他0.18% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>竹陞科技-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>663.0</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>663.0</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>637.0</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1726,14 +1726,14 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>249.0</t>
+          <t>186.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-32.45</t>
+          <t>-27.56</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-22.94</t>
+          <t>-23.88</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,7 +1874,7 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1884,63 +1884,63 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.22</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>60.54</t>
+          <t>76.04</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-6.43</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-11.22</t>
+          <t>-11.65</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>639.2</t>
+          <t>644.0</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>683.15</v>
+        <v>678.35</v>
       </c>
       <c r="AN4" t="n">
-        <v>769.46</v>
+        <v>767.8200000000001</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>692.9</t>
+          <t>695.44</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-34.77</t>
+          <t>-33.00</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-33.83</t>
+          <t>-33.66</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-137.60</t>
+          <t>-137.42</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>406522.3519736843</t>
+          <t>407575.7262295082</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>161450.0</t>
+          <t>119696.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>146674</v>
+        <v>143452.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>217118.3</t>
+          <t>198038.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>615716.62</v>
+        <v>598609.88</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-70444</t>
+          <t>-54585</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-52873.98683047794</t>
+          <t>-52877.79427775302</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-53467.41498024913</t>
+          <t>-52898.73523776597</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>161450.0</t>
+          <t>119696.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>150.48</t>
+          <t>147.42</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>656.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>637.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>647.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>247.0</t>
+          <t>249.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-27.97</t>
+          <t>-32.45</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-24.94</t>
+          <t>-22.94</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,7 +2304,7 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -2314,63 +2314,63 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>37.51</t>
+          <t>60.54</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-6.43</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-10.5</t>
+          <t>-11.22</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>630.2</t>
+          <t>639.2</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>688.8</v>
+        <v>683.15</v>
       </c>
       <c r="AN5" t="n">
-        <v>769.62</v>
+        <v>769.46</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>690.04</t>
+          <t>692.9</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-11.17</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-37.34</t>
+          <t>-34.77</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-33.59</t>
+          <t>-33.83</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-137.34</t>
+          <t>-137.60</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>406522.3519736843</t>
+          <t>407575.7262295082</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>159302.0</t>
+          <t>161450.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>166838.8</v>
+        <v>146674</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>231634.1</t>
+          <t>217118.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>622148.62</v>
+        <v>615716.62</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-64795</t>
+          <t>-70444</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-52766.09080324681</t>
+          <t>-52873.98683047794</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-56843.90693450192</t>
+          <t>-53467.41498024913</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>159302.0</t>
+          <t>161450.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>143.98</t>
+          <t>150.48</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>651.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>658.0</t>
+          <t>656.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>247.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-22.82</t>
+          <t>-27.97</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-24.94</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,7 +2734,7 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2744,32 +2744,32 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>37.51</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-9.86</t>
+          <t>-10.5</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>12.14</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2778,29 +2778,29 @@
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>694.75</v>
+        <v>688.8</v>
       </c>
       <c r="AN6" t="n">
-        <v>770.74</v>
+        <v>769.62</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>687.31</t>
+          <t>690.04</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-17.45</t>
+          <t>-11.17</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-38.35</t>
+          <t>-37.34</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-32.65</t>
+          <t>-33.59</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-136.30</t>
+          <t>-137.34</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>406522.3519736843</t>
+          <t>407575.7262295082</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>184090</v>
+        <v>166838.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>238520.8</t>
+          <t>231634.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>625496.02</v>
+        <v>622148.62</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-54430</t>
+          <t>-64795</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-52024.66968847315</t>
+          <t>-52766.09080324681</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-59407.18447863078</t>
+          <t>-56843.90693450192</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>95711.0</t>
+          <t>159302.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>144.74</t>
+          <t>143.98</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>651.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>652.0</t>
+          <t>658.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>636.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>640.0</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>283.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-18.38</t>
+          <t>-22.82</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,7 +3164,7 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>30.93</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
@@ -3189,17 +3189,17 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-10.13</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-9.11</t>
+          <t>-9.86</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -3208,29 +3208,29 @@
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>701.25</v>
+        <v>694.75</v>
       </c>
       <c r="AN7" t="n">
-        <v>771.5599999999999</v>
+        <v>770.74</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>684.56</t>
+          <t>687.31</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-25.78</t>
+          <t>-17.45</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-39.28</t>
+          <t>-38.35</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-31.23</t>
+          <t>-32.65</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-134.72</t>
+          <t>-136.30</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>406522.3519736843</t>
+          <t>407575.7262295082</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>213249.4</v>
+        <v>184090</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>261286.0</t>
+          <t>238520.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>631907.8</v>
+        <v>625496.02</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-48036</t>
+          <t>-54430</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-50682.39427208085</t>
+          <t>-52024.66968847315</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-54134.00295314955</t>
+          <t>-59407.18447863078</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>181105.0</t>
+          <t>95711.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3416,17 +3416,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>654.0</t>
+          <t>652.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>629.0</t>
+          <t>636.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>283.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-18.38</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-26.71</t>
+          <t>-24.71</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,7 +3594,7 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -3604,63 +3604,63 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>12.62</t>
+          <t>30.93</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-10.13</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-9.11</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>13.29</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>631.4</t>
+          <t>630.2</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>706</v>
+        <v>701.25</v>
       </c>
       <c r="AN8" t="n">
-        <v>772.34</v>
+        <v>771.5599999999999</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>681.75</t>
+          <t>684.56</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-36.56</t>
+          <t>-25.78</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-39.90</t>
+          <t>-39.2